--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122789059</v>
+        <v>122789232</v>
       </c>
       <c r="B2" t="n">
-        <v>98347</v>
+        <v>78766</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,39 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -727,13 +726,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513471</v>
+        <v>513455</v>
       </c>
       <c r="R2" t="n">
-        <v>6732628</v>
+        <v>6732564</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +761,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +771,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -788,22 +787,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122789232</v>
+        <v>122785451</v>
       </c>
       <c r="B3" t="n">
-        <v>78762</v>
+        <v>97309</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,52 +811,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513455</v>
+        <v>513456</v>
       </c>
       <c r="R3" t="n">
-        <v>6732564</v>
+        <v>6732571</v>
       </c>
       <c r="S3" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -886,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,19 +893,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -927,7 +914,7 @@
         <v>122789060</v>
       </c>
       <c r="B4" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1049,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122785451</v>
+        <v>122789602</v>
       </c>
       <c r="B5" t="n">
-        <v>97301</v>
+        <v>56688</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1065,34 +1052,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513456</v>
+        <v>513429</v>
       </c>
       <c r="R5" t="n">
-        <v>6732571</v>
+        <v>6732681</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1124,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1134,7 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Några hundra spillning</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1149,12 +1141,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1278,10 +1270,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122785684</v>
+        <v>122789059</v>
       </c>
       <c r="B7" t="n">
-        <v>98347</v>
+        <v>98355</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1311,17 +1303,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kyrkleden, Kyrkleden, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513524</v>
+        <v>513471</v>
       </c>
       <c r="R7" t="n">
-        <v>6732635</v>
+        <v>6732628</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1353,7 +1357,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1363,7 +1367,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,28 +1376,29 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122789602</v>
+        <v>122785684</v>
       </c>
       <c r="B8" t="n">
-        <v>56688</v>
+        <v>98355</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1402,38 +1407,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Kyrkleden, Kyrkleden, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513429</v>
+        <v>513524</v>
       </c>
       <c r="R8" t="n">
-        <v>6732681</v>
+        <v>6732635</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1465,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1475,12 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Några hundra spillning</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1495,22 +1495,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122791693</v>
+        <v>122798012</v>
       </c>
       <c r="B9" t="n">
-        <v>56688</v>
+        <v>90909</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,37 +1523,48 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100138</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513491</v>
+        <v>513484</v>
       </c>
       <c r="R9" t="n">
-        <v>6732749</v>
+        <v>6732609</v>
       </c>
       <c r="S9" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1582,7 +1593,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1592,12 +1603,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1606,6 +1612,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1624,10 +1631,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122789158</v>
+        <v>122791590</v>
       </c>
       <c r="B10" t="n">
-        <v>98347</v>
+        <v>97318</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1640,28 +1647,24 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>552</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Cypresslummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium tristachyum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Pursh</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
@@ -1672,10 +1675,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513468</v>
+        <v>513512</v>
       </c>
       <c r="R10" t="n">
-        <v>6732639</v>
+        <v>6732717</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1707,7 +1710,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1717,12 +1720,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
+          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,10 +1753,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122798012</v>
+        <v>122791693</v>
       </c>
       <c r="B11" t="n">
-        <v>90905</v>
+        <v>56688</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1766,48 +1769,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513484</v>
+        <v>513491</v>
       </c>
       <c r="R11" t="n">
-        <v>6732609</v>
+        <v>6732749</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1836,7 +1828,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1846,7 +1838,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1855,7 +1852,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1874,10 +1870,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122791590</v>
+        <v>122789158</v>
       </c>
       <c r="B12" t="n">
-        <v>97310</v>
+        <v>98355</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1890,24 +1886,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>552</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cypresslummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium tristachyum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pursh</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1918,10 +1918,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513512</v>
+        <v>513468</v>
       </c>
       <c r="R12" t="n">
-        <v>6732717</v>
+        <v>6732639</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,7 +1953,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1963,12 +1963,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
+          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1999,7 +1999,7 @@
         <v>122790237</v>
       </c>
       <c r="B13" t="n">
-        <v>97301</v>
+        <v>97309</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2108,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122789796</v>
+        <v>122788763</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>98355</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,38 +2120,46 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513425</v>
+        <v>513482</v>
       </c>
       <c r="R14" t="n">
-        <v>6732654</v>
+        <v>6732623</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2183,7 +2191,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2193,7 +2201,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2202,6 +2215,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2220,10 +2234,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122792630</v>
+        <v>122789796</v>
       </c>
       <c r="B15" t="n">
-        <v>97301</v>
+        <v>5173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2236,21 +2250,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2260,10 +2274,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513571</v>
+        <v>513425</v>
       </c>
       <c r="R15" t="n">
-        <v>6732676</v>
+        <v>6732654</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2309,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2305,7 +2319,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2444,10 +2458,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122788763</v>
+        <v>122792630</v>
       </c>
       <c r="B17" t="n">
-        <v>98347</v>
+        <v>97309</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2456,46 +2470,38 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513482</v>
+        <v>513571</v>
       </c>
       <c r="R17" t="n">
-        <v>6732623</v>
+        <v>6732676</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2527,7 +2533,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2537,12 +2543,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2551,7 +2552,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122785451</v>
+        <v>122789060</v>
       </c>
       <c r="B3" t="n">
-        <v>97309</v>
+        <v>98355</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,41 +811,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513456</v>
+        <v>513469</v>
       </c>
       <c r="R3" t="n">
-        <v>6732571</v>
+        <v>6732636</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,28 +905,29 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122789060</v>
+        <v>122785451</v>
       </c>
       <c r="B4" t="n">
-        <v>98355</v>
+        <v>97309</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -923,53 +936,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513469</v>
+        <v>513456</v>
       </c>
       <c r="R4" t="n">
-        <v>6732636</v>
+        <v>6732571</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1017,19 +1018,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1270,7 +1270,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122789059</v>
+        <v>122785684</v>
       </c>
       <c r="B7" t="n">
         <v>98355</v>
@@ -1303,29 +1303,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Kyrkleden, Kyrkleden, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513471</v>
+        <v>513524</v>
       </c>
       <c r="R7" t="n">
-        <v>6732628</v>
+        <v>6732635</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1357,7 +1345,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1367,7 +1355,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1376,26 +1364,25 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122785684</v>
+        <v>122789059</v>
       </c>
       <c r="B8" t="n">
         <v>98355</v>
@@ -1428,17 +1415,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kyrkleden, Kyrkleden, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513524</v>
+        <v>513471</v>
       </c>
       <c r="R8" t="n">
-        <v>6732635</v>
+        <v>6732628</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1469,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1479,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1489,28 +1488,29 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122798012</v>
+        <v>122788763</v>
       </c>
       <c r="B9" t="n">
-        <v>90909</v>
+        <v>98355</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1519,49 +1519,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513484</v>
+        <v>513482</v>
       </c>
       <c r="R9" t="n">
-        <v>6732609</v>
+        <v>6732623</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1593,7 +1590,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1603,7 +1600,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1631,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122791590</v>
+        <v>122798012</v>
       </c>
       <c r="B10" t="n">
-        <v>97318</v>
+        <v>90909</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1643,42 +1645,49 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>552</v>
+        <v>5447</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Cypresslummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium tristachyum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Pursh</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513512</v>
+        <v>513484</v>
       </c>
       <c r="R10" t="n">
-        <v>6732717</v>
+        <v>6732609</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1710,7 +1719,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1720,12 +1729,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1753,10 +1757,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122791693</v>
+        <v>122790237</v>
       </c>
       <c r="B11" t="n">
-        <v>56688</v>
+        <v>97309</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1769,21 +1773,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1793,13 +1797,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513491</v>
+        <v>513429</v>
       </c>
       <c r="R11" t="n">
-        <v>6732749</v>
+        <v>6732604</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1828,7 +1832,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1838,12 +1842,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1870,10 +1869,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122789158</v>
+        <v>122791590</v>
       </c>
       <c r="B12" t="n">
-        <v>98355</v>
+        <v>97318</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1886,28 +1885,24 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>552</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Cypresslummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium tristachyum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
+          <t>Pursh</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1918,10 +1913,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513468</v>
+        <v>513512</v>
       </c>
       <c r="R12" t="n">
-        <v>6732639</v>
+        <v>6732717</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,7 +1948,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1963,12 +1958,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
+          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1996,10 +1991,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122790237</v>
+        <v>122791693</v>
       </c>
       <c r="B13" t="n">
-        <v>97309</v>
+        <v>56688</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2012,21 +2007,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2036,13 +2031,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513429</v>
+        <v>513491</v>
       </c>
       <c r="R13" t="n">
-        <v>6732604</v>
+        <v>6732749</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2071,7 +2066,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2081,7 +2076,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,10 +2108,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122788763</v>
+        <v>122792108</v>
       </c>
       <c r="B14" t="n">
-        <v>98355</v>
+        <v>8441</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2120,46 +2120,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513482</v>
+        <v>513619</v>
       </c>
       <c r="R14" t="n">
-        <v>6732623</v>
+        <v>6732790</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2191,7 +2183,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2201,12 +2193,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2215,7 +2202,6 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>
@@ -2234,10 +2220,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122789796</v>
+        <v>122792630</v>
       </c>
       <c r="B15" t="n">
-        <v>5173</v>
+        <v>97309</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2250,21 +2236,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2274,10 +2260,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513425</v>
+        <v>513571</v>
       </c>
       <c r="R15" t="n">
-        <v>6732654</v>
+        <v>6732676</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2309,7 +2295,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2319,7 +2305,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2346,10 +2332,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122792108</v>
+        <v>122789158</v>
       </c>
       <c r="B16" t="n">
-        <v>8441</v>
+        <v>98355</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2358,38 +2344,46 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513619</v>
+        <v>513468</v>
       </c>
       <c r="R16" t="n">
-        <v>6732790</v>
+        <v>6732639</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2421,7 +2415,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2431,7 +2425,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2440,6 +2439,7 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2458,10 +2458,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122792630</v>
+        <v>122789796</v>
       </c>
       <c r="B17" t="n">
-        <v>97309</v>
+        <v>5173</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,21 +2474,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2498,10 +2498,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513571</v>
+        <v>513425</v>
       </c>
       <c r="R17" t="n">
-        <v>6732676</v>
+        <v>6732654</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2533,7 +2533,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2543,7 +2543,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD17" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122789232</v>
+        <v>122785451</v>
       </c>
       <c r="B2" t="n">
-        <v>78766</v>
+        <v>97311</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,52 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513455</v>
+        <v>513456</v>
       </c>
       <c r="R2" t="n">
-        <v>6732564</v>
+        <v>6732571</v>
       </c>
       <c r="S2" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -771,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -780,19 +769,18 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -802,7 +790,7 @@
         <v>122789060</v>
       </c>
       <c r="B3" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -924,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122785451</v>
+        <v>122789232</v>
       </c>
       <c r="B4" t="n">
-        <v>97309</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -936,41 +924,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513456</v>
+        <v>513455</v>
       </c>
       <c r="R4" t="n">
-        <v>6732571</v>
+        <v>6732564</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +998,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +1008,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,25 +1017,26 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122789602</v>
+        <v>122789501</v>
       </c>
       <c r="B5" t="n">
         <v>56688</v>
@@ -1076,10 +1076,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513429</v>
+        <v>513426</v>
       </c>
       <c r="R5" t="n">
-        <v>6732681</v>
+        <v>6732668</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1121,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>Några hundra spillning</t>
+          <t>Ett 40-tal spillning i upplösning under äldre/gammal tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1153,10 +1153,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122789501</v>
+        <v>122785684</v>
       </c>
       <c r="B6" t="n">
-        <v>56688</v>
+        <v>98357</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1165,38 +1165,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Kyrkleden, Kyrkleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513426</v>
+        <v>513524</v>
       </c>
       <c r="R6" t="n">
-        <v>6732668</v>
+        <v>6732635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,12 +1238,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ett 40-tal spillning i upplösning under äldre/gammal tall</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1258,22 +1253,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122785684</v>
+        <v>122789602</v>
       </c>
       <c r="B7" t="n">
-        <v>98355</v>
+        <v>56688</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1282,38 +1277,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kyrkleden, Kyrkleden, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513524</v>
+        <v>513429</v>
       </c>
       <c r="R7" t="n">
-        <v>6732635</v>
+        <v>6732681</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1345,7 +1340,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1355,7 +1350,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Några hundra spillning</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,12 +1370,12 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
@@ -1385,7 +1385,7 @@
         <v>122789059</v>
       </c>
       <c r="B8" t="n">
-        <v>98355</v>
+        <v>98357</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1507,10 +1507,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122788763</v>
+        <v>122791590</v>
       </c>
       <c r="B9" t="n">
-        <v>98355</v>
+        <v>97320</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,28 +1523,24 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>552</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Cypresslummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium tristachyum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>Pursh</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1555,10 +1551,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513482</v>
+        <v>513512</v>
       </c>
       <c r="R9" t="n">
-        <v>6732623</v>
+        <v>6732717</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1600,12 +1596,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Uppskattat antal</t>
+          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,10 +1629,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122798012</v>
+        <v>122792108</v>
       </c>
       <c r="B10" t="n">
-        <v>90909</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,45 +1645,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5447</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513484</v>
+        <v>513619</v>
       </c>
       <c r="R10" t="n">
-        <v>6732609</v>
+        <v>6732790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1719,7 +1704,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1729,7 +1714,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,7 +1723,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1757,10 +1741,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122790237</v>
+        <v>122789158</v>
       </c>
       <c r="B11" t="n">
-        <v>97309</v>
+        <v>98357</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1769,38 +1753,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513429</v>
+        <v>513468</v>
       </c>
       <c r="R11" t="n">
-        <v>6732604</v>
+        <v>6732639</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1832,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1842,7 +1834,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,6 +1848,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1869,10 +1867,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122791590</v>
+        <v>122791693</v>
       </c>
       <c r="B12" t="n">
-        <v>97318</v>
+        <v>56688</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1881,45 +1879,41 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>552</v>
+        <v>100138</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cypresslummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium tristachyum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pursh</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513512</v>
+        <v>513491</v>
       </c>
       <c r="R12" t="n">
-        <v>6732717</v>
+        <v>6732749</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1948,7 +1942,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1958,12 +1952,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1972,7 +1966,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1991,10 +1984,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122791693</v>
+        <v>122790237</v>
       </c>
       <c r="B13" t="n">
-        <v>56688</v>
+        <v>97311</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2007,21 +2000,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2031,13 +2024,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513491</v>
+        <v>513429</v>
       </c>
       <c r="R13" t="n">
-        <v>6732749</v>
+        <v>6732604</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2066,7 +2059,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2076,12 +2069,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2108,10 +2096,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122792108</v>
+        <v>122789796</v>
       </c>
       <c r="B14" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2124,21 +2112,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2148,10 +2136,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513619</v>
+        <v>513425</v>
       </c>
       <c r="R14" t="n">
-        <v>6732790</v>
+        <v>6732654</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2183,7 +2171,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2193,7 +2181,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2220,10 +2208,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122792630</v>
+        <v>122788763</v>
       </c>
       <c r="B15" t="n">
-        <v>97309</v>
+        <v>98357</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2232,38 +2220,46 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513571</v>
+        <v>513482</v>
       </c>
       <c r="R15" t="n">
-        <v>6732676</v>
+        <v>6732623</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2295,7 +2291,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2305,7 +2301,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2314,6 +2315,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2332,10 +2334,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122789158</v>
+        <v>122792630</v>
       </c>
       <c r="B16" t="n">
-        <v>98355</v>
+        <v>97311</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2344,46 +2346,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513468</v>
+        <v>513571</v>
       </c>
       <c r="R16" t="n">
-        <v>6732639</v>
+        <v>6732676</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2415,7 +2409,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2425,12 +2419,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2439,7 +2428,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2455,118 +2443,6 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>122789796</v>
-      </c>
-      <c r="B17" t="n">
-        <v>5173</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>100526</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Bronshjon</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>Falun, Falun, Dlr</t>
-        </is>
-      </c>
-      <c r="Q17" t="n">
-        <v>513425</v>
-      </c>
-      <c r="R17" t="n">
-        <v>6732654</v>
-      </c>
-      <c r="S17" t="n">
-        <v>10</v>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>15:12</t>
-        </is>
-      </c>
-      <c r="AD17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT17" t="inlineStr"/>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY16"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1036,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122789501</v>
+        <v>122785684</v>
       </c>
       <c r="B5" t="n">
-        <v>56688</v>
+        <v>98357</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,38 +1048,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Kyrkleden, Kyrkleden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513426</v>
+        <v>513524</v>
       </c>
       <c r="R5" t="n">
-        <v>6732668</v>
+        <v>6732635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,12 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ett 40-tal spillning i upplösning under äldre/gammal tall</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1141,19 +1136,19 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122785684</v>
+        <v>122789059</v>
       </c>
       <c r="B6" t="n">
         <v>98357</v>
@@ -1186,17 +1181,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kyrkleden, Kyrkleden, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513524</v>
+        <v>513471</v>
       </c>
       <c r="R6" t="n">
-        <v>6732635</v>
+        <v>6732628</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1228,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1238,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1247,28 +1254,29 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122789602</v>
+        <v>122791590</v>
       </c>
       <c r="B7" t="n">
-        <v>56688</v>
+        <v>97320</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1277,38 +1285,42 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>552</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Cypresslummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium tristachyum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Pursh</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513429</v>
+        <v>513512</v>
       </c>
       <c r="R7" t="n">
-        <v>6732681</v>
+        <v>6732717</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1340,7 +1352,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1350,12 +1362,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Några hundra spillning</t>
+          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1364,6 +1376,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1382,10 +1395,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122789059</v>
+        <v>122792108</v>
       </c>
       <c r="B8" t="n">
-        <v>98357</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1394,50 +1407,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513471</v>
+        <v>513619</v>
       </c>
       <c r="R8" t="n">
-        <v>6732628</v>
+        <v>6732790</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1469,7 +1470,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1479,7 +1480,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1488,29 +1489,28 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122791590</v>
+        <v>122789158</v>
       </c>
       <c r="B9" t="n">
-        <v>97320</v>
+        <v>98357</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,24 +1523,28 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>552</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Cypresslummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium tristachyum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Pursh</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
@@ -1551,10 +1555,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513512</v>
+        <v>513468</v>
       </c>
       <c r="R9" t="n">
-        <v>6732717</v>
+        <v>6732639</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1586,7 +1590,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,12 +1600,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
+          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1629,10 +1633,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122792108</v>
+        <v>122791693</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>56688</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1645,21 +1649,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>100138</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1669,13 +1673,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513619</v>
+        <v>513491</v>
       </c>
       <c r="R10" t="n">
-        <v>6732790</v>
+        <v>6732749</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1704,7 +1708,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1714,7 +1718,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1741,10 +1750,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122789158</v>
+        <v>122790237</v>
       </c>
       <c r="B11" t="n">
-        <v>98357</v>
+        <v>97311</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1753,46 +1762,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513468</v>
+        <v>513429</v>
       </c>
       <c r="R11" t="n">
-        <v>6732639</v>
+        <v>6732604</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,7 +1825,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,12 +1835,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1848,7 +1844,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1867,10 +1862,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122791693</v>
+        <v>122789796</v>
       </c>
       <c r="B12" t="n">
-        <v>56688</v>
+        <v>5173</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1883,21 +1878,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1907,13 +1902,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513491</v>
+        <v>513425</v>
       </c>
       <c r="R12" t="n">
-        <v>6732749</v>
+        <v>6732654</v>
       </c>
       <c r="S12" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1942,7 +1937,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1952,12 +1947,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1984,10 +1974,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122790237</v>
+        <v>122788763</v>
       </c>
       <c r="B13" t="n">
-        <v>97311</v>
+        <v>98357</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1996,38 +1986,46 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513429</v>
+        <v>513482</v>
       </c>
       <c r="R13" t="n">
-        <v>6732604</v>
+        <v>6732623</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2059,7 +2057,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2069,7 +2067,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2078,6 +2081,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2096,10 +2100,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122789796</v>
+        <v>122792630</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>97311</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2112,21 +2116,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2136,10 +2140,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513425</v>
+        <v>513571</v>
       </c>
       <c r="R14" t="n">
-        <v>6732654</v>
+        <v>6732676</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2171,7 +2175,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,7 +2185,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2205,244 +2209,6 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" t="n">
-        <v>122788763</v>
-      </c>
-      <c r="B15" t="n">
-        <v>98357</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E15" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>Falun, Falun, Dlr</t>
-        </is>
-      </c>
-      <c r="Q15" t="n">
-        <v>513482</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6732623</v>
-      </c>
-      <c r="S15" t="n">
-        <v>10</v>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
-        </is>
-      </c>
-      <c r="AD15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF15" t="inlineStr"/>
-      <c r="AG15" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT15" t="inlineStr"/>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AY15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>122792630</v>
-      </c>
-      <c r="B16" t="n">
-        <v>97311</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E16" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>Falun, Falun, Dlr</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>513571</v>
-      </c>
-      <c r="R16" t="n">
-        <v>6732676</v>
-      </c>
-      <c r="S16" t="n">
-        <v>10</v>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>Leksand</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>2025-02-27</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AD16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT16" t="inlineStr"/>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>Evalena Sköld</t>
-        </is>
-      </c>
-      <c r="AY16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122785451</v>
+        <v>122789060</v>
       </c>
       <c r="B2" t="n">
-        <v>97311</v>
+        <v>98357</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513456</v>
+        <v>513469</v>
       </c>
       <c r="R2" t="n">
-        <v>6732571</v>
+        <v>6732636</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,28 +781,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122789060</v>
+        <v>122785451</v>
       </c>
       <c r="B3" t="n">
-        <v>98357</v>
+        <v>97311</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,53 +812,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513469</v>
+        <v>513456</v>
       </c>
       <c r="R3" t="n">
-        <v>6732636</v>
+        <v>6732571</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,29 +894,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122789232</v>
+        <v>122789059</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>98357</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,38 +924,39 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -963,13 +964,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513455</v>
+        <v>513471</v>
       </c>
       <c r="R4" t="n">
-        <v>6732564</v>
+        <v>6732628</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -998,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1008,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1024,22 +1025,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122785684</v>
+        <v>122789232</v>
       </c>
       <c r="B5" t="n">
-        <v>98357</v>
+        <v>78766</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1048,41 +1049,52 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kyrkleden, Kyrkleden, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513524</v>
+        <v>513455</v>
       </c>
       <c r="R5" t="n">
-        <v>6732635</v>
+        <v>6732564</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1111,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1133,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,6 +1142,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1148,7 +1161,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122789059</v>
+        <v>122785684</v>
       </c>
       <c r="B6" t="n">
         <v>98357</v>
@@ -1181,29 +1194,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Kyrkleden, Kyrkleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513471</v>
+        <v>513524</v>
       </c>
       <c r="R6" t="n">
-        <v>6732628</v>
+        <v>6732635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,29 +1255,28 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122791590</v>
+        <v>122789158</v>
       </c>
       <c r="B7" t="n">
-        <v>97320</v>
+        <v>98357</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,24 +1289,28 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>552</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Cypresslummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium tristachyum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Pursh</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
       <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
@@ -1317,10 +1321,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513512</v>
+        <v>513468</v>
       </c>
       <c r="R7" t="n">
-        <v>6732717</v>
+        <v>6732639</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1352,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1362,12 +1366,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
+          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1395,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122792108</v>
+        <v>122789796</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,21 +1415,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1435,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513619</v>
+        <v>513425</v>
       </c>
       <c r="R8" t="n">
-        <v>6732790</v>
+        <v>6732654</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1470,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1480,7 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1507,7 +1511,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122789158</v>
+        <v>122788763</v>
       </c>
       <c r="B9" t="n">
         <v>98357</v>
@@ -1542,7 +1546,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1555,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513468</v>
+        <v>513482</v>
       </c>
       <c r="R9" t="n">
-        <v>6732639</v>
+        <v>6732623</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1590,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1600,12 +1604,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1633,10 +1637,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122791693</v>
+        <v>122790237</v>
       </c>
       <c r="B10" t="n">
-        <v>56688</v>
+        <v>97311</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1649,21 +1653,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1673,13 +1677,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513491</v>
+        <v>513429</v>
       </c>
       <c r="R10" t="n">
-        <v>6732749</v>
+        <v>6732604</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1708,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1718,12 +1722,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1750,7 +1749,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122790237</v>
+        <v>122792630</v>
       </c>
       <c r="B11" t="n">
         <v>97311</v>
@@ -1790,10 +1789,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513429</v>
+        <v>513571</v>
       </c>
       <c r="R11" t="n">
-        <v>6732604</v>
+        <v>6732676</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1825,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1835,7 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1862,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122789796</v>
+        <v>122791590</v>
       </c>
       <c r="B12" t="n">
-        <v>5173</v>
+        <v>97320</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1874,38 +1873,42 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>552</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Cypresslummer</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium tristachyum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Pursh</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513425</v>
+        <v>513512</v>
       </c>
       <c r="R12" t="n">
-        <v>6732654</v>
+        <v>6732717</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1937,7 +1940,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1947,7 +1950,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1956,6 +1964,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1974,10 +1983,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122788763</v>
+        <v>122792108</v>
       </c>
       <c r="B13" t="n">
-        <v>98357</v>
+        <v>8441</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1986,46 +1995,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513482</v>
+        <v>513619</v>
       </c>
       <c r="R13" t="n">
-        <v>6732623</v>
+        <v>6732790</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2057,7 +2058,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2067,12 +2068,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2081,7 +2077,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2100,10 +2095,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122792630</v>
+        <v>122791693</v>
       </c>
       <c r="B14" t="n">
-        <v>97311</v>
+        <v>56688</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2116,21 +2111,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2140,13 +2135,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513571</v>
+        <v>513491</v>
       </c>
       <c r="R14" t="n">
-        <v>6732676</v>
+        <v>6732749</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2175,7 +2170,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2185,7 +2180,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122789060</v>
+        <v>122785451</v>
       </c>
       <c r="B2" t="n">
-        <v>98357</v>
+        <v>97319</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513469</v>
+        <v>513456</v>
       </c>
       <c r="R2" t="n">
-        <v>6732636</v>
+        <v>6732571</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,29 +769,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122785451</v>
+        <v>122789059</v>
       </c>
       <c r="B3" t="n">
-        <v>97311</v>
+        <v>98365</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,38 +799,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513456</v>
+        <v>513471</v>
       </c>
       <c r="R3" t="n">
-        <v>6732571</v>
+        <v>6732628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -875,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,6 +893,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122789059</v>
+        <v>122785684</v>
       </c>
       <c r="B4" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -945,29 +945,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Kyrkleden, Kyrkleden, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513471</v>
+        <v>513524</v>
       </c>
       <c r="R4" t="n">
-        <v>6732628</v>
+        <v>6732635</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1018,19 +1006,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1161,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122785684</v>
+        <v>122789060</v>
       </c>
       <c r="B6" t="n">
-        <v>98357</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1194,20 +1181,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Kyrkleden, Kyrkleden, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513524</v>
+        <v>513469</v>
       </c>
       <c r="R6" t="n">
-        <v>6732635</v>
+        <v>6732636</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1236,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1246,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,6 +1254,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122789158</v>
+        <v>122792108</v>
       </c>
       <c r="B7" t="n">
-        <v>98357</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,46 +1285,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513468</v>
+        <v>513619</v>
       </c>
       <c r="R7" t="n">
-        <v>6732639</v>
+        <v>6732790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,12 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,7 +1367,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1399,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122789796</v>
+        <v>122789158</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,38 +1397,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513425</v>
+        <v>513468</v>
       </c>
       <c r="R8" t="n">
-        <v>6732654</v>
+        <v>6732639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1478,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,6 +1492,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1511,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122788763</v>
+        <v>122790237</v>
       </c>
       <c r="B9" t="n">
-        <v>98357</v>
+        <v>97319</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,46 +1523,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513482</v>
+        <v>513429</v>
       </c>
       <c r="R9" t="n">
-        <v>6732623</v>
+        <v>6732604</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,12 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1618,7 +1605,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1637,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122790237</v>
+        <v>122792630</v>
       </c>
       <c r="B10" t="n">
-        <v>97311</v>
+        <v>97319</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1677,10 +1663,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513429</v>
+        <v>513571</v>
       </c>
       <c r="R10" t="n">
-        <v>6732604</v>
+        <v>6732676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1698,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,7 +1708,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122792630</v>
+        <v>122789796</v>
       </c>
       <c r="B11" t="n">
-        <v>97311</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1765,21 +1751,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1789,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513571</v>
+        <v>513425</v>
       </c>
       <c r="R11" t="n">
-        <v>6732676</v>
+        <v>6732654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,7 +1810,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,7 +1820,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1861,10 +1847,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122791590</v>
+        <v>122788763</v>
       </c>
       <c r="B12" t="n">
-        <v>97320</v>
+        <v>98365</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1877,24 +1863,28 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>552</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Cypresslummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium tristachyum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Pursh</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
@@ -1905,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513512</v>
+        <v>513482</v>
       </c>
       <c r="R12" t="n">
-        <v>6732717</v>
+        <v>6732623</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1940,7 +1930,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1950,12 +1940,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1983,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122792108</v>
+        <v>122798012</v>
       </c>
       <c r="B13" t="n">
-        <v>8441</v>
+        <v>90917</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1999,34 +1989,45 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>106545</v>
+        <v>5447</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513619</v>
+        <v>513484</v>
       </c>
       <c r="R13" t="n">
-        <v>6732790</v>
+        <v>6732609</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2058,7 +2059,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2068,7 +2069,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2077,6 +2078,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2095,10 +2097,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122791693</v>
+        <v>122791590</v>
       </c>
       <c r="B14" t="n">
-        <v>56688</v>
+        <v>97325</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2111,37 +2113,41 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513491</v>
+        <v>513512</v>
       </c>
       <c r="R14" t="n">
-        <v>6732749</v>
+        <v>6732717</v>
       </c>
       <c r="S14" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2170,7 +2176,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2180,12 +2186,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC14" t="inlineStr">
         <is>
-          <t>Blåbärsspillning</t>
+          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2194,6 +2200,7 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY14"/>
+  <dimension ref="A1:AY15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2217,6 +2217,127 @@
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>123174254</v>
+      </c>
+      <c r="B15" t="n">
+        <v>78766</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>513372</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6732617</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:21</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>stora långa tuvor varav några sätt mycket högre än jag nådde, på tall</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY15"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122785451</v>
+        <v>122788391</v>
       </c>
       <c r="B2" t="n">
         <v>97319</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -912,7 +912,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122785684</v>
+        <v>122789060</v>
       </c>
       <c r="B4" t="n">
         <v>98365</v>
@@ -945,20 +945,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Kyrkleden, Kyrkleden, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513524</v>
+        <v>513469</v>
       </c>
       <c r="R4" t="n">
-        <v>6732635</v>
+        <v>6732636</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +999,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +1009,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,6 +1018,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1024,10 +1037,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122789232</v>
+        <v>122785684</v>
       </c>
       <c r="B5" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1036,52 +1049,41 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Kyrkleden, Kyrkleden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513455</v>
+        <v>513524</v>
       </c>
       <c r="R5" t="n">
-        <v>6732564</v>
+        <v>6732635</v>
       </c>
       <c r="S5" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1110,7 +1112,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1122,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,7 +1131,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1148,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122789060</v>
+        <v>122789232</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,39 +1161,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513469</v>
+        <v>513455</v>
       </c>
       <c r="R6" t="n">
-        <v>6732636</v>
+        <v>6732564</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122789158</v>
+        <v>122789796</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,46 +1397,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513468</v>
+        <v>513425</v>
       </c>
       <c r="R8" t="n">
-        <v>6732639</v>
+        <v>6732654</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,12 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,7 +1479,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1511,7 +1497,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122790237</v>
+        <v>122792630</v>
       </c>
       <c r="B9" t="n">
         <v>97319</v>
@@ -1551,10 +1537,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513429</v>
+        <v>513571</v>
       </c>
       <c r="R9" t="n">
-        <v>6732604</v>
+        <v>6732676</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1586,7 +1572,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1582,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1623,10 +1609,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122792630</v>
+        <v>122788763</v>
       </c>
       <c r="B10" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,38 +1621,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513571</v>
+        <v>513482</v>
       </c>
       <c r="R10" t="n">
-        <v>6732676</v>
+        <v>6732623</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,7 +1692,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1708,7 +1702,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,6 +1716,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1735,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122789796</v>
+        <v>122790237</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>97319</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1751,21 +1751,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1775,10 +1775,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513425</v>
+        <v>513429</v>
       </c>
       <c r="R11" t="n">
-        <v>6732654</v>
+        <v>6732604</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1820,7 +1820,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1847,7 +1847,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122788763</v>
+        <v>122789158</v>
       </c>
       <c r="B12" t="n">
         <v>98365</v>
@@ -1882,7 +1882,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J12" t="inlineStr"/>
@@ -1895,10 +1895,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513482</v>
+        <v>513468</v>
       </c>
       <c r="R12" t="n">
-        <v>6732623</v>
+        <v>6732639</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1940,12 +1940,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>Uppskattat antal</t>
+          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,10 +1973,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122798012</v>
+        <v>122791590</v>
       </c>
       <c r="B13" t="n">
-        <v>90917</v>
+        <v>97325</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1989,45 +1989,38 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>221941</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513484</v>
+        <v>513512</v>
       </c>
       <c r="R13" t="n">
-        <v>6732609</v>
+        <v>6732717</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2059,7 +2052,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2069,7 +2062,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2097,10 +2095,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122791590</v>
+        <v>122798012</v>
       </c>
       <c r="B14" t="n">
-        <v>97325</v>
+        <v>90917</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2113,38 +2111,45 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>221941</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513512</v>
+        <v>513484</v>
       </c>
       <c r="R14" t="n">
-        <v>6732717</v>
+        <v>6732609</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2176,7 +2181,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2186,12 +2191,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2338,6 +2338,272 @@
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>123232534</v>
+      </c>
+      <c r="B16" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>513567</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6732735</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>12:49</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>123231827</v>
+      </c>
+      <c r="B17" t="n">
+        <v>5173</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>513425</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6732651</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2604,6 +2604,948 @@
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>123260949</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97319</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran , Dlr</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>513664</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6732742</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>123261310</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97319</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran , Dlr</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>513330</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6732609</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>123260928</v>
+      </c>
+      <c r="B20" t="n">
+        <v>97319</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran , Dlr</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>513636</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6732786</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF20" t="inlineStr"/>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>123261212</v>
+      </c>
+      <c r="B21" t="n">
+        <v>78790</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran , Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>513415</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6732527</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF21" t="inlineStr"/>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>123261453</v>
+      </c>
+      <c r="B22" t="n">
+        <v>97319</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran , Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>513425</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6732551</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:12</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>123260757</v>
+      </c>
+      <c r="B23" t="n">
+        <v>78790</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran , Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>513591</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6732867</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>123263453</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57428</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>102621</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Sparvuggla</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran , Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>513517</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6732664</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>123260571</v>
+      </c>
+      <c r="B25" t="n">
+        <v>97319</v>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>513341</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6732624</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -1735,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122790237</v>
+        <v>122789158</v>
       </c>
       <c r="B11" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,38 +1747,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513429</v>
+        <v>513468</v>
       </c>
       <c r="R11" t="n">
-        <v>6732604</v>
+        <v>6732639</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1810,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1820,7 +1828,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1829,6 +1842,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1847,10 +1861,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122789158</v>
+        <v>122798012</v>
       </c>
       <c r="B12" t="n">
-        <v>98365</v>
+        <v>90917</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1859,46 +1873,49 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr"/>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>513468</v>
+        <v>513484</v>
       </c>
       <c r="R12" t="n">
-        <v>6732639</v>
+        <v>6732609</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1930,7 +1947,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1940,12 +1957,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
+          <t>14:03</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,10 +1985,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122791590</v>
+        <v>123174254</v>
       </c>
       <c r="B13" t="n">
-        <v>97325</v>
+        <v>78766</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1985,42 +1997,41 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>513512</v>
+        <v>513372</v>
       </c>
       <c r="R13" t="n">
-        <v>6732717</v>
+        <v>6732617</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2047,27 +2058,27 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>VU i Rödlistan 2020 Typisk art i 5130 Enbuskmarker Boreal region (BOR) Kontinental region (CON)</t>
+          <t>stora långa tuvor varav några sätt mycket högre än jag nådde, på tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2095,10 +2106,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122798012</v>
+        <v>123232534</v>
       </c>
       <c r="B14" t="n">
-        <v>90917</v>
+        <v>5173</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2111,45 +2122,39 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5447</v>
+        <v>100526</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513484</v>
+        <v>513567</v>
       </c>
       <c r="R14" t="n">
-        <v>6732609</v>
+        <v>6732735</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2176,22 +2181,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:03</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2219,10 +2224,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123174254</v>
+        <v>123231827</v>
       </c>
       <c r="B15" t="n">
-        <v>78766</v>
+        <v>5173</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2231,30 +2236,32 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2262,10 +2269,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513372</v>
+        <v>513425</v>
       </c>
       <c r="R15" t="n">
-        <v>6732617</v>
+        <v>6732651</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2297,7 +2304,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2307,12 +2314,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>stora långa tuvor varav några sätt mycket högre än jag nådde, på tall</t>
+          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2324,6 +2331,31 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2340,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123232534</v>
+        <v>123260949</v>
       </c>
       <c r="B16" t="n">
-        <v>5173</v>
+        <v>97319</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2356,39 +2388,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513567</v>
+        <v>513664</v>
       </c>
       <c r="R16" t="n">
-        <v>6732735</v>
+        <v>6732742</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2415,22 +2446,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2458,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123231827</v>
+        <v>123261310</v>
       </c>
       <c r="B17" t="n">
-        <v>5173</v>
+        <v>97319</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2474,39 +2505,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513425</v>
+        <v>513330</v>
       </c>
       <c r="R17" t="n">
-        <v>6732651</v>
+        <v>6732609</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2538,7 +2568,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2548,12 +2578,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2565,31 +2590,6 @@
       <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2606,7 +2606,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123260949</v>
+        <v>123260928</v>
       </c>
       <c r="B18" t="n">
         <v>97319</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513664</v>
+        <v>513636</v>
       </c>
       <c r="R18" t="n">
-        <v>6732742</v>
+        <v>6732786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2685,7 +2685,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2695,7 +2695,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2723,10 +2723,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123261310</v>
+        <v>123261212</v>
       </c>
       <c r="B19" t="n">
-        <v>97319</v>
+        <v>78790</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,27 +2739,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2767,10 +2766,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513330</v>
+        <v>513415</v>
       </c>
       <c r="R19" t="n">
-        <v>6732609</v>
+        <v>6732527</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2802,7 +2801,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2812,7 +2811,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2840,7 +2839,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123260928</v>
+        <v>123261453</v>
       </c>
       <c r="B20" t="n">
         <v>97319</v>
@@ -2884,10 +2883,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513636</v>
+        <v>513425</v>
       </c>
       <c r="R20" t="n">
-        <v>6732786</v>
+        <v>6732551</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2914,22 +2913,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2957,7 +2956,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123261212</v>
+        <v>123260757</v>
       </c>
       <c r="B21" t="n">
         <v>78790</v>
@@ -3000,10 +2999,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513415</v>
+        <v>513591</v>
       </c>
       <c r="R21" t="n">
-        <v>6732527</v>
+        <v>6732867</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3030,22 +3029,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3073,10 +3072,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123261453</v>
+        <v>123263453</v>
       </c>
       <c r="B22" t="n">
-        <v>97319</v>
+        <v>57428</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3089,27 +3088,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>102621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3117,13 +3120,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513425</v>
+        <v>513517</v>
       </c>
       <c r="R22" t="n">
-        <v>6732551</v>
+        <v>6732664</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3152,7 +3155,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3162,7 +3165,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3171,7 +3179,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3190,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123260757</v>
+        <v>123260571</v>
       </c>
       <c r="B23" t="n">
-        <v>78790</v>
+        <v>97319</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3206,37 +3213,38 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513591</v>
+        <v>513341</v>
       </c>
       <c r="R23" t="n">
-        <v>6732867</v>
+        <v>6732624</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3268,7 +3276,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3278,7 +3286,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3306,10 +3314,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>123263453</v>
+        <v>122791590</v>
       </c>
       <c r="B24" t="n">
-        <v>57428</v>
+        <v>97325</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3322,45 +3330,41 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>102621</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513517</v>
+        <v>513512</v>
       </c>
       <c r="R24" t="n">
-        <v>6732664</v>
+        <v>6732717</v>
       </c>
       <c r="S24" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3384,27 +3388,27 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
         <is>
-          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
+          <t>Typisk art i 9010 Taiga (Alpin region (ALP) Typisk art i 2320 Rissandhedar  Boreal region (BOR),  Kontinental region (CON))</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3413,6 +3417,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3431,7 +3436,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>123260571</v>
+        <v>122790237</v>
       </c>
       <c r="B25" t="n">
         <v>97319</v>
@@ -3471,14 +3476,14 @@
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513341</v>
+        <v>513429</v>
       </c>
       <c r="R25" t="n">
-        <v>6732624</v>
+        <v>6732604</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3505,22 +3510,22 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122789059</v>
+        <v>122785684</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -820,29 +820,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Kyrkleden, Kyrkleden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513471</v>
+        <v>513524</v>
       </c>
       <c r="R3" t="n">
-        <v>6732628</v>
+        <v>6732635</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -874,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,29 +881,28 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122789060</v>
+        <v>122789232</v>
       </c>
       <c r="B4" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,39 +911,38 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -964,13 +950,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513469</v>
+        <v>513455</v>
       </c>
       <c r="R4" t="n">
-        <v>6732636</v>
+        <v>6732564</v>
       </c>
       <c r="S4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -999,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1009,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1037,7 +1023,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122785684</v>
+        <v>122789059</v>
       </c>
       <c r="B5" t="n">
         <v>98365</v>
@@ -1070,17 +1056,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kyrkleden, Kyrkleden, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513524</v>
+        <v>513471</v>
       </c>
       <c r="R5" t="n">
-        <v>6732635</v>
+        <v>6732628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1112,7 +1110,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1122,7 +1120,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,28 +1129,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122789232</v>
+        <v>122789060</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>98365</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,38 +1160,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513455</v>
+        <v>513469</v>
       </c>
       <c r="R6" t="n">
-        <v>6732564</v>
+        <v>6732636</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122792108</v>
+        <v>122792630</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>97319</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513619</v>
+        <v>513571</v>
       </c>
       <c r="R7" t="n">
-        <v>6732790</v>
+        <v>6732676</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122789796</v>
+        <v>122788763</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>98365</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,38 +1397,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513425</v>
+        <v>513482</v>
       </c>
       <c r="R8" t="n">
-        <v>6732654</v>
+        <v>6732623</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,7 +1478,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1479,6 +1492,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1497,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122792630</v>
+        <v>122789158</v>
       </c>
       <c r="B9" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,38 +1523,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513571</v>
+        <v>513468</v>
       </c>
       <c r="R9" t="n">
-        <v>6732676</v>
+        <v>6732639</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1572,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1582,7 +1604,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1591,6 +1618,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1609,10 +1637,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122788763</v>
+        <v>122792108</v>
       </c>
       <c r="B10" t="n">
-        <v>98365</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1621,46 +1649,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513482</v>
+        <v>513619</v>
       </c>
       <c r="R10" t="n">
-        <v>6732623</v>
+        <v>6732790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1692,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1702,12 +1722,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1716,7 +1731,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1735,10 +1749,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122789158</v>
+        <v>122789796</v>
       </c>
       <c r="B11" t="n">
-        <v>98365</v>
+        <v>5173</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,46 +1761,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513468</v>
+        <v>513425</v>
       </c>
       <c r="R11" t="n">
-        <v>6732639</v>
+        <v>6732654</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,12 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,7 +1843,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123232534</v>
+        <v>123231827</v>
       </c>
       <c r="B14" t="n">
         <v>5173</v>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513567</v>
+        <v>513425</v>
       </c>
       <c r="R14" t="n">
-        <v>6732735</v>
+        <v>6732651</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,7 +2196,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,6 +2213,31 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2224,7 +2254,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123231827</v>
+        <v>123232534</v>
       </c>
       <c r="B15" t="n">
         <v>5173</v>
@@ -2269,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513425</v>
+        <v>513567</v>
       </c>
       <c r="R15" t="n">
-        <v>6732651</v>
+        <v>6732735</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2304,7 +2334,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2314,12 +2344,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,31 +2356,6 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2372,7 +2372,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123260949</v>
+        <v>123260571</v>
       </c>
       <c r="B16" t="n">
         <v>97319</v>
@@ -2412,14 +2412,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513664</v>
+        <v>513341</v>
       </c>
       <c r="R16" t="n">
-        <v>6732742</v>
+        <v>6732624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2461,7 +2461,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,7 +2489,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123261310</v>
+        <v>123260949</v>
       </c>
       <c r="B17" t="n">
         <v>97319</v>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513330</v>
+        <v>513664</v>
       </c>
       <c r="R17" t="n">
-        <v>6732609</v>
+        <v>6732742</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2563,22 +2563,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,7 +2606,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123260928</v>
+        <v>123261310</v>
       </c>
       <c r="B18" t="n">
         <v>97319</v>
@@ -2650,10 +2650,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513636</v>
+        <v>513330</v>
       </c>
       <c r="R18" t="n">
-        <v>6732786</v>
+        <v>6732609</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2680,22 +2680,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2839,10 +2839,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123261453</v>
+        <v>123263453</v>
       </c>
       <c r="B20" t="n">
-        <v>97319</v>
+        <v>57428</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2855,27 +2855,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>102621</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2883,13 +2887,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513425</v>
+        <v>513517</v>
       </c>
       <c r="R20" t="n">
-        <v>6732551</v>
+        <v>6732664</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2918,7 +2922,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2928,7 +2932,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,7 +2946,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2956,10 +2964,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123260757</v>
+        <v>123261453</v>
       </c>
       <c r="B21" t="n">
-        <v>78790</v>
+        <v>97319</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2972,26 +2980,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2999,10 +3008,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513591</v>
+        <v>513425</v>
       </c>
       <c r="R21" t="n">
-        <v>6732867</v>
+        <v>6732551</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3029,22 +3038,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3072,10 +3081,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123263453</v>
+        <v>123260757</v>
       </c>
       <c r="B22" t="n">
-        <v>57428</v>
+        <v>78790</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3088,31 +3097,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102621</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3120,13 +3124,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513517</v>
+        <v>513591</v>
       </c>
       <c r="R22" t="n">
-        <v>6732664</v>
+        <v>6732867</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3150,27 +3154,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3179,6 +3178,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3197,7 +3197,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123260571</v>
+        <v>123260928</v>
       </c>
       <c r="B23" t="n">
         <v>97319</v>
@@ -3237,14 +3237,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513341</v>
+        <v>513636</v>
       </c>
       <c r="R23" t="n">
-        <v>6732624</v>
+        <v>6732786</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122788391</v>
+        <v>122785684</v>
       </c>
       <c r="B2" t="n">
-        <v>97319</v>
+        <v>98365</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Kyrkleden, Kyrkleden, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513456</v>
+        <v>513524</v>
       </c>
       <c r="R2" t="n">
-        <v>6732571</v>
+        <v>6732635</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,19 +775,19 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122785684</v>
+        <v>122789060</v>
       </c>
       <c r="B3" t="n">
         <v>98365</v>
@@ -820,20 +820,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kyrkleden, Kyrkleden, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513524</v>
+        <v>513469</v>
       </c>
       <c r="R3" t="n">
-        <v>6732635</v>
+        <v>6732636</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +893,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122789232</v>
+        <v>122788391</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
+        <v>97319</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,52 +924,41 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513455</v>
+        <v>513456</v>
       </c>
       <c r="R4" t="n">
-        <v>6732564</v>
+        <v>6732571</v>
       </c>
       <c r="S4" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -985,7 +987,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -995,7 +997,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1004,19 +1006,18 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1148,10 +1149,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122789060</v>
+        <v>122789232</v>
       </c>
       <c r="B6" t="n">
-        <v>98365</v>
+        <v>78766</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1160,39 +1161,38 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513469</v>
+        <v>513455</v>
       </c>
       <c r="R6" t="n">
-        <v>6732636</v>
+        <v>6732564</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122792630</v>
+        <v>122792108</v>
       </c>
       <c r="B7" t="n">
-        <v>97319</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513571</v>
+        <v>513619</v>
       </c>
       <c r="R7" t="n">
-        <v>6732676</v>
+        <v>6732790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,7 +1385,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122788763</v>
+        <v>122789158</v>
       </c>
       <c r="B8" t="n">
         <v>98365</v>
@@ -1420,7 +1420,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J8" t="inlineStr"/>
@@ -1433,10 +1433,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513482</v>
+        <v>513468</v>
       </c>
       <c r="R8" t="n">
-        <v>6732623</v>
+        <v>6732639</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,12 +1478,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Uppskattat antal</t>
+          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1511,7 +1511,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122789158</v>
+        <v>122788763</v>
       </c>
       <c r="B9" t="n">
         <v>98365</v>
@@ -1546,7 +1546,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1559,10 +1559,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513468</v>
+        <v>513482</v>
       </c>
       <c r="R9" t="n">
-        <v>6732639</v>
+        <v>6732623</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,12 +1604,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1637,10 +1637,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122792108</v>
+        <v>122792630</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>97319</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,21 +1653,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1677,10 +1677,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513619</v>
+        <v>513571</v>
       </c>
       <c r="R10" t="n">
-        <v>6732790</v>
+        <v>6732676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1712,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,7 +1722,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -2106,7 +2106,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123231827</v>
+        <v>123232534</v>
       </c>
       <c r="B14" t="n">
         <v>5173</v>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513425</v>
+        <v>513567</v>
       </c>
       <c r="R14" t="n">
-        <v>6732651</v>
+        <v>6732735</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,12 +2196,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,31 +2208,6 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2254,7 +2224,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123232534</v>
+        <v>123231827</v>
       </c>
       <c r="B15" t="n">
         <v>5173</v>
@@ -2299,10 +2269,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513567</v>
+        <v>513425</v>
       </c>
       <c r="R15" t="n">
-        <v>6732735</v>
+        <v>6732651</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2334,7 +2304,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2344,7 +2314,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2356,6 +2331,31 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2372,7 +2372,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123260571</v>
+        <v>123261310</v>
       </c>
       <c r="B16" t="n">
         <v>97319</v>
@@ -2412,14 +2412,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513341</v>
+        <v>513330</v>
       </c>
       <c r="R16" t="n">
-        <v>6732624</v>
+        <v>6732609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2446,22 +2446,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2606,10 +2606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123261310</v>
+        <v>123263453</v>
       </c>
       <c r="B18" t="n">
-        <v>97319</v>
+        <v>57428</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2622,27 +2622,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>102621</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2650,13 +2654,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513330</v>
+        <v>513517</v>
       </c>
       <c r="R18" t="n">
-        <v>6732609</v>
+        <v>6732664</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2685,7 +2689,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2695,7 +2699,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2704,7 +2713,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2723,10 +2731,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123261212</v>
+        <v>123261453</v>
       </c>
       <c r="B19" t="n">
-        <v>78790</v>
+        <v>97319</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2739,26 +2747,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2766,10 +2775,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513415</v>
+        <v>513425</v>
       </c>
       <c r="R19" t="n">
-        <v>6732527</v>
+        <v>6732551</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2801,7 +2810,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2811,7 +2820,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2839,10 +2848,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123263453</v>
+        <v>123261212</v>
       </c>
       <c r="B20" t="n">
-        <v>57428</v>
+        <v>78790</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2855,31 +2864,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102621</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2887,13 +2891,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513517</v>
+        <v>513415</v>
       </c>
       <c r="R20" t="n">
-        <v>6732664</v>
+        <v>6732527</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2922,7 +2926,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2932,12 +2936,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2946,6 +2945,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2964,10 +2964,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123261453</v>
+        <v>123260757</v>
       </c>
       <c r="B21" t="n">
-        <v>97319</v>
+        <v>78790</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2980,27 +2980,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3008,10 +3007,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513425</v>
+        <v>513591</v>
       </c>
       <c r="R21" t="n">
-        <v>6732551</v>
+        <v>6732867</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3038,22 +3037,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3081,10 +3080,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123260757</v>
+        <v>123260928</v>
       </c>
       <c r="B22" t="n">
-        <v>78790</v>
+        <v>97319</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3097,26 +3096,27 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513591</v>
+        <v>513636</v>
       </c>
       <c r="R22" t="n">
-        <v>6732867</v>
+        <v>6732786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3197,7 +3197,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123260928</v>
+        <v>123260571</v>
       </c>
       <c r="B23" t="n">
         <v>97319</v>
@@ -3237,14 +3237,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513636</v>
+        <v>513341</v>
       </c>
       <c r="R23" t="n">
-        <v>6732786</v>
+        <v>6732624</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3314,10 +3314,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122791590</v>
+        <v>122790237</v>
       </c>
       <c r="B24" t="n">
-        <v>97325</v>
+        <v>97319</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3330,16 +3330,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513512</v>
+        <v>513429</v>
       </c>
       <c r="R24" t="n">
-        <v>6732717</v>
+        <v>6732604</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3403,12 +3403,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Typisk art i 9010 Taiga (Alpin region (ALP) Typisk art i 2320 Rissandhedar  Boreal region (BOR),  Kontinental region (CON))</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3436,10 +3431,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122790237</v>
+        <v>122791590</v>
       </c>
       <c r="B25" t="n">
-        <v>97319</v>
+        <v>97325</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3452,16 +3447,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3480,10 +3475,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513429</v>
+        <v>513512</v>
       </c>
       <c r="R25" t="n">
-        <v>6732604</v>
+        <v>6732717</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3515,7 +3510,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3525,7 +3520,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Typisk art i 9010 Taiga (Alpin region (ALP) Typisk art i 2320 Rissandhedar  Boreal region (BOR),  Kontinental region (CON))</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122785684</v>
+        <v>122788391</v>
       </c>
       <c r="B2" t="n">
-        <v>98365</v>
+        <v>97322</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kyrkleden, Kyrkleden, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513524</v>
+        <v>513456</v>
       </c>
       <c r="R2" t="n">
-        <v>6732635</v>
+        <v>6732571</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -775,22 +775,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122789060</v>
+        <v>122785684</v>
       </c>
       <c r="B3" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,32 +820,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Kyrkleden, Kyrkleden, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513469</v>
+        <v>513524</v>
       </c>
       <c r="R3" t="n">
-        <v>6732636</v>
+        <v>6732635</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,7 +881,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -912,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122788391</v>
+        <v>122789232</v>
       </c>
       <c r="B4" t="n">
-        <v>97319</v>
+        <v>78769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -924,41 +911,52 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>513456</v>
+        <v>513455</v>
       </c>
       <c r="R4" t="n">
-        <v>6732571</v>
+        <v>6732564</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -987,7 +985,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -997,7 +995,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,18 +1004,19 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1027,7 +1026,7 @@
         <v>122789059</v>
       </c>
       <c r="B5" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1149,10 +1148,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122789232</v>
+        <v>122789060</v>
       </c>
       <c r="B6" t="n">
-        <v>78766</v>
+        <v>98368</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,38 +1160,39 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513455</v>
+        <v>513469</v>
       </c>
       <c r="R6" t="n">
-        <v>6732564</v>
+        <v>6732636</v>
       </c>
       <c r="S6" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122792108</v>
+        <v>122792630</v>
       </c>
       <c r="B7" t="n">
-        <v>8441</v>
+        <v>97322</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1289,21 +1289,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>106545</v>
+        <v>221945</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1313,10 +1313,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513619</v>
+        <v>513571</v>
       </c>
       <c r="R7" t="n">
-        <v>6732790</v>
+        <v>6732676</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122789158</v>
+        <v>122789796</v>
       </c>
       <c r="B8" t="n">
-        <v>98365</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,46 +1397,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513468</v>
+        <v>513425</v>
       </c>
       <c r="R8" t="n">
-        <v>6732639</v>
+        <v>6732654</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,12 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,7 +1479,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1511,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122788763</v>
+        <v>122789158</v>
       </c>
       <c r="B9" t="n">
-        <v>98365</v>
+        <v>98368</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1546,7 +1532,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J9" t="inlineStr"/>
@@ -1559,10 +1545,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513482</v>
+        <v>513468</v>
       </c>
       <c r="R9" t="n">
-        <v>6732623</v>
+        <v>6732639</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1594,7 +1580,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1604,12 +1590,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Uppskattat antal</t>
+          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1637,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122792630</v>
+        <v>122792108</v>
       </c>
       <c r="B10" t="n">
-        <v>97319</v>
+        <v>8441</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1653,21 +1639,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1677,10 +1663,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513571</v>
+        <v>513619</v>
       </c>
       <c r="R10" t="n">
-        <v>6732676</v>
+        <v>6732790</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1712,7 +1698,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1722,7 +1708,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1749,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122789796</v>
+        <v>122788763</v>
       </c>
       <c r="B11" t="n">
-        <v>5173</v>
+        <v>98368</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,38 +1747,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513425</v>
+        <v>513482</v>
       </c>
       <c r="R11" t="n">
-        <v>6732654</v>
+        <v>6732623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,7 +1828,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,6 +1842,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>122798012</v>
       </c>
       <c r="B12" t="n">
-        <v>90917</v>
+        <v>90920</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>123174254</v>
       </c>
       <c r="B13" t="n">
-        <v>78766</v>
+        <v>78769</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123232534</v>
+        <v>123231827</v>
       </c>
       <c r="B14" t="n">
         <v>5173</v>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513567</v>
+        <v>513425</v>
       </c>
       <c r="R14" t="n">
-        <v>6732735</v>
+        <v>6732651</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,7 +2196,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,6 +2213,31 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2224,7 +2254,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123231827</v>
+        <v>123232534</v>
       </c>
       <c r="B15" t="n">
         <v>5173</v>
@@ -2269,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513425</v>
+        <v>513567</v>
       </c>
       <c r="R15" t="n">
-        <v>6732651</v>
+        <v>6732735</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2304,7 +2334,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2314,12 +2344,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,31 +2356,6 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123261310</v>
+        <v>123261212</v>
       </c>
       <c r="B16" t="n">
-        <v>97319</v>
+        <v>78793</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2388,27 +2388,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2416,10 +2415,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513330</v>
+        <v>513415</v>
       </c>
       <c r="R16" t="n">
-        <v>6732609</v>
+        <v>6732527</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2451,7 +2450,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2461,7 +2460,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,10 +2488,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123260949</v>
+        <v>123260757</v>
       </c>
       <c r="B17" t="n">
-        <v>97319</v>
+        <v>78793</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2505,27 +2504,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2533,10 +2531,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513664</v>
+        <v>513591</v>
       </c>
       <c r="R17" t="n">
-        <v>6732742</v>
+        <v>6732867</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2568,7 +2566,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2578,7 +2576,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,10 +2604,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123263453</v>
+        <v>123261310</v>
       </c>
       <c r="B18" t="n">
-        <v>57428</v>
+        <v>97322</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2622,31 +2620,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102621</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2654,13 +2648,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513517</v>
+        <v>513330</v>
       </c>
       <c r="R18" t="n">
-        <v>6732664</v>
+        <v>6732609</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2689,7 +2683,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2699,12 +2693,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2713,6 +2702,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2731,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123261453</v>
+        <v>123260571</v>
       </c>
       <c r="B19" t="n">
-        <v>97319</v>
+        <v>97322</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2771,14 +2761,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513425</v>
+        <v>513341</v>
       </c>
       <c r="R19" t="n">
-        <v>6732551</v>
+        <v>6732624</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2805,22 +2795,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2848,10 +2838,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123261212</v>
+        <v>123261453</v>
       </c>
       <c r="B20" t="n">
-        <v>78790</v>
+        <v>97322</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2864,26 +2854,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2891,10 +2882,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513415</v>
+        <v>513425</v>
       </c>
       <c r="R20" t="n">
-        <v>6732527</v>
+        <v>6732551</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2926,7 +2917,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2936,7 +2927,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2964,10 +2955,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123260757</v>
+        <v>123260928</v>
       </c>
       <c r="B21" t="n">
-        <v>78790</v>
+        <v>97322</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2980,26 +2971,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3007,10 +2999,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513591</v>
+        <v>513636</v>
       </c>
       <c r="R21" t="n">
-        <v>6732867</v>
+        <v>6732786</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3042,7 +3034,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3052,7 +3044,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3080,10 +3072,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123260928</v>
+        <v>123263453</v>
       </c>
       <c r="B22" t="n">
-        <v>97319</v>
+        <v>57431</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3096,27 +3088,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>102621</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3124,13 +3120,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513636</v>
+        <v>513517</v>
       </c>
       <c r="R22" t="n">
-        <v>6732786</v>
+        <v>6732664</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3154,22 +3150,27 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3178,7 +3179,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3197,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123260571</v>
+        <v>123260949</v>
       </c>
       <c r="B23" t="n">
-        <v>97319</v>
+        <v>97322</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3237,14 +3237,14 @@
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513341</v>
+        <v>513664</v>
       </c>
       <c r="R23" t="n">
-        <v>6732624</v>
+        <v>6732742</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3314,10 +3314,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122790237</v>
+        <v>122791590</v>
       </c>
       <c r="B24" t="n">
-        <v>97319</v>
+        <v>97328</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3330,16 +3330,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513429</v>
+        <v>513512</v>
       </c>
       <c r="R24" t="n">
-        <v>6732604</v>
+        <v>6732717</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3403,7 +3403,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Typisk art i 9010 Taiga (Alpin region (ALP) Typisk art i 2320 Rissandhedar  Boreal region (BOR),  Kontinental region (CON))</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3431,10 +3436,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122791590</v>
+        <v>122790237</v>
       </c>
       <c r="B25" t="n">
-        <v>97325</v>
+        <v>97322</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3447,16 +3452,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3475,10 +3480,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513512</v>
+        <v>513429</v>
       </c>
       <c r="R25" t="n">
-        <v>6732717</v>
+        <v>6732604</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3510,7 +3515,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3520,12 +3525,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Typisk art i 9010 Taiga (Alpin region (ALP) Typisk art i 2320 Rissandhedar  Boreal region (BOR),  Kontinental region (CON))</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>122788391</v>
       </c>
       <c r="B2" t="n">
-        <v>97322</v>
+        <v>97324</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122785684</v>
+        <v>122789060</v>
       </c>
       <c r="B3" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -820,20 +820,32 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr"/>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kyrkleden, Kyrkleden, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513524</v>
+        <v>513469</v>
       </c>
       <c r="R3" t="n">
-        <v>6732635</v>
+        <v>6732636</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,6 +893,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,7 +915,7 @@
         <v>122789232</v>
       </c>
       <c r="B4" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1023,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122789059</v>
+        <v>122785684</v>
       </c>
       <c r="B5" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1056,29 +1069,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Kyrkleden, Kyrkleden, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513471</v>
+        <v>513524</v>
       </c>
       <c r="R5" t="n">
-        <v>6732628</v>
+        <v>6732635</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1110,7 +1111,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1120,7 +1121,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1129,29 +1130,28 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122789060</v>
+        <v>122789059</v>
       </c>
       <c r="B6" t="n">
-        <v>98368</v>
+        <v>98370</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1183,12 +1183,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -1200,13 +1200,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513469</v>
+        <v>513471</v>
       </c>
       <c r="R6" t="n">
-        <v>6732636</v>
+        <v>6732628</v>
       </c>
       <c r="S6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1261,22 +1261,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122792630</v>
+        <v>122788763</v>
       </c>
       <c r="B7" t="n">
-        <v>97322</v>
+        <v>98370</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,38 +1285,46 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513571</v>
+        <v>513482</v>
       </c>
       <c r="R7" t="n">
-        <v>6732676</v>
+        <v>6732623</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1348,7 +1356,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1358,7 +1366,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1367,6 +1380,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1385,10 +1399,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122789796</v>
+        <v>122792108</v>
       </c>
       <c r="B8" t="n">
-        <v>5173</v>
+        <v>8441</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1401,21 +1415,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>106545</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1425,10 +1439,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513425</v>
+        <v>513619</v>
       </c>
       <c r="R8" t="n">
-        <v>6732654</v>
+        <v>6732790</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1460,7 +1474,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1470,7 +1484,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1497,10 +1511,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122789158</v>
+        <v>122789796</v>
       </c>
       <c r="B9" t="n">
-        <v>98368</v>
+        <v>5173</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1509,46 +1523,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513468</v>
+        <v>513425</v>
       </c>
       <c r="R9" t="n">
-        <v>6732639</v>
+        <v>6732654</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1580,7 +1586,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1590,12 +1596,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1604,7 +1605,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122792108</v>
+        <v>122789158</v>
       </c>
       <c r="B10" t="n">
-        <v>8441</v>
+        <v>98370</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,38 +1635,46 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513619</v>
+        <v>513468</v>
       </c>
       <c r="R10" t="n">
-        <v>6732790</v>
+        <v>6732639</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1698,7 +1706,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1708,7 +1716,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1717,6 +1730,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1735,10 +1749,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122788763</v>
+        <v>122792630</v>
       </c>
       <c r="B11" t="n">
-        <v>98368</v>
+        <v>97324</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1747,46 +1761,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513482</v>
+        <v>513571</v>
       </c>
       <c r="R11" t="n">
-        <v>6732623</v>
+        <v>6732676</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1818,7 +1824,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1828,12 +1834,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1842,7 +1843,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>122798012</v>
       </c>
       <c r="B12" t="n">
-        <v>90920</v>
+        <v>90922</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>123174254</v>
       </c>
       <c r="B13" t="n">
-        <v>78769</v>
+        <v>78771</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123261212</v>
+        <v>123260757</v>
       </c>
       <c r="B16" t="n">
-        <v>78793</v>
+        <v>78795</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2415,10 +2415,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513415</v>
+        <v>513591</v>
       </c>
       <c r="R16" t="n">
-        <v>6732527</v>
+        <v>6732867</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2445,22 +2445,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2488,10 +2488,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123260757</v>
+        <v>123261212</v>
       </c>
       <c r="B17" t="n">
-        <v>78793</v>
+        <v>78795</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513591</v>
+        <v>513415</v>
       </c>
       <c r="R17" t="n">
-        <v>6732867</v>
+        <v>6732527</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2561,22 +2561,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2604,10 +2604,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123261310</v>
+        <v>123261453</v>
       </c>
       <c r="B18" t="n">
-        <v>97322</v>
+        <v>97324</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2648,10 +2648,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513330</v>
+        <v>513425</v>
       </c>
       <c r="R18" t="n">
-        <v>6732609</v>
+        <v>6732551</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2693,7 +2693,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,10 +2721,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123260571</v>
+        <v>123260949</v>
       </c>
       <c r="B19" t="n">
-        <v>97322</v>
+        <v>97324</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2761,14 +2761,14 @@
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513341</v>
+        <v>513664</v>
       </c>
       <c r="R19" t="n">
-        <v>6732624</v>
+        <v>6732742</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2800,7 +2800,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2838,10 +2838,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123261453</v>
+        <v>123260928</v>
       </c>
       <c r="B20" t="n">
-        <v>97322</v>
+        <v>97324</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2882,10 +2882,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513425</v>
+        <v>513636</v>
       </c>
       <c r="R20" t="n">
-        <v>6732551</v>
+        <v>6732786</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2912,22 +2912,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2955,10 +2955,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123260928</v>
+        <v>123261310</v>
       </c>
       <c r="B21" t="n">
-        <v>97322</v>
+        <v>97324</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2999,10 +2999,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513636</v>
+        <v>513330</v>
       </c>
       <c r="R21" t="n">
-        <v>6732786</v>
+        <v>6732609</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3029,22 +3029,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3072,10 +3072,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123263453</v>
+        <v>123260571</v>
       </c>
       <c r="B22" t="n">
-        <v>57431</v>
+        <v>97324</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3088,45 +3088,41 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>102621</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513517</v>
+        <v>513341</v>
       </c>
       <c r="R22" t="n">
-        <v>6732664</v>
+        <v>6732624</v>
       </c>
       <c r="S22" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3150,27 +3146,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3179,6 +3170,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3197,10 +3189,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123260949</v>
+        <v>123263453</v>
       </c>
       <c r="B23" t="n">
-        <v>97322</v>
+        <v>57431</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3213,27 +3205,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3241,13 +3237,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513664</v>
+        <v>513517</v>
       </c>
       <c r="R23" t="n">
-        <v>6732742</v>
+        <v>6732664</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3271,22 +3267,27 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3295,7 +3296,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>122791590</v>
       </c>
       <c r="B24" t="n">
-        <v>97328</v>
+        <v>97330</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3439,7 +3439,7 @@
         <v>122790237</v>
       </c>
       <c r="B25" t="n">
-        <v>97322</v>
+        <v>97324</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122788391</v>
+        <v>122789060</v>
       </c>
       <c r="B2" t="n">
-        <v>97324</v>
+        <v>98370</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,53 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513456</v>
+        <v>513469</v>
       </c>
       <c r="R2" t="n">
-        <v>6732571</v>
+        <v>6732636</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,28 +781,29 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122789060</v>
+        <v>122788391</v>
       </c>
       <c r="B3" t="n">
-        <v>98370</v>
+        <v>97324</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,53 +812,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513469</v>
+        <v>513456</v>
       </c>
       <c r="R3" t="n">
-        <v>6732636</v>
+        <v>6732571</v>
       </c>
       <c r="S3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -874,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -884,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -893,19 +894,18 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -1273,10 +1273,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>122788763</v>
+        <v>122792108</v>
       </c>
       <c r="B7" t="n">
-        <v>98370</v>
+        <v>8441</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1285,46 +1285,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>513482</v>
+        <v>513619</v>
       </c>
       <c r="R7" t="n">
-        <v>6732623</v>
+        <v>6732790</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1356,7 +1348,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1366,12 +1358,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
+          <t>17:27</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,7 +1367,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1399,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122792108</v>
+        <v>122788763</v>
       </c>
       <c r="B8" t="n">
-        <v>8441</v>
+        <v>98370</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1411,38 +1397,46 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>106545</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513619</v>
+        <v>513482</v>
       </c>
       <c r="R8" t="n">
-        <v>6732790</v>
+        <v>6732623</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1474,7 +1468,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1484,7 +1478,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>17:27</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1493,6 +1492,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122789060</v>
+        <v>122788391</v>
       </c>
       <c r="B2" t="n">
-        <v>98370</v>
+        <v>97330</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,53 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>513469</v>
+        <v>513456</v>
       </c>
       <c r="R2" t="n">
-        <v>6732636</v>
+        <v>6732571</v>
       </c>
       <c r="S2" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -781,29 +769,28 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122788391</v>
+        <v>122789060</v>
       </c>
       <c r="B3" t="n">
-        <v>97324</v>
+        <v>98376</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -812,41 +799,53 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>513456</v>
+        <v>513469</v>
       </c>
       <c r="R3" t="n">
-        <v>6732571</v>
+        <v>6732636</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -875,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -885,7 +884,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,18 +893,19 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -915,7 +915,7 @@
         <v>122789232</v>
       </c>
       <c r="B4" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122785684</v>
+        <v>122789059</v>
       </c>
       <c r="B5" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1069,17 +1069,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Kyrkleden, Kyrkleden, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>513524</v>
+        <v>513471</v>
       </c>
       <c r="R5" t="n">
-        <v>6732635</v>
+        <v>6732628</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,7 +1123,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1121,7 +1133,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:21</t>
+          <t>14:23</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1130,28 +1142,29 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Lisa Olson</t>
+          <t>Göran Ehn</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122789059</v>
+        <v>122785684</v>
       </c>
       <c r="B6" t="n">
-        <v>98370</v>
+        <v>98376</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1181,29 +1194,17 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Kyrkleden, Kyrkleden, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>513471</v>
+        <v>513524</v>
       </c>
       <c r="R6" t="n">
-        <v>6732628</v>
+        <v>6732635</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1235,7 +1236,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1245,7 +1246,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:23</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1254,19 +1255,18 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Göran Ehn</t>
+          <t>Lisa Olson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -1385,10 +1385,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>122788763</v>
+        <v>122789796</v>
       </c>
       <c r="B8" t="n">
-        <v>98370</v>
+        <v>5173</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1397,46 +1397,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>513482</v>
+        <v>513425</v>
       </c>
       <c r="R8" t="n">
-        <v>6732623</v>
+        <v>6732654</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1468,7 +1460,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1478,12 +1470,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:58</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Uppskattat antal</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1492,7 +1479,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1511,10 +1497,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>122789796</v>
+        <v>122789158</v>
       </c>
       <c r="B9" t="n">
-        <v>5173</v>
+        <v>98376</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1523,38 +1509,46 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>513425</v>
+        <v>513468</v>
       </c>
       <c r="R9" t="n">
-        <v>6732654</v>
+        <v>6732639</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1586,7 +1580,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1596,7 +1590,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1605,6 +1604,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1623,10 +1623,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>122789158</v>
+        <v>122792630</v>
       </c>
       <c r="B10" t="n">
-        <v>98370</v>
+        <v>97330</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1635,46 +1635,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>513468</v>
+        <v>513571</v>
       </c>
       <c r="R10" t="n">
-        <v>6732639</v>
+        <v>6732676</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1706,7 +1698,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1716,12 +1708,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:28</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>uppskattat antal, kontinuitetsskog blockig terräng nära mosse</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1730,7 +1717,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1749,10 +1735,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>122792630</v>
+        <v>122788763</v>
       </c>
       <c r="B11" t="n">
-        <v>97324</v>
+        <v>98376</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1761,38 +1747,46 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>513571</v>
+        <v>513482</v>
       </c>
       <c r="R11" t="n">
-        <v>6732676</v>
+        <v>6732623</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1824,7 +1818,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1834,7 +1828,12 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Uppskattat antal</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1843,6 +1842,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>122798012</v>
       </c>
       <c r="B12" t="n">
-        <v>90922</v>
+        <v>90928</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>123174254</v>
       </c>
       <c r="B13" t="n">
-        <v>78771</v>
+        <v>78772</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2106,7 +2106,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123231827</v>
+        <v>123232534</v>
       </c>
       <c r="B14" t="n">
         <v>5173</v>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513425</v>
+        <v>513567</v>
       </c>
       <c r="R14" t="n">
-        <v>6732651</v>
+        <v>6732735</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,12 +2196,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,31 +2208,6 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2254,7 +2224,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123232534</v>
+        <v>123231827</v>
       </c>
       <c r="B15" t="n">
         <v>5173</v>
@@ -2299,10 +2269,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513567</v>
+        <v>513425</v>
       </c>
       <c r="R15" t="n">
-        <v>6732735</v>
+        <v>6732651</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2334,7 +2304,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2344,7 +2314,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2356,6 +2331,31 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123260757</v>
+        <v>123260949</v>
       </c>
       <c r="B16" t="n">
-        <v>78795</v>
+        <v>97330</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2388,26 +2388,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2415,10 +2416,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513591</v>
+        <v>513664</v>
       </c>
       <c r="R16" t="n">
-        <v>6732867</v>
+        <v>6732742</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2450,7 +2451,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2460,7 +2461,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2488,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123261212</v>
+        <v>123260571</v>
       </c>
       <c r="B17" t="n">
-        <v>78795</v>
+        <v>97330</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2504,37 +2505,38 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513415</v>
+        <v>513341</v>
       </c>
       <c r="R17" t="n">
-        <v>6732527</v>
+        <v>6732624</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2561,22 +2563,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2604,10 +2606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123261453</v>
+        <v>123261212</v>
       </c>
       <c r="B18" t="n">
-        <v>97324</v>
+        <v>78796</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2620,27 +2622,26 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2648,10 +2649,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513425</v>
+        <v>513415</v>
       </c>
       <c r="R18" t="n">
-        <v>6732551</v>
+        <v>6732527</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2683,7 +2684,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2693,7 +2694,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2721,10 +2722,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123260949</v>
+        <v>123263453</v>
       </c>
       <c r="B19" t="n">
-        <v>97324</v>
+        <v>57431</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2737,27 +2738,31 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>102621</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2765,13 +2770,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513664</v>
+        <v>513517</v>
       </c>
       <c r="R19" t="n">
-        <v>6732742</v>
+        <v>6732664</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2795,22 +2800,27 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2819,7 +2829,6 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -2838,10 +2847,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123260928</v>
+        <v>123261453</v>
       </c>
       <c r="B20" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2882,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513636</v>
+        <v>513425</v>
       </c>
       <c r="R20" t="n">
-        <v>6732786</v>
+        <v>6732551</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2912,22 +2921,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2955,10 +2964,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123261310</v>
+        <v>123260757</v>
       </c>
       <c r="B21" t="n">
-        <v>97324</v>
+        <v>78796</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2971,27 +2980,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2999,10 +3007,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513330</v>
+        <v>513591</v>
       </c>
       <c r="R21" t="n">
-        <v>6732609</v>
+        <v>6732867</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3029,22 +3037,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3072,10 +3080,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123260571</v>
+        <v>123260928</v>
       </c>
       <c r="B22" t="n">
-        <v>97324</v>
+        <v>97330</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3112,14 +3120,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513341</v>
+        <v>513636</v>
       </c>
       <c r="R22" t="n">
-        <v>6732624</v>
+        <v>6732786</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3151,7 +3159,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3161,7 +3169,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3189,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123263453</v>
+        <v>123261310</v>
       </c>
       <c r="B23" t="n">
-        <v>57431</v>
+        <v>97330</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3205,31 +3213,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3237,13 +3241,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513517</v>
+        <v>513330</v>
       </c>
       <c r="R23" t="n">
-        <v>6732664</v>
+        <v>6732609</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3272,7 +3276,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3282,12 +3286,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3296,6 +3295,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3314,7 +3314,7 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122791590</v>
+        <v>122790237</v>
       </c>
       <c r="B24" t="n">
         <v>97330</v>
@@ -3330,16 +3330,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513512</v>
+        <v>513429</v>
       </c>
       <c r="R24" t="n">
-        <v>6732717</v>
+        <v>6732604</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3403,12 +3403,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Typisk art i 9010 Taiga (Alpin region (ALP) Typisk art i 2320 Rissandhedar  Boreal region (BOR),  Kontinental region (CON))</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3436,10 +3431,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122790237</v>
+        <v>122791590</v>
       </c>
       <c r="B25" t="n">
-        <v>97324</v>
+        <v>97336</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3452,16 +3447,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3480,10 +3475,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513429</v>
+        <v>513512</v>
       </c>
       <c r="R25" t="n">
-        <v>6732604</v>
+        <v>6732717</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3515,7 +3510,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3525,7 +3520,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Typisk art i 9010 Taiga (Alpin region (ALP) Typisk art i 2320 Rissandhedar  Boreal region (BOR),  Kontinental region (CON))</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -1864,7 +1864,7 @@
         <v>122798012</v>
       </c>
       <c r="B12" t="n">
-        <v>90931</v>
+        <v>90948</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>123174254</v>
       </c>
       <c r="B13" t="n">
-        <v>78775</v>
+        <v>78781</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123232534</v>
+        <v>123231827</v>
       </c>
       <c r="B14" t="n">
-        <v>5173</v>
+        <v>5174</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513567</v>
+        <v>513425</v>
       </c>
       <c r="R14" t="n">
-        <v>6732735</v>
+        <v>6732651</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,7 +2196,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,6 +2213,31 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2224,10 +2254,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123231827</v>
+        <v>123232534</v>
       </c>
       <c r="B15" t="n">
-        <v>5173</v>
+        <v>5174</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2269,10 +2299,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513425</v>
+        <v>513567</v>
       </c>
       <c r="R15" t="n">
-        <v>6732651</v>
+        <v>6732735</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2304,7 +2334,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2314,12 +2344,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2331,31 +2356,6 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123261453</v>
+        <v>123260949</v>
       </c>
       <c r="B16" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513425</v>
+        <v>513664</v>
       </c>
       <c r="R16" t="n">
-        <v>6732551</v>
+        <v>6732742</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2446,22 +2446,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123260571</v>
+        <v>123261453</v>
       </c>
       <c r="B17" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2529,14 +2529,14 @@
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513341</v>
+        <v>513425</v>
       </c>
       <c r="R17" t="n">
-        <v>6732624</v>
+        <v>6732551</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2563,22 +2563,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,10 +2606,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123260757</v>
+        <v>123260571</v>
       </c>
       <c r="B18" t="n">
-        <v>78799</v>
+        <v>97350</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2622,37 +2622,38 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513591</v>
+        <v>513341</v>
       </c>
       <c r="R18" t="n">
-        <v>6732867</v>
+        <v>6732624</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2684,7 +2685,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2694,7 +2695,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2722,10 +2723,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123260949</v>
+        <v>123261212</v>
       </c>
       <c r="B19" t="n">
-        <v>97333</v>
+        <v>78805</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2738,27 +2739,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2766,10 +2766,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513664</v>
+        <v>513415</v>
       </c>
       <c r="R19" t="n">
-        <v>6732742</v>
+        <v>6732527</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2796,22 +2796,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2839,10 +2839,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123260928</v>
+        <v>123260757</v>
       </c>
       <c r="B20" t="n">
-        <v>97333</v>
+        <v>78805</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2855,27 +2855,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2883,10 +2882,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513636</v>
+        <v>513591</v>
       </c>
       <c r="R20" t="n">
-        <v>6732786</v>
+        <v>6732867</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2918,7 +2917,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2928,7 +2927,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2956,10 +2955,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123263453</v>
+        <v>123260928</v>
       </c>
       <c r="B21" t="n">
-        <v>57431</v>
+        <v>97350</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2972,31 +2971,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102621</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3004,13 +2999,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513517</v>
+        <v>513636</v>
       </c>
       <c r="R21" t="n">
-        <v>6732664</v>
+        <v>6732786</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3034,27 +3029,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3063,6 +3053,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3084,7 +3075,7 @@
         <v>123261310</v>
       </c>
       <c r="B22" t="n">
-        <v>97333</v>
+        <v>97350</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3198,10 +3189,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123261212</v>
+        <v>123263453</v>
       </c>
       <c r="B23" t="n">
-        <v>78799</v>
+        <v>57437</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3214,26 +3205,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6434</v>
+        <v>102621</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3241,13 +3237,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513415</v>
+        <v>513517</v>
       </c>
       <c r="R23" t="n">
-        <v>6732527</v>
+        <v>6732664</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3276,7 +3272,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3286,7 +3282,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3295,7 +3296,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3314,10 +3314,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122791590</v>
+        <v>122790237</v>
       </c>
       <c r="B24" t="n">
-        <v>97339</v>
+        <v>97350</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3330,16 +3330,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513512</v>
+        <v>513429</v>
       </c>
       <c r="R24" t="n">
-        <v>6732717</v>
+        <v>6732604</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3403,12 +3403,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Typisk art i 9010 Taiga (Alpin region (ALP) Typisk art i 2320 Rissandhedar  Boreal region (BOR),  Kontinental region (CON))</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3436,10 +3431,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122790237</v>
+        <v>122791590</v>
       </c>
       <c r="B25" t="n">
-        <v>97333</v>
+        <v>97356</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3452,16 +3447,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3480,10 +3475,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513429</v>
+        <v>513512</v>
       </c>
       <c r="R25" t="n">
-        <v>6732604</v>
+        <v>6732717</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3515,7 +3510,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3525,7 +3520,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Typisk art i 9010 Taiga (Alpin region (ALP) Typisk art i 2320 Rissandhedar  Boreal region (BOR),  Kontinental region (CON))</t>
         </is>
       </c>
       <c r="AD25" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -1864,7 +1864,7 @@
         <v>122798012</v>
       </c>
       <c r="B12" t="n">
-        <v>90948</v>
+        <v>90953</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>123174254</v>
       </c>
       <c r="B13" t="n">
-        <v>78781</v>
+        <v>78786</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2106,10 +2106,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>123231827</v>
+        <v>123232534</v>
       </c>
       <c r="B14" t="n">
-        <v>5174</v>
+        <v>5176</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2151,10 +2151,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>513425</v>
+        <v>513567</v>
       </c>
       <c r="R14" t="n">
-        <v>6732651</v>
+        <v>6732735</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:11</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2196,12 +2196,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,31 +2208,6 @@
       <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
@@ -2254,10 +2224,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>123232534</v>
+        <v>123231827</v>
       </c>
       <c r="B15" t="n">
-        <v>5174</v>
+        <v>5176</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2299,10 +2269,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>513567</v>
+        <v>513425</v>
       </c>
       <c r="R15" t="n">
-        <v>6732735</v>
+        <v>6732651</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2334,7 +2304,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2344,7 +2314,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>12:49</t>
+          <t>13:11</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>250227 var den döda gamla granen intakt men 250228 på eftermiddagen var stammen avsågad nära roten men stod på ett mirakulöst sätt ändå kvar på en liten del av stubben.</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2356,6 +2331,31 @@
       <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Picea abies # Död gammal gran med drygt hälften av barken kvar.</t>
+        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123260949</v>
+        <v>123261453</v>
       </c>
       <c r="B16" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2416,10 +2416,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513664</v>
+        <v>513425</v>
       </c>
       <c r="R16" t="n">
-        <v>6732742</v>
+        <v>6732551</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2446,22 +2446,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123261453</v>
+        <v>123261310</v>
       </c>
       <c r="B17" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2533,10 +2533,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513425</v>
+        <v>513330</v>
       </c>
       <c r="R17" t="n">
-        <v>6732551</v>
+        <v>6732609</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2609,7 +2609,7 @@
         <v>123260571</v>
       </c>
       <c r="B18" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2726,7 +2726,7 @@
         <v>123261212</v>
       </c>
       <c r="B19" t="n">
-        <v>78805</v>
+        <v>78810</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123260757</v>
+        <v>123260928</v>
       </c>
       <c r="B20" t="n">
-        <v>78805</v>
+        <v>97367</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2855,26 +2855,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2882,10 +2883,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513591</v>
+        <v>513636</v>
       </c>
       <c r="R20" t="n">
-        <v>6732867</v>
+        <v>6732786</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2917,7 +2918,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2927,7 +2928,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2955,10 +2956,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123260928</v>
+        <v>123263453</v>
       </c>
       <c r="B21" t="n">
-        <v>97350</v>
+        <v>57440</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2971,27 +2972,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>102621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2999,13 +3004,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513636</v>
+        <v>513517</v>
       </c>
       <c r="R21" t="n">
-        <v>6732786</v>
+        <v>6732664</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3029,22 +3034,27 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3053,7 +3063,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3072,10 +3081,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123261310</v>
+        <v>123260757</v>
       </c>
       <c r="B22" t="n">
-        <v>97350</v>
+        <v>78810</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3088,27 +3097,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -3116,10 +3124,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513330</v>
+        <v>513591</v>
       </c>
       <c r="R22" t="n">
-        <v>6732609</v>
+        <v>6732867</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3146,22 +3154,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3189,10 +3197,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123263453</v>
+        <v>123260949</v>
       </c>
       <c r="B23" t="n">
-        <v>57437</v>
+        <v>97367</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3205,31 +3213,27 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>102621</v>
+        <v>221945</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3237,13 +3241,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513517</v>
+        <v>513664</v>
       </c>
       <c r="R23" t="n">
-        <v>6732664</v>
+        <v>6732742</v>
       </c>
       <c r="S23" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3267,27 +3271,22 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3296,6 +3295,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>122790237</v>
       </c>
       <c r="B24" t="n">
-        <v>97350</v>
+        <v>97367</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>122791590</v>
       </c>
       <c r="B25" t="n">
-        <v>97356</v>
+        <v>97373</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -1864,7 +1864,7 @@
         <v>122798012</v>
       </c>
       <c r="B12" t="n">
-        <v>90953</v>
+        <v>90955</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1988,7 +1988,7 @@
         <v>123174254</v>
       </c>
       <c r="B13" t="n">
-        <v>78786</v>
+        <v>78788</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123261453</v>
+        <v>123260757</v>
       </c>
       <c r="B16" t="n">
-        <v>97367</v>
+        <v>78812</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2388,27 +2388,26 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2416,10 +2415,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513425</v>
+        <v>513591</v>
       </c>
       <c r="R16" t="n">
-        <v>6732551</v>
+        <v>6732867</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2446,22 +2445,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,10 +2488,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123261310</v>
+        <v>123261453</v>
       </c>
       <c r="B17" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2533,10 +2532,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513330</v>
+        <v>513425</v>
       </c>
       <c r="R17" t="n">
-        <v>6732609</v>
+        <v>6732551</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2568,7 +2567,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2578,7 +2577,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2606,10 +2605,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123260571</v>
+        <v>123260928</v>
       </c>
       <c r="B18" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2646,14 +2645,14 @@
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513341</v>
+        <v>513636</v>
       </c>
       <c r="R18" t="n">
-        <v>6732624</v>
+        <v>6732786</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2685,7 +2684,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2695,7 +2694,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2726,7 +2725,7 @@
         <v>123261212</v>
       </c>
       <c r="B19" t="n">
-        <v>78810</v>
+        <v>78812</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2839,10 +2838,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123260928</v>
+        <v>123263453</v>
       </c>
       <c r="B20" t="n">
-        <v>97367</v>
+        <v>57441</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2855,27 +2854,31 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>221945</v>
+        <v>102621</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2883,13 +2886,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513636</v>
+        <v>513517</v>
       </c>
       <c r="R20" t="n">
-        <v>6732786</v>
+        <v>6732664</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2913,22 +2916,27 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2937,7 +2945,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2956,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123263453</v>
+        <v>123261310</v>
       </c>
       <c r="B21" t="n">
-        <v>57440</v>
+        <v>97369</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2972,31 +2979,27 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>102621</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3004,13 +3007,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513517</v>
+        <v>513330</v>
       </c>
       <c r="R21" t="n">
-        <v>6732664</v>
+        <v>6732609</v>
       </c>
       <c r="S21" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3039,7 +3042,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3049,12 +3052,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3063,6 +3061,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3081,10 +3080,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123260757</v>
+        <v>123260571</v>
       </c>
       <c r="B22" t="n">
-        <v>78810</v>
+        <v>97369</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3097,37 +3096,38 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513591</v>
+        <v>513341</v>
       </c>
       <c r="R22" t="n">
-        <v>6732867</v>
+        <v>6732624</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3200,7 +3200,7 @@
         <v>123260949</v>
       </c>
       <c r="B23" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>122790237</v>
       </c>
       <c r="B24" t="n">
-        <v>97367</v>
+        <v>97369</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>122791590</v>
       </c>
       <c r="B25" t="n">
-        <v>97373</v>
+        <v>97375</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AY61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3551,6 +3551,4258 @@
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>123174129</v>
+      </c>
+      <c r="B26" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>513357</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6732614</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fjäder från en äldre tjäderhanne</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>123174256</v>
+      </c>
+      <c r="B27" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>513476</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6732711</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>123174131</v>
+      </c>
+      <c r="B28" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>513575</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6732778</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På mossig stubbe, troligen blåbärsspillning</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>123950247</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>513435</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6732618</v>
+      </c>
+      <c r="S29" t="n">
+        <v>5</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>123951429</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>513440</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6732637</v>
+      </c>
+      <c r="S30" t="n">
+        <v>1</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>123950117</v>
+      </c>
+      <c r="B31" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>513452</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6732659</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>13:44</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>123951286</v>
+      </c>
+      <c r="B32" t="n">
+        <v>97375</v>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>513430</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6732614</v>
+      </c>
+      <c r="S32" t="n">
+        <v>1</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Kammossa linnea, olika vitmossor, björnmossaetc</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>123949969</v>
+      </c>
+      <c r="B33" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>513443</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6732646</v>
+      </c>
+      <c r="S33" t="n">
+        <v>1</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Mellanskog avverkar</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>123174258</v>
+      </c>
+      <c r="B34" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>513428</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6732689</v>
+      </c>
+      <c r="S34" t="n">
+        <v>25</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>06:51</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>123954347</v>
+      </c>
+      <c r="B35" t="n">
+        <v>97369</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>513440</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6732637</v>
+      </c>
+      <c r="S35" t="n">
+        <v>1</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>123953880</v>
+      </c>
+      <c r="B36" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>513440</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6732637</v>
+      </c>
+      <c r="S36" t="n">
+        <v>1</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>123950905</v>
+      </c>
+      <c r="B37" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>513442</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6732642</v>
+      </c>
+      <c r="S37" t="n">
+        <v>1</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>123950580</v>
+      </c>
+      <c r="B38" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>513442</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6732640</v>
+      </c>
+      <c r="S38" t="n">
+        <v>5</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>14:08</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>123951771</v>
+      </c>
+      <c r="B39" t="n">
+        <v>97375</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>513461</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6732598</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>15:04</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>123951412</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>513434</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6732611</v>
+      </c>
+      <c r="S40" t="n">
+        <v>1</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>14:44</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>123949803</v>
+      </c>
+      <c r="B41" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>513439</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6732649</v>
+      </c>
+      <c r="S41" t="n">
+        <v>5</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>13:32</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>123953103</v>
+      </c>
+      <c r="B42" t="n">
+        <v>5176</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>513440</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6732637</v>
+      </c>
+      <c r="S42" t="n">
+        <v>1</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>123951367</v>
+      </c>
+      <c r="B43" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>513441</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6732633</v>
+      </c>
+      <c r="S43" t="n">
+        <v>1</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Åke Sköld</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>123954554</v>
+      </c>
+      <c r="B44" t="n">
+        <v>97369</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Lögkarsmyren, Dlr</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>513484</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6732609</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>16:59</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>123949914</v>
+      </c>
+      <c r="B45" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>513440</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6732648</v>
+      </c>
+      <c r="S45" t="n">
+        <v>5</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>123951744</v>
+      </c>
+      <c r="B46" t="n">
+        <v>97375</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>513434</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6732611</v>
+      </c>
+      <c r="S46" t="n">
+        <v>1</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Dålig uppkoppling, bilder går inte atr få med</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>123174186</v>
+      </c>
+      <c r="B47" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>513473</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6732751</v>
+      </c>
+      <c r="S47" t="n">
+        <v>25</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Trol. sovträd med färsk och äldre spillning under</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>123174162</v>
+      </c>
+      <c r="B48" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>513433</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6732675</v>
+      </c>
+      <c r="S48" t="n">
+        <v>25</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Under tall, troligt sovträd</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>123174259</v>
+      </c>
+      <c r="B49" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>513476</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6732720</v>
+      </c>
+      <c r="S49" t="n">
+        <v>25</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-03-05</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>122789501</v>
+      </c>
+      <c r="B50" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Falun, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>513426</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6732668</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>123174257</v>
+      </c>
+      <c r="B51" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>513437</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6732675</v>
+      </c>
+      <c r="S51" t="n">
+        <v>25</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:47</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>123956562</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97369</v>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>513514</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6732646</v>
+      </c>
+      <c r="S52" t="n">
+        <v>25</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>18:54</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>123956767</v>
+      </c>
+      <c r="B53" t="n">
+        <v>97369</v>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>513447</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6732560</v>
+      </c>
+      <c r="S53" t="n">
+        <v>1</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>123174130</v>
+      </c>
+      <c r="B54" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran , Dlr</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>513586</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6732786</v>
+      </c>
+      <c r="S54" t="n">
+        <v>25</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-02-28</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>123950844</v>
+      </c>
+      <c r="B55" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>513461</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6732632</v>
+      </c>
+      <c r="S55" t="n">
+        <v>100</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>123952048</v>
+      </c>
+      <c r="B56" t="n">
+        <v>98504</v>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>513425</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6732651</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>123953543</v>
+      </c>
+      <c r="B57" t="n">
+        <v>78788</v>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>513415</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6732596</v>
+      </c>
+      <c r="S57" t="n">
+        <v>25</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>16:21</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>122789602</v>
+      </c>
+      <c r="B58" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Falun, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>513429</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6732681</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Några hundratal spillning under s.k. sovtall</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>122791693</v>
+      </c>
+      <c r="B59" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Falun, Falun, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>513491</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6732749</v>
+      </c>
+      <c r="S59" t="n">
+        <v>25</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-02-27</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>123174141</v>
+      </c>
+      <c r="B60" t="n">
+        <v>56700</v>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>513432</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6732690</v>
+      </c>
+      <c r="S60" t="n">
+        <v>25</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-03-02</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Sovträd med spillning under.</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>123951665</v>
+      </c>
+      <c r="B61" t="n">
+        <v>97369</v>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>513434</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6732611</v>
+      </c>
+      <c r="S61" t="n">
+        <v>1</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -2963,7 +2963,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123261310</v>
+        <v>123260571</v>
       </c>
       <c r="B21" t="n">
         <v>97369</v>
@@ -3003,14 +3003,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513330</v>
+        <v>513341</v>
       </c>
       <c r="R21" t="n">
-        <v>6732609</v>
+        <v>6732624</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3037,22 +3037,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3080,7 +3080,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123260571</v>
+        <v>123261310</v>
       </c>
       <c r="B22" t="n">
         <v>97369</v>
@@ -3120,14 +3120,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513341</v>
+        <v>513330</v>
       </c>
       <c r="R22" t="n">
-        <v>6732624</v>
+        <v>6732609</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3154,22 +3154,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -4160,7 +4160,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123950117</v>
+        <v>123949969</v>
       </c>
       <c r="B31" t="n">
         <v>98504</v>
@@ -4193,29 +4193,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513452</v>
+        <v>513443</v>
       </c>
       <c r="R31" t="n">
-        <v>6732659</v>
+        <v>6732646</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4244,7 +4239,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4254,7 +4249,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4263,18 +4263,19 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
+      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4398,7 +4399,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123949969</v>
+        <v>123950117</v>
       </c>
       <c r="B33" t="n">
         <v>98504</v>
@@ -4431,24 +4432,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513443</v>
+        <v>513452</v>
       </c>
       <c r="R33" t="n">
-        <v>6732646</v>
+        <v>6732659</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4477,7 +4483,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4487,12 +4493,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Mellanskog avverkar</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4501,19 +4502,18 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4869,7 +4869,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123950905</v>
+        <v>123950580</v>
       </c>
       <c r="B37" t="n">
         <v>98504</v>
@@ -4912,10 +4912,10 @@
         <v>513442</v>
       </c>
       <c r="R37" t="n">
-        <v>6732642</v>
+        <v>6732640</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4944,7 +4944,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4954,12 +4954,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4986,7 +4981,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123950580</v>
+        <v>123950905</v>
       </c>
       <c r="B38" t="n">
         <v>98504</v>
@@ -5029,10 +5024,10 @@
         <v>513442</v>
       </c>
       <c r="R38" t="n">
-        <v>6732640</v>
+        <v>6732642</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5061,7 +5056,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5071,7 +5066,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
         </is>
       </c>
       <c r="AD38" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -2372,10 +2372,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123260757</v>
+        <v>123260571</v>
       </c>
       <c r="B16" t="n">
-        <v>78812</v>
+        <v>96957</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2388,37 +2388,38 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513591</v>
+        <v>513341</v>
       </c>
       <c r="R16" t="n">
-        <v>6732867</v>
+        <v>6732624</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2450,7 +2451,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2460,7 +2461,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2488,10 +2489,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123261453</v>
+        <v>123260757</v>
       </c>
       <c r="B17" t="n">
-        <v>97369</v>
+        <v>78812</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2504,27 +2505,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513425</v>
+        <v>513591</v>
       </c>
       <c r="R17" t="n">
-        <v>6732551</v>
+        <v>6732867</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2562,22 +2562,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2605,10 +2605,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123260928</v>
+        <v>123263453</v>
       </c>
       <c r="B18" t="n">
-        <v>97369</v>
+        <v>57441</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2621,27 +2621,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>102621</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2649,13 +2653,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513636</v>
+        <v>513517</v>
       </c>
       <c r="R18" t="n">
-        <v>6732786</v>
+        <v>6732664</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2679,22 +2683,27 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2703,7 +2712,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2722,10 +2730,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123261212</v>
+        <v>123260928</v>
       </c>
       <c r="B19" t="n">
-        <v>78812</v>
+        <v>96957</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2738,26 +2746,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
@@ -2765,10 +2774,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513415</v>
+        <v>513636</v>
       </c>
       <c r="R19" t="n">
-        <v>6732527</v>
+        <v>6732786</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2795,22 +2804,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2838,10 +2847,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123263453</v>
+        <v>123261212</v>
       </c>
       <c r="B20" t="n">
-        <v>57441</v>
+        <v>78812</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2854,31 +2863,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>102621</v>
+        <v>6434</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2886,13 +2890,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513517</v>
+        <v>513415</v>
       </c>
       <c r="R20" t="n">
-        <v>6732664</v>
+        <v>6732527</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2921,7 +2925,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2931,12 +2935,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2945,6 +2944,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2963,10 +2963,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123260571</v>
+        <v>123261310</v>
       </c>
       <c r="B21" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -3003,14 +3003,14 @@
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513341</v>
+        <v>513330</v>
       </c>
       <c r="R21" t="n">
-        <v>6732624</v>
+        <v>6732609</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3037,22 +3037,22 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3080,10 +3080,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123261310</v>
+        <v>123261453</v>
       </c>
       <c r="B22" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -3124,10 +3124,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513330</v>
+        <v>513425</v>
       </c>
       <c r="R22" t="n">
-        <v>6732609</v>
+        <v>6732551</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3159,7 +3159,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3200,7 +3200,7 @@
         <v>123260949</v>
       </c>
       <c r="B23" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>122790237</v>
       </c>
       <c r="B24" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3434,7 +3434,7 @@
         <v>122791590</v>
       </c>
       <c r="B25" t="n">
-        <v>97375</v>
+        <v>96963</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3553,10 +3553,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123174129</v>
+        <v>123951367</v>
       </c>
       <c r="B26" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3565,53 +3565,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513357</v>
+        <v>513441</v>
       </c>
       <c r="R26" t="n">
-        <v>6732614</v>
+        <v>6732633</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3635,27 +3623,22 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Fjäder från en äldre tjäderhanne</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3670,22 +3653,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123174256</v>
+        <v>123953103</v>
       </c>
       <c r="B27" t="n">
-        <v>56700</v>
+        <v>5176</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3698,45 +3681,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513476</v>
+        <v>513440</v>
       </c>
       <c r="R27" t="n">
-        <v>6732711</v>
+        <v>6732637</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3760,22 +3735,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3790,22 +3765,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123174131</v>
+        <v>123949914</v>
       </c>
       <c r="B28" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3814,49 +3789,41 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513575</v>
+        <v>513440</v>
       </c>
       <c r="R28" t="n">
-        <v>6732778</v>
+        <v>6732648</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3880,27 +3847,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>På mossig stubbe, troligen blåbärsspillning</t>
+          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3927,10 +3894,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123950247</v>
+        <v>123954347</v>
       </c>
       <c r="B29" t="n">
-        <v>98504</v>
+        <v>96957</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3939,45 +3906,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513435</v>
+        <v>513440</v>
       </c>
       <c r="R29" t="n">
-        <v>6732618</v>
+        <v>6732637</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -4006,7 +3969,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4016,12 +3979,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4036,22 +3994,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123951429</v>
+        <v>123951286</v>
       </c>
       <c r="B30" t="n">
-        <v>98504</v>
+        <v>96963</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4060,25 +4018,25 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -4088,10 +4046,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513440</v>
+        <v>513430</v>
       </c>
       <c r="R30" t="n">
-        <v>6732637</v>
+        <v>6732614</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4123,7 +4081,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4133,7 +4091,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Kammossa linnea, olika vitmossor, björnmossaetc</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4148,22 +4111,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123949969</v>
+        <v>123950844</v>
       </c>
       <c r="B31" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4194,23 +4157,19 @@
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513443</v>
+        <v>513461</v>
       </c>
       <c r="R31" t="n">
-        <v>6732646</v>
+        <v>6732632</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4239,7 +4198,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4249,12 +4208,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Mellanskog avverkar</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4263,7 +4217,6 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
@@ -4282,10 +4235,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123951286</v>
+        <v>123953543</v>
       </c>
       <c r="B32" t="n">
-        <v>97375</v>
+        <v>78788</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4294,25 +4247,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4322,13 +4275,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513430</v>
+        <v>513415</v>
       </c>
       <c r="R32" t="n">
-        <v>6732614</v>
+        <v>6732596</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4357,7 +4310,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4367,12 +4320,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Kammossa linnea, olika vitmossor, björnmossaetc</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4399,10 +4347,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123950117</v>
+        <v>123949969</v>
       </c>
       <c r="B33" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4432,29 +4380,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513452</v>
+        <v>513443</v>
       </c>
       <c r="R33" t="n">
-        <v>6732659</v>
+        <v>6732646</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4483,7 +4426,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4493,7 +4436,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4502,25 +4450,26 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123174258</v>
+        <v>123174131</v>
       </c>
       <c r="B34" t="n">
         <v>56700</v>
@@ -4558,7 +4507,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4568,10 +4517,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513428</v>
+        <v>513575</v>
       </c>
       <c r="R34" t="n">
-        <v>6732689</v>
+        <v>6732778</v>
       </c>
       <c r="S34" t="n">
         <v>25</v>
@@ -4598,22 +4547,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>På mossig stubbe, troligen blåbärsspillning</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4640,10 +4594,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123954347</v>
+        <v>123953720</v>
       </c>
       <c r="B35" t="n">
-        <v>97369</v>
+        <v>56700</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4656,21 +4610,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4715,7 +4669,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4725,7 +4679,12 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4752,10 +4711,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123953880</v>
+        <v>123951599</v>
       </c>
       <c r="B36" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4764,43 +4723,38 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513440</v>
+        <v>513434</v>
       </c>
       <c r="R36" t="n">
-        <v>6732637</v>
+        <v>6732611</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4832,7 +4786,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4842,7 +4796,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Snön har legat länge i de skuggiga svackorna</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4857,22 +4816,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123950580</v>
+        <v>123174141</v>
       </c>
       <c r="B37" t="n">
-        <v>98504</v>
+        <v>56700</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4881,41 +4840,49 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513442</v>
+        <v>513432</v>
       </c>
       <c r="R37" t="n">
-        <v>6732640</v>
+        <v>6732690</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4939,22 +4906,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Sovträd med spillning under.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4984,7 +4956,7 @@
         <v>123950905</v>
       </c>
       <c r="B38" t="n">
-        <v>98504</v>
+        <v>98079</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5098,10 +5070,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123951771</v>
+        <v>123174258</v>
       </c>
       <c r="B39" t="n">
-        <v>97375</v>
+        <v>56700</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5114,37 +5086,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513461</v>
+        <v>513428</v>
       </c>
       <c r="R39" t="n">
-        <v>6732598</v>
+        <v>6732689</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5168,22 +5148,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5210,10 +5190,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123951412</v>
+        <v>123174129</v>
       </c>
       <c r="B40" t="n">
-        <v>98504</v>
+        <v>56700</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5222,41 +5202,53 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513434</v>
+        <v>513357</v>
       </c>
       <c r="R40" t="n">
-        <v>6732611</v>
+        <v>6732614</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5280,22 +5272,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Fjäder från en äldre tjäderhanne</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5322,10 +5319,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123949803</v>
+        <v>123956562</v>
       </c>
       <c r="B41" t="n">
-        <v>98504</v>
+        <v>96957</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5334,41 +5331,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513439</v>
+        <v>513514</v>
       </c>
       <c r="R41" t="n">
-        <v>6732649</v>
+        <v>6732646</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5397,7 +5394,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5407,7 +5404,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5434,10 +5431,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123953103</v>
+        <v>123950117</v>
       </c>
       <c r="B42" t="n">
-        <v>5176</v>
+        <v>98079</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5446,41 +5443,50 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513440</v>
+        <v>513452</v>
       </c>
       <c r="R42" t="n">
-        <v>6732637</v>
+        <v>6732659</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5509,7 +5515,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5519,7 +5525,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5546,10 +5552,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123951367</v>
+        <v>123951771</v>
       </c>
       <c r="B43" t="n">
-        <v>98504</v>
+        <v>96963</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5558,41 +5564,41 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513441</v>
+        <v>513461</v>
       </c>
       <c r="R43" t="n">
-        <v>6732633</v>
+        <v>6732598</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5621,7 +5627,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5631,7 +5637,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5646,22 +5652,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123954554</v>
+        <v>122791693</v>
       </c>
       <c r="B44" t="n">
-        <v>97369</v>
+        <v>56700</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5674,37 +5680,45 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513484</v>
+        <v>513491</v>
       </c>
       <c r="R44" t="n">
-        <v>6732609</v>
+        <v>6732749</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5728,22 +5742,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5770,10 +5789,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123949914</v>
+        <v>123951744</v>
       </c>
       <c r="B45" t="n">
-        <v>98504</v>
+        <v>96963</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5782,25 +5801,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5810,13 +5829,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513440</v>
+        <v>513434</v>
       </c>
       <c r="R45" t="n">
-        <v>6732648</v>
+        <v>6732611</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5845,7 +5864,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5855,12 +5874,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
+          <t>Dålig uppkoppling, bilder går inte atr få med</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5887,10 +5906,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123951744</v>
+        <v>123955316</v>
       </c>
       <c r="B46" t="n">
-        <v>97375</v>
+        <v>98079</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5899,38 +5918,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513434</v>
+        <v>513440</v>
       </c>
       <c r="R46" t="n">
-        <v>6732611</v>
+        <v>6732637</v>
       </c>
       <c r="S46" t="n">
         <v>1</v>
@@ -5962,7 +5981,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5972,12 +5991,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Dålig uppkoppling, bilder går inte atr få med</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5992,22 +6006,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123174186</v>
+        <v>123949803</v>
       </c>
       <c r="B47" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6016,49 +6030,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513473</v>
+        <v>513439</v>
       </c>
       <c r="R47" t="n">
-        <v>6732751</v>
+        <v>6732649</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6082,27 +6088,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>07:39</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Trol. sovträd med färsk och äldre spillning under</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6129,7 +6130,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123174162</v>
+        <v>123174259</v>
       </c>
       <c r="B48" t="n">
         <v>56700</v>
@@ -6177,10 +6178,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513433</v>
+        <v>513476</v>
       </c>
       <c r="R48" t="n">
-        <v>6732675</v>
+        <v>6732720</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6212,7 +6213,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6222,12 +6223,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Under tall, troligt sovträd</t>
+          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6254,10 +6255,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123174259</v>
+        <v>123956767</v>
       </c>
       <c r="B49" t="n">
-        <v>56700</v>
+        <v>96957</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6270,45 +6271,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513476</v>
+        <v>513447</v>
       </c>
       <c r="R49" t="n">
-        <v>6732720</v>
+        <v>6732560</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6332,27 +6325,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>07:31</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6379,10 +6367,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>122789501</v>
+        <v>123950580</v>
       </c>
       <c r="B50" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6391,53 +6379,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513426</v>
+        <v>513442</v>
       </c>
       <c r="R50" t="n">
-        <v>6732668</v>
+        <v>6732640</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6461,27 +6437,22 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6508,10 +6479,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123174257</v>
+        <v>123950247</v>
       </c>
       <c r="B51" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6520,49 +6491,45 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513437</v>
+        <v>513435</v>
       </c>
       <c r="R51" t="n">
-        <v>6732675</v>
+        <v>6732618</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6586,22 +6553,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6628,10 +6600,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123956562</v>
+        <v>122789501</v>
       </c>
       <c r="B52" t="n">
-        <v>97369</v>
+        <v>56700</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6644,37 +6616,49 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513514</v>
+        <v>513426</v>
       </c>
       <c r="R52" t="n">
-        <v>6732646</v>
+        <v>6732668</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6698,22 +6682,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6740,10 +6729,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123956767</v>
+        <v>123174162</v>
       </c>
       <c r="B53" t="n">
-        <v>97369</v>
+        <v>56700</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6756,37 +6745,45 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513447</v>
+        <v>513433</v>
       </c>
       <c r="R53" t="n">
-        <v>6732560</v>
+        <v>6732675</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6810,22 +6807,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Under tall, troligt sovträd</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6852,7 +6854,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123174130</v>
+        <v>123174256</v>
       </c>
       <c r="B54" t="n">
         <v>56700</v>
@@ -6890,20 +6892,20 @@
       <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513586</v>
+        <v>513476</v>
       </c>
       <c r="R54" t="n">
-        <v>6732786</v>
+        <v>6732711</v>
       </c>
       <c r="S54" t="n">
         <v>25</v>
@@ -6930,27 +6932,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6977,10 +6974,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123950844</v>
+        <v>123174130</v>
       </c>
       <c r="B55" t="n">
-        <v>98504</v>
+        <v>56700</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6989,41 +6986,49 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513461</v>
+        <v>513586</v>
       </c>
       <c r="R55" t="n">
-        <v>6732632</v>
+        <v>6732786</v>
       </c>
       <c r="S55" t="n">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7047,22 +7052,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7089,10 +7099,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123952048</v>
+        <v>123954554</v>
       </c>
       <c r="B56" t="n">
-        <v>98504</v>
+        <v>96957</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7101,38 +7111,38 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513425</v>
+        <v>513484</v>
       </c>
       <c r="R56" t="n">
-        <v>6732651</v>
+        <v>6732609</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7164,7 +7174,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -7174,12 +7184,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7206,10 +7211,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123953543</v>
+        <v>123174186</v>
       </c>
       <c r="B57" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7218,38 +7223,46 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513415</v>
+        <v>513473</v>
       </c>
       <c r="R57" t="n">
-        <v>6732596</v>
+        <v>6732751</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7276,22 +7289,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Trol. sovträd med färsk och äldre spillning under</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7318,7 +7336,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>122789602</v>
+        <v>123174257</v>
       </c>
       <c r="B58" t="n">
         <v>56700</v>
@@ -7362,17 +7380,17 @@
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513429</v>
+        <v>513437</v>
       </c>
       <c r="R58" t="n">
-        <v>6732681</v>
+        <v>6732675</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7396,27 +7414,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Några hundratal spillning under s.k. sovtall</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7443,7 +7456,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122791693</v>
+        <v>122789602</v>
       </c>
       <c r="B59" t="n">
         <v>56700</v>
@@ -7481,7 +7494,7 @@
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7491,13 +7504,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513491</v>
+        <v>513429</v>
       </c>
       <c r="R59" t="n">
-        <v>6732749</v>
+        <v>6732681</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7526,7 +7539,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7536,12 +7549,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Blåbärsspillning</t>
+          <t>Några hundratal spillning under s.k. sovtall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7568,10 +7581,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123174141</v>
+        <v>123952048</v>
       </c>
       <c r="B60" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7580,49 +7593,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513432</v>
+        <v>513425</v>
       </c>
       <c r="R60" t="n">
-        <v>6732690</v>
+        <v>6732651</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7646,27 +7651,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Sovträd med spillning under.</t>
+          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7696,7 +7701,7 @@
         <v>123951665</v>
       </c>
       <c r="B61" t="n">
-        <v>97369</v>
+        <v>96957</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -2847,10 +2847,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123261212</v>
+        <v>123261310</v>
       </c>
       <c r="B20" t="n">
-        <v>78812</v>
+        <v>96957</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2863,26 +2863,27 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6434</v>
+        <v>221945</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
@@ -2890,10 +2891,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513415</v>
+        <v>513330</v>
       </c>
       <c r="R20" t="n">
-        <v>6732527</v>
+        <v>6732609</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2925,7 +2926,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2935,7 +2936,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2963,10 +2964,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123261310</v>
+        <v>123261212</v>
       </c>
       <c r="B21" t="n">
-        <v>96957</v>
+        <v>78812</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2979,27 +2980,26 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3007,10 +3007,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513330</v>
+        <v>513415</v>
       </c>
       <c r="R21" t="n">
-        <v>6732609</v>
+        <v>6732527</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3052,7 +3052,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -4123,10 +4123,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123950844</v>
+        <v>123953543</v>
       </c>
       <c r="B31" t="n">
-        <v>98079</v>
+        <v>78788</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4135,38 +4135,38 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513461</v>
+        <v>513415</v>
       </c>
       <c r="R31" t="n">
-        <v>6732632</v>
+        <v>6732596</v>
       </c>
       <c r="S31" t="n">
         <v>25</v>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4208,7 +4208,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4235,10 +4235,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123953543</v>
+        <v>123949969</v>
       </c>
       <c r="B32" t="n">
-        <v>78788</v>
+        <v>98079</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4247,41 +4247,45 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513415</v>
+        <v>513443</v>
       </c>
       <c r="R32" t="n">
-        <v>6732596</v>
+        <v>6732646</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4310,7 +4314,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4320,7 +4324,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4329,6 +4338,7 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
+      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
@@ -4347,7 +4357,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123949969</v>
+        <v>123950844</v>
       </c>
       <c r="B33" t="n">
         <v>98079</v>
@@ -4381,23 +4391,19 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513443</v>
+        <v>513461</v>
       </c>
       <c r="R33" t="n">
-        <v>6732646</v>
+        <v>6732632</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4426,7 +4432,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4436,12 +4442,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Mellanskog avverkar</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4450,7 +4451,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -7099,10 +7099,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123954554</v>
+        <v>123174186</v>
       </c>
       <c r="B56" t="n">
-        <v>96957</v>
+        <v>56700</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7115,37 +7115,45 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513484</v>
+        <v>513473</v>
       </c>
       <c r="R56" t="n">
-        <v>6732609</v>
+        <v>6732751</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7169,22 +7177,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Trol. sovträd med färsk och äldre spillning under</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7211,7 +7224,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123174186</v>
+        <v>123174257</v>
       </c>
       <c r="B57" t="n">
         <v>56700</v>
@@ -7259,10 +7272,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513473</v>
+        <v>513437</v>
       </c>
       <c r="R57" t="n">
-        <v>6732751</v>
+        <v>6732675</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7289,27 +7302,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>07:39</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Trol. sovträd med färsk och äldre spillning under</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7336,10 +7344,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123174257</v>
+        <v>123954554</v>
       </c>
       <c r="B58" t="n">
-        <v>56700</v>
+        <v>96957</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7352,45 +7360,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513437</v>
+        <v>513484</v>
       </c>
       <c r="R58" t="n">
-        <v>6732675</v>
+        <v>6732609</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7414,22 +7414,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD58" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -2372,7 +2372,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>123260571</v>
+        <v>123261310</v>
       </c>
       <c r="B16" t="n">
         <v>96957</v>
@@ -2412,14 +2412,14 @@
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>513341</v>
+        <v>513330</v>
       </c>
       <c r="R16" t="n">
-        <v>6732624</v>
+        <v>6732609</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2446,22 +2446,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2489,7 +2489,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>123260757</v>
+        <v>123261212</v>
       </c>
       <c r="B17" t="n">
         <v>78812</v>
@@ -2532,10 +2532,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>513591</v>
+        <v>513415</v>
       </c>
       <c r="R17" t="n">
-        <v>6732867</v>
+        <v>6732527</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2562,22 +2562,22 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2605,10 +2605,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>123263453</v>
+        <v>123260928</v>
       </c>
       <c r="B18" t="n">
-        <v>57441</v>
+        <v>96957</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2621,31 +2621,27 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>102621</v>
+        <v>221945</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2653,13 +2649,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>513517</v>
+        <v>513636</v>
       </c>
       <c r="R18" t="n">
-        <v>6732664</v>
+        <v>6732786</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2683,27 +2679,22 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>07:28</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>07:28</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2712,6 +2703,7 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2730,7 +2722,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>123260928</v>
+        <v>123261453</v>
       </c>
       <c r="B19" t="n">
         <v>96957</v>
@@ -2774,10 +2766,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>513636</v>
+        <v>513425</v>
       </c>
       <c r="R19" t="n">
-        <v>6732786</v>
+        <v>6732551</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2804,22 +2796,22 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:12</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2847,7 +2839,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>123261310</v>
+        <v>123260949</v>
       </c>
       <c r="B20" t="n">
         <v>96957</v>
@@ -2891,10 +2883,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>513330</v>
+        <v>513664</v>
       </c>
       <c r="R20" t="n">
-        <v>6732609</v>
+        <v>6732742</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2921,22 +2913,22 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2964,10 +2956,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>123261212</v>
+        <v>123263453</v>
       </c>
       <c r="B21" t="n">
-        <v>78812</v>
+        <v>57441</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2980,26 +2972,31 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>6434</v>
+        <v>102621</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -3007,13 +3004,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>513415</v>
+        <v>513517</v>
       </c>
       <c r="R21" t="n">
-        <v>6732527</v>
+        <v>6732664</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -3042,7 +3039,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>07:28</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -3052,7 +3049,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>07:28</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>När jag stod omgiven av granar, bredvid myren och den fina källan hörde jag något som lät som en sparvuggla. Eftersom jag hörde den i mars 2024 ca 200meter ifrån platsen jag befann mig på denna dag är det troligt att sparvugglan flyttade hit, om den överlevde kalavverkningen i juli augusti i sitt förra hem eftersom detta är det närmaste området med gammal skog.</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3061,7 +3063,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -3080,7 +3081,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>123261453</v>
+        <v>123260571</v>
       </c>
       <c r="B22" t="n">
         <v>96957</v>
@@ -3120,14 +3121,14 @@
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>513425</v>
+        <v>513341</v>
       </c>
       <c r="R22" t="n">
-        <v>6732551</v>
+        <v>6732624</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3154,22 +3155,22 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:12</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3197,10 +3198,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>123260949</v>
+        <v>123260757</v>
       </c>
       <c r="B23" t="n">
-        <v>96957</v>
+        <v>78812</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3213,27 +3214,26 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>221945</v>
+        <v>6434</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -3241,10 +3241,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>513664</v>
+        <v>513591</v>
       </c>
       <c r="R23" t="n">
-        <v>6732742</v>
+        <v>6732867</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3276,7 +3276,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3553,7 +3553,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123951367</v>
+        <v>123950580</v>
       </c>
       <c r="B26" t="n">
         <v>98079</v>
@@ -3593,13 +3593,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513441</v>
+        <v>513442</v>
       </c>
       <c r="R26" t="n">
-        <v>6732633</v>
+        <v>6732640</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3653,22 +3653,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123953103</v>
+        <v>123174258</v>
       </c>
       <c r="B27" t="n">
-        <v>5176</v>
+        <v>56700</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3681,37 +3681,45 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513440</v>
+        <v>513428</v>
       </c>
       <c r="R27" t="n">
-        <v>6732637</v>
+        <v>6732689</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3735,22 +3743,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3765,22 +3773,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123949914</v>
+        <v>123174141</v>
       </c>
       <c r="B28" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3789,41 +3797,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513440</v>
+        <v>513432</v>
       </c>
       <c r="R28" t="n">
-        <v>6732648</v>
+        <v>6732690</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3847,27 +3863,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
+          <t>Sovträd med spillning under.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3894,10 +3910,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123954347</v>
+        <v>123174186</v>
       </c>
       <c r="B29" t="n">
-        <v>96957</v>
+        <v>56700</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3910,37 +3926,45 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513440</v>
+        <v>513473</v>
       </c>
       <c r="R29" t="n">
-        <v>6732637</v>
+        <v>6732751</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3964,22 +3988,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Trol. sovträd med färsk och äldre spillning under</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3994,22 +4023,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123951286</v>
+        <v>123955316</v>
       </c>
       <c r="B30" t="n">
-        <v>96963</v>
+        <v>98079</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4018,38 +4047,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513430</v>
+        <v>513440</v>
       </c>
       <c r="R30" t="n">
-        <v>6732614</v>
+        <v>6732637</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
@@ -4081,7 +4110,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4091,12 +4120,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Kammossa linnea, olika vitmossor, björnmossaetc</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4111,22 +4135,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123953543</v>
+        <v>123956767</v>
       </c>
       <c r="B31" t="n">
-        <v>78788</v>
+        <v>96957</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4135,41 +4159,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>221945</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513415</v>
+        <v>513447</v>
       </c>
       <c r="R31" t="n">
-        <v>6732596</v>
+        <v>6732560</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4198,7 +4222,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4208,7 +4232,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4235,7 +4259,7 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123949969</v>
+        <v>123950117</v>
       </c>
       <c r="B32" t="n">
         <v>98079</v>
@@ -4268,24 +4292,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513443</v>
+        <v>513452</v>
       </c>
       <c r="R32" t="n">
-        <v>6732646</v>
+        <v>6732659</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4314,7 +4343,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4324,12 +4353,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Mellanskog avverkar</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4338,29 +4362,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123950844</v>
+        <v>123174259</v>
       </c>
       <c r="B33" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4369,38 +4392,46 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513461</v>
+        <v>513476</v>
       </c>
       <c r="R33" t="n">
-        <v>6732632</v>
+        <v>6732720</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4427,22 +4458,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4594,10 +4630,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123953720</v>
+        <v>123950844</v>
       </c>
       <c r="B35" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4606,25 +4642,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4634,13 +4670,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513440</v>
+        <v>513461</v>
       </c>
       <c r="R35" t="n">
-        <v>6732637</v>
+        <v>6732632</v>
       </c>
       <c r="S35" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4669,7 +4705,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4679,12 +4715,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4699,22 +4730,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123951599</v>
+        <v>123174129</v>
       </c>
       <c r="B36" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4723,41 +4754,53 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513434</v>
+        <v>513357</v>
       </c>
       <c r="R36" t="n">
-        <v>6732611</v>
+        <v>6732614</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4781,27 +4824,27 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Snön har legat länge i de skuggiga svackorna</t>
+          <t>Fjäder från en äldre tjäderhanne</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4828,7 +4871,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123174141</v>
+        <v>123174162</v>
       </c>
       <c r="B37" t="n">
         <v>56700</v>
@@ -4876,10 +4919,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513432</v>
+        <v>513433</v>
       </c>
       <c r="R37" t="n">
-        <v>6732690</v>
+        <v>6732675</v>
       </c>
       <c r="S37" t="n">
         <v>25</v>
@@ -4906,27 +4949,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Sovträd med spillning under.</t>
+          <t>Under tall, troligt sovträd</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4953,10 +4996,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123950905</v>
+        <v>123954221</v>
       </c>
       <c r="B38" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4965,38 +5008,38 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513442</v>
+        <v>513440</v>
       </c>
       <c r="R38" t="n">
-        <v>6732642</v>
+        <v>6732637</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
@@ -5028,7 +5071,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5038,12 +5081,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5058,22 +5096,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123174258</v>
+        <v>123953103</v>
       </c>
       <c r="B39" t="n">
-        <v>56700</v>
+        <v>5176</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5086,45 +5124,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513428</v>
+        <v>513440</v>
       </c>
       <c r="R39" t="n">
-        <v>6732689</v>
+        <v>6732637</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5148,22 +5178,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5178,22 +5208,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123174129</v>
+        <v>123953543</v>
       </c>
       <c r="B40" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5202,50 +5232,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513357</v>
+        <v>513415</v>
       </c>
       <c r="R40" t="n">
-        <v>6732614</v>
+        <v>6732596</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5272,27 +5290,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Fjäder från en äldre tjäderhanne</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5319,10 +5332,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123956562</v>
+        <v>123951312</v>
       </c>
       <c r="B41" t="n">
-        <v>96957</v>
+        <v>96963</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5335,16 +5348,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5355,17 +5368,17 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513514</v>
+        <v>513430</v>
       </c>
       <c r="R41" t="n">
-        <v>6732646</v>
+        <v>6732614</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5394,7 +5407,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5404,7 +5417,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Några plantor</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5431,7 +5449,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123950117</v>
+        <v>123949914</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5464,29 +5482,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513452</v>
+        <v>513440</v>
       </c>
       <c r="R42" t="n">
-        <v>6732659</v>
+        <v>6732648</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5515,7 +5524,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5525,7 +5534,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5540,22 +5554,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123951771</v>
+        <v>123949969</v>
       </c>
       <c r="B43" t="n">
-        <v>96963</v>
+        <v>98079</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5564,41 +5578,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513461</v>
+        <v>513443</v>
       </c>
       <c r="R43" t="n">
-        <v>6732598</v>
+        <v>6732646</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5627,7 +5645,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5637,7 +5655,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5646,6 +5669,7 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
+      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5664,10 +5688,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>122791693</v>
+        <v>123951367</v>
       </c>
       <c r="B44" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5676,49 +5700,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513491</v>
+        <v>513441</v>
       </c>
       <c r="R44" t="n">
-        <v>6732749</v>
+        <v>6732633</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5742,27 +5758,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5777,22 +5788,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123951744</v>
+        <v>123952048</v>
       </c>
       <c r="B45" t="n">
-        <v>96963</v>
+        <v>98079</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5801,41 +5812,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513434</v>
+        <v>513425</v>
       </c>
       <c r="R45" t="n">
-        <v>6732611</v>
+        <v>6732651</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5864,7 +5875,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5874,12 +5885,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Dålig uppkoppling, bilder går inte atr få med</t>
+          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5906,10 +5917,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123955316</v>
+        <v>123956562</v>
       </c>
       <c r="B46" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5918,25 +5929,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5946,13 +5957,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513440</v>
+        <v>513514</v>
       </c>
       <c r="R46" t="n">
-        <v>6732637</v>
+        <v>6732646</v>
       </c>
       <c r="S46" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5981,7 +5992,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5991,7 +6002,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6006,22 +6017,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123949803</v>
+        <v>123951665</v>
       </c>
       <c r="B47" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6030,25 +6041,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6058,13 +6069,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513439</v>
+        <v>513434</v>
       </c>
       <c r="R47" t="n">
-        <v>6732649</v>
+        <v>6732611</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6093,7 +6104,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6103,7 +6114,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6130,7 +6141,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123174259</v>
+        <v>123174257</v>
       </c>
       <c r="B48" t="n">
         <v>56700</v>
@@ -6178,10 +6189,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513476</v>
+        <v>513437</v>
       </c>
       <c r="R48" t="n">
-        <v>6732720</v>
+        <v>6732675</v>
       </c>
       <c r="S48" t="n">
         <v>25</v>
@@ -6208,27 +6219,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>07:31</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6255,10 +6261,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123956767</v>
+        <v>123950905</v>
       </c>
       <c r="B49" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6267,38 +6273,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513447</v>
+        <v>513442</v>
       </c>
       <c r="R49" t="n">
-        <v>6732560</v>
+        <v>6732642</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6330,7 +6336,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6340,7 +6346,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6367,7 +6378,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123950580</v>
+        <v>123950247</v>
       </c>
       <c r="B50" t="n">
         <v>98079</v>
@@ -6400,17 +6411,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513442</v>
+        <v>513435</v>
       </c>
       <c r="R50" t="n">
-        <v>6732640</v>
+        <v>6732618</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -6442,7 +6457,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6452,7 +6467,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6479,10 +6499,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123950247</v>
+        <v>123951744</v>
       </c>
       <c r="B51" t="n">
-        <v>98079</v>
+        <v>96963</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6491,45 +6511,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513435</v>
+        <v>513434</v>
       </c>
       <c r="R51" t="n">
-        <v>6732618</v>
+        <v>6732611</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6558,7 +6574,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6568,12 +6584,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
+          <t>Dålig uppkoppling, bilder går inte atr få med</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6600,10 +6616,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>122789501</v>
+        <v>123949803</v>
       </c>
       <c r="B52" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6612,53 +6628,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513426</v>
+        <v>513439</v>
       </c>
       <c r="R52" t="n">
-        <v>6732668</v>
+        <v>6732649</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6682,27 +6686,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6729,7 +6728,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123174162</v>
+        <v>122791693</v>
       </c>
       <c r="B53" t="n">
         <v>56700</v>
@@ -6767,20 +6766,20 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513433</v>
+        <v>513491</v>
       </c>
       <c r="R53" t="n">
-        <v>6732675</v>
+        <v>6732749</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6807,27 +6806,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Under tall, troligt sovträd</t>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6854,7 +6853,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123174256</v>
+        <v>123953880</v>
       </c>
       <c r="B54" t="n">
         <v>56700</v>
@@ -6888,27 +6887,24 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
       <c r="M54" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513476</v>
+        <v>513440</v>
       </c>
       <c r="R54" t="n">
-        <v>6732711</v>
+        <v>6732637</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6932,22 +6928,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6962,22 +6958,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123174130</v>
+        <v>123951374</v>
       </c>
       <c r="B55" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6986,49 +6982,53 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513586</v>
+        <v>513434</v>
       </c>
       <c r="R55" t="n">
-        <v>6732786</v>
+        <v>6732611</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7052,27 +7052,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
+          <t>Avverkning pågår</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7081,6 +7081,7 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
+      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
@@ -7099,10 +7100,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123174186</v>
+        <v>123951771</v>
       </c>
       <c r="B56" t="n">
-        <v>56700</v>
+        <v>96963</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7115,45 +7116,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513473</v>
+        <v>513461</v>
       </c>
       <c r="R56" t="n">
-        <v>6732751</v>
+        <v>6732598</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7177,27 +7170,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>07:39</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Trol. sovträd med färsk och äldre spillning under</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7224,7 +7212,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123174257</v>
+        <v>122789602</v>
       </c>
       <c r="B57" t="n">
         <v>56700</v>
@@ -7268,17 +7256,17 @@
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513437</v>
+        <v>513429</v>
       </c>
       <c r="R57" t="n">
-        <v>6732675</v>
+        <v>6732681</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7302,22 +7290,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Några hundratal spillning under s.k. sovtall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7344,10 +7337,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123954554</v>
+        <v>123174130</v>
       </c>
       <c r="B58" t="n">
-        <v>96957</v>
+        <v>56700</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7360,37 +7353,45 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513484</v>
+        <v>513586</v>
       </c>
       <c r="R58" t="n">
-        <v>6732609</v>
+        <v>6732786</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7414,22 +7415,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7456,7 +7462,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122789602</v>
+        <v>122789501</v>
       </c>
       <c r="B59" t="n">
         <v>56700</v>
@@ -7489,7 +7495,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
@@ -7504,10 +7514,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513429</v>
+        <v>513426</v>
       </c>
       <c r="R59" t="n">
-        <v>6732681</v>
+        <v>6732668</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7539,7 +7549,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7549,12 +7559,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Några hundratal spillning under s.k. sovtall</t>
+          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7581,10 +7591,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123952048</v>
+        <v>123174256</v>
       </c>
       <c r="B60" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7593,41 +7603,49 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513425</v>
+        <v>513476</v>
       </c>
       <c r="R60" t="n">
-        <v>6732651</v>
+        <v>6732711</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7651,27 +7669,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7698,7 +7711,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123951665</v>
+        <v>123954554</v>
       </c>
       <c r="B61" t="n">
         <v>96957</v>
@@ -7734,17 +7747,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513434</v>
+        <v>513484</v>
       </c>
       <c r="R61" t="n">
-        <v>6732611</v>
+        <v>6732609</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7773,7 +7786,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7783,7 +7796,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY61"/>
+  <dimension ref="A1:AY62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3314,10 +3314,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>122790237</v>
+        <v>122791590</v>
       </c>
       <c r="B24" t="n">
-        <v>96957</v>
+        <v>96963</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3330,16 +3330,16 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
@@ -3358,10 +3358,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>513429</v>
+        <v>513512</v>
       </c>
       <c r="R24" t="n">
-        <v>6732604</v>
+        <v>6732717</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3393,7 +3393,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:54</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3403,7 +3403,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:54</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Typisk art i 9010 Taiga (Alpin region (ALP) Typisk art i 2320 Rissandhedar  Boreal region (BOR),  Kontinental region (CON))</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3431,10 +3436,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>122791590</v>
+        <v>122790237</v>
       </c>
       <c r="B25" t="n">
-        <v>96963</v>
+        <v>96957</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3447,16 +3452,16 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
@@ -3475,10 +3480,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>513512</v>
+        <v>513429</v>
       </c>
       <c r="R25" t="n">
-        <v>6732717</v>
+        <v>6732604</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3510,7 +3515,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:54</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3520,12 +3525,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:54</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Typisk art i 9010 Taiga (Alpin region (ALP) Typisk art i 2320 Rissandhedar  Boreal region (BOR),  Kontinental region (CON))</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -4996,10 +4996,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123954221</v>
+        <v>123953543</v>
       </c>
       <c r="B38" t="n">
-        <v>96957</v>
+        <v>78788</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5008,41 +5008,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513440</v>
+        <v>513415</v>
       </c>
       <c r="R38" t="n">
-        <v>6732637</v>
+        <v>6732596</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5096,12 +5096,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -5220,10 +5220,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123953543</v>
+        <v>123951312</v>
       </c>
       <c r="B40" t="n">
-        <v>78788</v>
+        <v>96963</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5232,25 +5232,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -5260,13 +5260,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513415</v>
+        <v>513430</v>
       </c>
       <c r="R40" t="n">
-        <v>6732596</v>
+        <v>6732614</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5295,7 +5295,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5305,7 +5305,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Några plantor</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5332,10 +5337,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123951312</v>
+        <v>123954221</v>
       </c>
       <c r="B41" t="n">
-        <v>96963</v>
+        <v>96957</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5348,16 +5353,16 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -5368,14 +5373,14 @@
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513430</v>
+        <v>513440</v>
       </c>
       <c r="R41" t="n">
-        <v>6732614</v>
+        <v>6732637</v>
       </c>
       <c r="S41" t="n">
         <v>1</v>
@@ -5407,7 +5412,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5417,12 +5422,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Några plantor</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5437,12 +5437,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -6141,10 +6141,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123174257</v>
+        <v>123950905</v>
       </c>
       <c r="B48" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6153,49 +6153,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513437</v>
+        <v>513442</v>
       </c>
       <c r="R48" t="n">
-        <v>6732675</v>
+        <v>6732642</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6219,22 +6211,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6261,7 +6258,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123950905</v>
+        <v>123950247</v>
       </c>
       <c r="B49" t="n">
         <v>98079</v>
@@ -6294,20 +6291,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513442</v>
+        <v>513435</v>
       </c>
       <c r="R49" t="n">
-        <v>6732642</v>
+        <v>6732618</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6336,7 +6337,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6346,12 +6347,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
+          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6378,10 +6379,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123950247</v>
+        <v>123951744</v>
       </c>
       <c r="B50" t="n">
-        <v>98079</v>
+        <v>96963</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6390,45 +6391,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513435</v>
+        <v>513434</v>
       </c>
       <c r="R50" t="n">
-        <v>6732618</v>
+        <v>6732611</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6457,7 +6454,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6467,12 +6464,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
+          <t>Dålig uppkoppling, bilder går inte atr få med</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6499,10 +6496,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123951744</v>
+        <v>123174257</v>
       </c>
       <c r="B51" t="n">
-        <v>96963</v>
+        <v>56700</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6515,37 +6512,45 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513434</v>
+        <v>513437</v>
       </c>
       <c r="R51" t="n">
-        <v>6732611</v>
+        <v>6732675</v>
       </c>
       <c r="S51" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6569,27 +6574,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Dålig uppkoppling, bilder går inte atr få med</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6853,10 +6853,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123953880</v>
+        <v>123951374</v>
       </c>
       <c r="B54" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6865,43 +6865,50 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513440</v>
+        <v>513434</v>
       </c>
       <c r="R54" t="n">
-        <v>6732637</v>
+        <v>6732611</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6933,7 +6940,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6943,7 +6950,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>14:40</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Avverkning pågår</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6952,28 +6964,29 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
+      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123951374</v>
+        <v>123953880</v>
       </c>
       <c r="B55" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6982,50 +6995,43 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513434</v>
+        <v>513440</v>
       </c>
       <c r="R55" t="n">
-        <v>6732611</v>
+        <v>6732637</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -7057,7 +7063,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7067,12 +7073,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Avverkning pågår</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7081,29 +7082,28 @@
       <c r="AE55" t="b">
         <v>0</v>
       </c>
-      <c r="AF55" t="inlineStr"/>
       <c r="AG55" t="b">
         <v>0</v>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123951771</v>
+        <v>122789602</v>
       </c>
       <c r="B56" t="n">
-        <v>96963</v>
+        <v>56700</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7116,34 +7116,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513461</v>
+        <v>513429</v>
       </c>
       <c r="R56" t="n">
-        <v>6732598</v>
+        <v>6732681</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7170,22 +7178,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Några hundratal spillning under s.k. sovtall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7212,10 +7225,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122789602</v>
+        <v>123951771</v>
       </c>
       <c r="B57" t="n">
-        <v>56700</v>
+        <v>96963</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7228,42 +7241,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513429</v>
+        <v>513461</v>
       </c>
       <c r="R57" t="n">
-        <v>6732681</v>
+        <v>6732598</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7290,27 +7295,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Några hundratal spillning under s.k. sovtall</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7821,6 +7821,132 @@
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>123956699</v>
+      </c>
+      <c r="B62" t="n">
+        <v>96957</v>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>513448</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6732560</v>
+      </c>
+      <c r="S62" t="n">
+        <v>1</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>18:59</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Delvis överkörda av skördare</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -3553,10 +3553,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123950580</v>
+        <v>123174129</v>
       </c>
       <c r="B26" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3565,41 +3565,53 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513442</v>
+        <v>513357</v>
       </c>
       <c r="R26" t="n">
-        <v>6732640</v>
+        <v>6732614</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3623,22 +3635,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Fjäder från en äldre tjäderhanne</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3665,7 +3682,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123174258</v>
+        <v>122791693</v>
       </c>
       <c r="B27" t="n">
         <v>56700</v>
@@ -3703,20 +3720,20 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513428</v>
+        <v>513491</v>
       </c>
       <c r="R27" t="n">
-        <v>6732689</v>
+        <v>6732749</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3743,22 +3760,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3785,10 +3807,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123174141</v>
+        <v>123949969</v>
       </c>
       <c r="B28" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3797,49 +3819,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513432</v>
+        <v>513443</v>
       </c>
       <c r="R28" t="n">
-        <v>6732690</v>
+        <v>6732646</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3863,27 +3881,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Sovträd med spillning under.</t>
+          <t>Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3892,6 +3910,7 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
+      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3910,10 +3929,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123174186</v>
+        <v>123954347</v>
       </c>
       <c r="B29" t="n">
-        <v>56700</v>
+        <v>96957</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3926,45 +3945,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513473</v>
+        <v>513440</v>
       </c>
       <c r="R29" t="n">
-        <v>6732751</v>
+        <v>6732637</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3988,27 +3999,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>07:39</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Trol. sovträd med färsk och äldre spillning under</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4023,19 +4029,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123955316</v>
+        <v>123950580</v>
       </c>
       <c r="B30" t="n">
         <v>98079</v>
@@ -4071,17 +4077,17 @@
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513440</v>
+        <v>513442</v>
       </c>
       <c r="R30" t="n">
-        <v>6732637</v>
+        <v>6732640</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4110,7 +4116,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4120,7 +4126,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4135,22 +4141,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123956767</v>
+        <v>123174141</v>
       </c>
       <c r="B31" t="n">
-        <v>96957</v>
+        <v>56700</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4163,37 +4169,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513447</v>
+        <v>513432</v>
       </c>
       <c r="R31" t="n">
-        <v>6732560</v>
+        <v>6732690</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4217,22 +4231,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Sovträd med spillning under.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4259,10 +4278,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123950117</v>
+        <v>123951744</v>
       </c>
       <c r="B32" t="n">
-        <v>98079</v>
+        <v>96963</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4271,50 +4290,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513452</v>
+        <v>513434</v>
       </c>
       <c r="R32" t="n">
-        <v>6732659</v>
+        <v>6732611</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4343,7 +4353,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4353,7 +4363,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Dålig uppkoppling, bilder går inte atr få med</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4368,22 +4383,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123174259</v>
+        <v>123954554</v>
       </c>
       <c r="B33" t="n">
-        <v>56700</v>
+        <v>96957</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4396,45 +4411,37 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513476</v>
+        <v>513484</v>
       </c>
       <c r="R33" t="n">
-        <v>6732720</v>
+        <v>6732609</v>
       </c>
       <c r="S33" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4458,27 +4465,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>07:31</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4505,10 +4507,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123174131</v>
+        <v>123952048</v>
       </c>
       <c r="B34" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4517,49 +4519,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513575</v>
+        <v>513425</v>
       </c>
       <c r="R34" t="n">
-        <v>6732778</v>
+        <v>6732651</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4583,27 +4577,27 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>På mossig stubbe, troligen blåbärsspillning</t>
+          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4630,7 +4624,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123950844</v>
+        <v>123951412</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -4666,17 +4660,17 @@
       <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513461</v>
+        <v>513434</v>
       </c>
       <c r="R35" t="n">
-        <v>6732632</v>
+        <v>6732611</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4705,7 +4699,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4715,7 +4709,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4742,10 +4736,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123174129</v>
+        <v>123951665</v>
       </c>
       <c r="B36" t="n">
-        <v>56700</v>
+        <v>96957</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4758,49 +4752,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513357</v>
+        <v>513434</v>
       </c>
       <c r="R36" t="n">
-        <v>6732614</v>
+        <v>6732611</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4824,27 +4806,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Fjäder från en äldre tjäderhanne</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4871,10 +4848,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123174162</v>
+        <v>123949803</v>
       </c>
       <c r="B37" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4883,49 +4860,41 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513433</v>
+        <v>513439</v>
       </c>
       <c r="R37" t="n">
-        <v>6732675</v>
+        <v>6732649</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4949,27 +4918,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Under tall, troligt sovträd</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4996,10 +4960,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123953543</v>
+        <v>123953880</v>
       </c>
       <c r="B38" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -5008,41 +4972,46 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513415</v>
+        <v>513440</v>
       </c>
       <c r="R38" t="n">
-        <v>6732596</v>
+        <v>6732637</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5071,7 +5040,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5081,7 +5050,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5096,22 +5065,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123953103</v>
+        <v>123174162</v>
       </c>
       <c r="B39" t="n">
-        <v>5176</v>
+        <v>56700</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5124,37 +5093,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513440</v>
+        <v>513433</v>
       </c>
       <c r="R39" t="n">
-        <v>6732637</v>
+        <v>6732675</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5178,22 +5155,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Under tall, troligt sovträd</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5208,22 +5190,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123951312</v>
+        <v>123956562</v>
       </c>
       <c r="B40" t="n">
-        <v>96963</v>
+        <v>96957</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5236,16 +5218,16 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
@@ -5256,17 +5238,17 @@
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513430</v>
+        <v>513514</v>
       </c>
       <c r="R40" t="n">
-        <v>6732614</v>
+        <v>6732646</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5295,7 +5277,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5305,12 +5287,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Några plantor</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5337,10 +5314,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123954221</v>
+        <v>123949914</v>
       </c>
       <c r="B41" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5349,41 +5326,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
         <v>513440</v>
       </c>
       <c r="R41" t="n">
-        <v>6732637</v>
+        <v>6732648</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5412,7 +5389,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5422,7 +5399,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5437,22 +5419,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123949914</v>
+        <v>123956767</v>
       </c>
       <c r="B42" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5461,41 +5443,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513440</v>
+        <v>513447</v>
       </c>
       <c r="R42" t="n">
-        <v>6732648</v>
+        <v>6732560</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5524,7 +5506,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5534,12 +5516,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5566,10 +5543,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123949969</v>
+        <v>122789602</v>
       </c>
       <c r="B43" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5578,45 +5555,49 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513443</v>
+        <v>513429</v>
       </c>
       <c r="R43" t="n">
-        <v>6732646</v>
+        <v>6732681</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5640,27 +5621,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Mellanskog avverkar</t>
+          <t>Några hundratal spillning under s.k. sovtall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5669,7 +5650,6 @@
       <c r="AE43" t="b">
         <v>0</v>
       </c>
-      <c r="AF43" t="inlineStr"/>
       <c r="AG43" t="b">
         <v>0</v>
       </c>
@@ -5688,7 +5668,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123951367</v>
+        <v>123955846</v>
       </c>
       <c r="B44" t="n">
         <v>98079</v>
@@ -5724,14 +5704,14 @@
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513441</v>
+        <v>513440</v>
       </c>
       <c r="R44" t="n">
-        <v>6732633</v>
+        <v>6732637</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5763,7 +5743,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5773,7 +5753,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5800,7 +5780,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123952048</v>
+        <v>123950905</v>
       </c>
       <c r="B45" t="n">
         <v>98079</v>
@@ -5836,17 +5816,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513425</v>
+        <v>513442</v>
       </c>
       <c r="R45" t="n">
-        <v>6732651</v>
+        <v>6732642</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5875,7 +5855,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5885,12 +5865,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
+          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5917,10 +5897,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123956562</v>
+        <v>122789501</v>
       </c>
       <c r="B46" t="n">
-        <v>96957</v>
+        <v>56700</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5933,37 +5913,49 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513514</v>
+        <v>513426</v>
       </c>
       <c r="R46" t="n">
-        <v>6732646</v>
+        <v>6732668</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5987,22 +5979,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6029,10 +6026,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123951665</v>
+        <v>123950117</v>
       </c>
       <c r="B47" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6041,41 +6038,50 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513434</v>
+        <v>513452</v>
       </c>
       <c r="R47" t="n">
-        <v>6732611</v>
+        <v>6732659</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6104,7 +6110,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6114,7 +6120,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6129,22 +6135,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123950905</v>
+        <v>123174130</v>
       </c>
       <c r="B48" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6153,41 +6159,49 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513442</v>
+        <v>513586</v>
       </c>
       <c r="R48" t="n">
-        <v>6732642</v>
+        <v>6732786</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6211,27 +6225,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
+          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6258,10 +6272,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123950247</v>
+        <v>123174257</v>
       </c>
       <c r="B49" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6270,45 +6284,49 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513435</v>
+        <v>513437</v>
       </c>
       <c r="R49" t="n">
-        <v>6732618</v>
+        <v>6732675</v>
       </c>
       <c r="S49" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6332,27 +6350,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6379,10 +6392,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123951744</v>
+        <v>123174259</v>
       </c>
       <c r="B50" t="n">
-        <v>96963</v>
+        <v>56700</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6395,37 +6408,45 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513434</v>
+        <v>513476</v>
       </c>
       <c r="R50" t="n">
-        <v>6732611</v>
+        <v>6732720</v>
       </c>
       <c r="S50" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6449,27 +6470,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Dålig uppkoppling, bilder går inte atr få med</t>
+          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6496,10 +6517,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123174257</v>
+        <v>123953543</v>
       </c>
       <c r="B51" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6508,46 +6529,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513437</v>
+        <v>513415</v>
       </c>
       <c r="R51" t="n">
-        <v>6732675</v>
+        <v>6732596</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6574,22 +6587,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6616,10 +6629,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123949803</v>
+        <v>123951286</v>
       </c>
       <c r="B52" t="n">
-        <v>98079</v>
+        <v>96963</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6628,25 +6641,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6656,13 +6669,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513439</v>
+        <v>513430</v>
       </c>
       <c r="R52" t="n">
-        <v>6732649</v>
+        <v>6732614</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6691,7 +6704,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6701,7 +6714,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Kammossa linnea, olika vitmossor, björnmossaetc</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6728,7 +6746,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>122791693</v>
+        <v>123174131</v>
       </c>
       <c r="B53" t="n">
         <v>56700</v>
@@ -6772,14 +6790,14 @@
       <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513491</v>
+        <v>513575</v>
       </c>
       <c r="R53" t="n">
-        <v>6732749</v>
+        <v>6732778</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6806,27 +6824,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Blåbärsspillning</t>
+          <t>På mossig stubbe, troligen blåbärsspillning</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6853,10 +6871,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123951374</v>
+        <v>123953103</v>
       </c>
       <c r="B54" t="n">
-        <v>98079</v>
+        <v>5176</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6865,50 +6883,38 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513434</v>
+        <v>513440</v>
       </c>
       <c r="R54" t="n">
-        <v>6732611</v>
+        <v>6732637</v>
       </c>
       <c r="S54" t="n">
         <v>1</v>
@@ -6940,7 +6946,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6950,12 +6956,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:40</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Avverkning pågår</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6964,29 +6965,28 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123953880</v>
+        <v>123951367</v>
       </c>
       <c r="B55" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6995,43 +6995,38 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513440</v>
+        <v>513441</v>
       </c>
       <c r="R55" t="n">
-        <v>6732637</v>
+        <v>6732633</v>
       </c>
       <c r="S55" t="n">
         <v>1</v>
@@ -7063,7 +7058,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7073,7 +7068,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7100,7 +7095,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122789602</v>
+        <v>123174256</v>
       </c>
       <c r="B56" t="n">
         <v>56700</v>
@@ -7144,17 +7139,17 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513429</v>
+        <v>513476</v>
       </c>
       <c r="R56" t="n">
-        <v>6732681</v>
+        <v>6732711</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7178,27 +7173,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Några hundratal spillning under s.k. sovtall</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7337,10 +7327,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123174130</v>
+        <v>123950247</v>
       </c>
       <c r="B58" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7349,49 +7339,45 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513586</v>
+        <v>513435</v>
       </c>
       <c r="R58" t="n">
-        <v>6732786</v>
+        <v>6732618</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7415,27 +7401,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
+          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7462,7 +7448,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122789501</v>
+        <v>123174258</v>
       </c>
       <c r="B59" t="n">
         <v>56700</v>
@@ -7495,11 +7481,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
@@ -7510,17 +7492,17 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513426</v>
+        <v>513428</v>
       </c>
       <c r="R59" t="n">
-        <v>6732668</v>
+        <v>6732689</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7544,27 +7526,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7591,7 +7568,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123174256</v>
+        <v>123174186</v>
       </c>
       <c r="B60" t="n">
         <v>56700</v>
@@ -7639,10 +7616,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513476</v>
+        <v>513473</v>
       </c>
       <c r="R60" t="n">
-        <v>6732711</v>
+        <v>6732751</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7669,22 +7646,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Trol. sovträd med färsk och äldre spillning under</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7711,10 +7693,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123954554</v>
+        <v>123950844</v>
       </c>
       <c r="B61" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7723,41 +7705,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513484</v>
+        <v>513461</v>
       </c>
       <c r="R61" t="n">
-        <v>6732609</v>
+        <v>6732632</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7786,7 +7768,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7796,7 +7778,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -5077,10 +5077,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123174162</v>
+        <v>123956562</v>
       </c>
       <c r="B39" t="n">
-        <v>56700</v>
+        <v>96957</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5093,42 +5093,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513433</v>
+        <v>513514</v>
       </c>
       <c r="R39" t="n">
-        <v>6732675</v>
+        <v>6732646</v>
       </c>
       <c r="S39" t="n">
         <v>25</v>
@@ -5155,27 +5147,22 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Under tall, troligt sovträd</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5202,10 +5189,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123956562</v>
+        <v>123174162</v>
       </c>
       <c r="B40" t="n">
-        <v>96957</v>
+        <v>56700</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5218,34 +5205,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513514</v>
+        <v>513433</v>
       </c>
       <c r="R40" t="n">
-        <v>6732646</v>
+        <v>6732675</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5272,22 +5267,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Under tall, troligt sovträd</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5314,10 +5314,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123949914</v>
+        <v>123956767</v>
       </c>
       <c r="B41" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5326,41 +5326,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513440</v>
+        <v>513447</v>
       </c>
       <c r="R41" t="n">
-        <v>6732648</v>
+        <v>6732560</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5399,12 +5399,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5431,10 +5426,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123956767</v>
+        <v>123949914</v>
       </c>
       <c r="B42" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5443,41 +5438,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513447</v>
+        <v>513440</v>
       </c>
       <c r="R42" t="n">
-        <v>6732560</v>
+        <v>6732648</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5506,7 +5501,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5516,7 +5511,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -7095,10 +7095,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123174256</v>
+        <v>123951771</v>
       </c>
       <c r="B56" t="n">
-        <v>56700</v>
+        <v>96963</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7111,45 +7111,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513476</v>
+        <v>513461</v>
       </c>
       <c r="R56" t="n">
-        <v>6732711</v>
+        <v>6732598</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7173,22 +7165,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7215,10 +7207,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123951771</v>
+        <v>123174256</v>
       </c>
       <c r="B57" t="n">
-        <v>96963</v>
+        <v>56700</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7231,37 +7223,45 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513461</v>
+        <v>513476</v>
       </c>
       <c r="R57" t="n">
-        <v>6732598</v>
+        <v>6732711</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7285,22 +7285,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD57" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -3553,7 +3553,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123174129</v>
+        <v>123953720</v>
       </c>
       <c r="B26" t="n">
         <v>56700</v>
@@ -3586,32 +3586,20 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513357</v>
+        <v>513440</v>
       </c>
       <c r="R26" t="n">
-        <v>6732614</v>
+        <v>6732637</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3635,27 +3623,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Fjäder från en äldre tjäderhanne</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3670,22 +3658,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>122791693</v>
+        <v>123950580</v>
       </c>
       <c r="B27" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3694,49 +3682,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513491</v>
+        <v>513442</v>
       </c>
       <c r="R27" t="n">
-        <v>6732749</v>
+        <v>6732640</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3760,27 +3740,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3807,7 +3782,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123949969</v>
+        <v>123949914</v>
       </c>
       <c r="B28" t="n">
         <v>98079</v>
@@ -3841,23 +3816,19 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513443</v>
+        <v>513440</v>
       </c>
       <c r="R28" t="n">
-        <v>6732646</v>
+        <v>6732648</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3886,7 +3857,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3896,12 +3867,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
         <is>
-          <t>Mellanskog avverkar</t>
+          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3910,7 +3881,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3929,10 +3899,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123954347</v>
+        <v>123949969</v>
       </c>
       <c r="B29" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3941,38 +3911,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513440</v>
+        <v>513443</v>
       </c>
       <c r="R29" t="n">
-        <v>6732637</v>
+        <v>6732646</v>
       </c>
       <c r="S29" t="n">
         <v>1</v>
@@ -4004,7 +3978,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4014,7 +3988,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4023,25 +4002,26 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123950580</v>
+        <v>123951599</v>
       </c>
       <c r="B30" t="n">
         <v>98079</v>
@@ -4081,13 +4061,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513442</v>
+        <v>513434</v>
       </c>
       <c r="R30" t="n">
-        <v>6732640</v>
+        <v>6732611</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4116,7 +4096,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4126,7 +4106,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Snön har legat länge i de skuggiga svackorna</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4153,10 +4138,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123174141</v>
+        <v>123953103</v>
       </c>
       <c r="B31" t="n">
-        <v>56700</v>
+        <v>5176</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4169,45 +4154,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513432</v>
+        <v>513440</v>
       </c>
       <c r="R31" t="n">
-        <v>6732690</v>
+        <v>6732637</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4231,27 +4208,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Sovträd med spillning under.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4266,22 +4238,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123951744</v>
+        <v>123954221</v>
       </c>
       <c r="B32" t="n">
-        <v>96963</v>
+        <v>96957</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4294,16 +4266,16 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -4314,14 +4286,14 @@
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513434</v>
+        <v>513440</v>
       </c>
       <c r="R32" t="n">
-        <v>6732611</v>
+        <v>6732637</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4353,7 +4325,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4363,12 +4335,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Dålig uppkoppling, bilder går inte atr få med</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4383,22 +4350,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123954554</v>
+        <v>123951312</v>
       </c>
       <c r="B33" t="n">
-        <v>96957</v>
+        <v>96963</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4411,16 +4378,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -4431,17 +4398,17 @@
       <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513484</v>
+        <v>513430</v>
       </c>
       <c r="R33" t="n">
-        <v>6732609</v>
+        <v>6732614</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4470,7 +4437,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4480,7 +4447,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Några plantor</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4507,10 +4479,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123952048</v>
+        <v>123956767</v>
       </c>
       <c r="B34" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4519,41 +4491,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513425</v>
+        <v>513447</v>
       </c>
       <c r="R34" t="n">
-        <v>6732651</v>
+        <v>6732560</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4582,7 +4554,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4592,12 +4564,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4624,7 +4591,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123951412</v>
+        <v>123951429</v>
       </c>
       <c r="B35" t="n">
         <v>98079</v>
@@ -4664,10 +4631,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513434</v>
+        <v>513440</v>
       </c>
       <c r="R35" t="n">
-        <v>6732611</v>
+        <v>6732637</v>
       </c>
       <c r="S35" t="n">
         <v>1</v>
@@ -4699,7 +4666,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4709,7 +4676,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4724,19 +4691,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123951665</v>
+        <v>123954554</v>
       </c>
       <c r="B36" t="n">
         <v>96957</v>
@@ -4772,17 +4739,17 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513434</v>
+        <v>513484</v>
       </c>
       <c r="R36" t="n">
-        <v>6732611</v>
+        <v>6732609</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4811,7 +4778,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4821,7 +4788,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4848,7 +4815,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123949803</v>
+        <v>123952048</v>
       </c>
       <c r="B37" t="n">
         <v>98079</v>
@@ -4884,17 +4851,17 @@
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513439</v>
+        <v>513425</v>
       </c>
       <c r="R37" t="n">
-        <v>6732649</v>
+        <v>6732651</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4923,7 +4890,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4933,7 +4900,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4960,7 +4932,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123953880</v>
+        <v>123174186</v>
       </c>
       <c r="B38" t="n">
         <v>56700</v>
@@ -4994,24 +4966,27 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513440</v>
+        <v>513473</v>
       </c>
       <c r="R38" t="n">
-        <v>6732637</v>
+        <v>6732751</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5035,22 +5010,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Trol. sovträd med färsk och äldre spillning under</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5065,22 +5045,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123956562</v>
+        <v>123950117</v>
       </c>
       <c r="B39" t="n">
-        <v>96957</v>
+        <v>98079</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5089,41 +5069,50 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513514</v>
+        <v>513452</v>
       </c>
       <c r="R39" t="n">
-        <v>6732646</v>
+        <v>6732659</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5152,7 +5141,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5162,7 +5151,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5177,22 +5166,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123174162</v>
+        <v>123950844</v>
       </c>
       <c r="B40" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5201,46 +5190,38 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513433</v>
+        <v>513461</v>
       </c>
       <c r="R40" t="n">
-        <v>6732675</v>
+        <v>6732632</v>
       </c>
       <c r="S40" t="n">
         <v>25</v>
@@ -5267,27 +5248,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Under tall, troligt sovträd</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5314,10 +5290,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123956767</v>
+        <v>123174257</v>
       </c>
       <c r="B41" t="n">
-        <v>96957</v>
+        <v>56700</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5330,37 +5306,45 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513447</v>
+        <v>513437</v>
       </c>
       <c r="R41" t="n">
-        <v>6732560</v>
+        <v>6732675</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5384,22 +5368,22 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5426,7 +5410,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123949914</v>
+        <v>123950905</v>
       </c>
       <c r="B42" t="n">
         <v>98079</v>
@@ -5466,13 +5450,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513440</v>
+        <v>513442</v>
       </c>
       <c r="R42" t="n">
-        <v>6732648</v>
+        <v>6732642</v>
       </c>
       <c r="S42" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5501,7 +5485,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5511,12 +5495,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
+          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5543,10 +5527,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122789602</v>
+        <v>123950247</v>
       </c>
       <c r="B43" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5555,49 +5539,45 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513429</v>
+        <v>513435</v>
       </c>
       <c r="R43" t="n">
-        <v>6732681</v>
+        <v>6732618</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5621,27 +5601,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Några hundratal spillning under s.k. sovtall</t>
+          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5668,10 +5648,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123955846</v>
+        <v>123951771</v>
       </c>
       <c r="B44" t="n">
-        <v>98079</v>
+        <v>96963</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5680,25 +5660,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5708,13 +5688,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513440</v>
+        <v>513461</v>
       </c>
       <c r="R44" t="n">
-        <v>6732637</v>
+        <v>6732598</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5743,7 +5723,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5753,7 +5733,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5768,22 +5748,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123950905</v>
+        <v>123951744</v>
       </c>
       <c r="B45" t="n">
-        <v>98079</v>
+        <v>96963</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5792,25 +5772,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5820,10 +5800,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513442</v>
+        <v>513434</v>
       </c>
       <c r="R45" t="n">
-        <v>6732642</v>
+        <v>6732611</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5855,7 +5835,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5865,12 +5845,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
+          <t>Dålig uppkoppling, bilder går inte atr få med</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6026,10 +6006,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123950117</v>
+        <v>123951665</v>
       </c>
       <c r="B47" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6038,50 +6018,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J47" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513452</v>
+        <v>513434</v>
       </c>
       <c r="R47" t="n">
-        <v>6732659</v>
+        <v>6732611</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6110,7 +6081,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6120,7 +6091,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6135,12 +6106,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -6272,7 +6243,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123174257</v>
+        <v>123174129</v>
       </c>
       <c r="B49" t="n">
         <v>56700</v>
@@ -6305,12 +6276,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6320,10 +6295,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513437</v>
+        <v>513357</v>
       </c>
       <c r="R49" t="n">
-        <v>6732675</v>
+        <v>6732614</v>
       </c>
       <c r="S49" t="n">
         <v>25</v>
@@ -6355,7 +6330,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6365,7 +6340,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Fjäder från en äldre tjäderhanne</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6392,7 +6372,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123174259</v>
+        <v>123174131</v>
       </c>
       <c r="B50" t="n">
         <v>56700</v>
@@ -6430,7 +6410,7 @@
       <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N50" t="inlineStr"/>
@@ -6440,10 +6420,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513476</v>
+        <v>513575</v>
       </c>
       <c r="R50" t="n">
-        <v>6732720</v>
+        <v>6732778</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6470,27 +6450,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
+          <t>På mossig stubbe, troligen blåbärsspillning</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6517,10 +6497,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123953543</v>
+        <v>123174259</v>
       </c>
       <c r="B51" t="n">
-        <v>78788</v>
+        <v>56700</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6529,38 +6509,46 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513415</v>
+        <v>513476</v>
       </c>
       <c r="R51" t="n">
-        <v>6732596</v>
+        <v>6732720</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6587,22 +6575,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6629,10 +6622,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123951286</v>
+        <v>123174162</v>
       </c>
       <c r="B52" t="n">
-        <v>96963</v>
+        <v>56700</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6645,37 +6638,45 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513430</v>
+        <v>513433</v>
       </c>
       <c r="R52" t="n">
-        <v>6732614</v>
+        <v>6732675</v>
       </c>
       <c r="S52" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6699,27 +6700,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Kammossa linnea, olika vitmossor, björnmossaetc</t>
+          <t>Under tall, troligt sovträd</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6746,7 +6747,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123174131</v>
+        <v>123174141</v>
       </c>
       <c r="B53" t="n">
         <v>56700</v>
@@ -6784,7 +6785,7 @@
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N53" t="inlineStr"/>
@@ -6794,10 +6795,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513575</v>
+        <v>513432</v>
       </c>
       <c r="R53" t="n">
-        <v>6732778</v>
+        <v>6732690</v>
       </c>
       <c r="S53" t="n">
         <v>25</v>
@@ -6824,27 +6825,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>På mossig stubbe, troligen blåbärsspillning</t>
+          <t>Sovträd med spillning under.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6871,10 +6872,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123953103</v>
+        <v>122791693</v>
       </c>
       <c r="B54" t="n">
-        <v>5176</v>
+        <v>56700</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6887,37 +6888,45 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513440</v>
+        <v>513491</v>
       </c>
       <c r="R54" t="n">
-        <v>6732637</v>
+        <v>6732749</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6941,22 +6950,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6971,22 +6985,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123951367</v>
+        <v>123956562</v>
       </c>
       <c r="B55" t="n">
-        <v>98079</v>
+        <v>96957</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6995,41 +7009,41 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513441</v>
+        <v>513514</v>
       </c>
       <c r="R55" t="n">
-        <v>6732633</v>
+        <v>6732646</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7058,7 +7072,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -7068,7 +7082,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7083,22 +7097,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123951771</v>
+        <v>122789602</v>
       </c>
       <c r="B56" t="n">
-        <v>96963</v>
+        <v>56700</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7111,34 +7125,42 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513461</v>
+        <v>513429</v>
       </c>
       <c r="R56" t="n">
-        <v>6732598</v>
+        <v>6732681</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7165,22 +7187,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Några hundratal spillning under s.k. sovtall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7207,10 +7234,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123174256</v>
+        <v>123951367</v>
       </c>
       <c r="B57" t="n">
-        <v>56700</v>
+        <v>98079</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7219,49 +7246,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513476</v>
+        <v>513441</v>
       </c>
       <c r="R57" t="n">
-        <v>6732711</v>
+        <v>6732633</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7285,22 +7304,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7315,22 +7334,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123950247</v>
+        <v>123174256</v>
       </c>
       <c r="B58" t="n">
-        <v>98079</v>
+        <v>56700</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7339,45 +7358,49 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513435</v>
+        <v>513476</v>
       </c>
       <c r="R58" t="n">
-        <v>6732618</v>
+        <v>6732711</v>
       </c>
       <c r="S58" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7401,27 +7424,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7568,10 +7586,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123174186</v>
+        <v>123953543</v>
       </c>
       <c r="B60" t="n">
-        <v>56700</v>
+        <v>78788</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7580,46 +7598,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513473</v>
+        <v>513415</v>
       </c>
       <c r="R60" t="n">
-        <v>6732751</v>
+        <v>6732596</v>
       </c>
       <c r="S60" t="n">
         <v>25</v>
@@ -7646,27 +7656,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>07:39</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Trol. sovträd med färsk och äldre spillning under</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7693,7 +7698,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123950844</v>
+        <v>123949803</v>
       </c>
       <c r="B61" t="n">
         <v>98079</v>
@@ -7729,17 +7734,17 @@
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513461</v>
+        <v>513439</v>
       </c>
       <c r="R61" t="n">
-        <v>6732632</v>
+        <v>6732649</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7768,7 +7773,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7778,7 +7783,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -3553,7 +3553,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123952048</v>
+        <v>123955316</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3593,13 +3593,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513425</v>
+        <v>513440</v>
       </c>
       <c r="R26" t="n">
-        <v>6732651</v>
+        <v>6732637</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3638,12 +3638,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3658,19 +3653,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123953880</v>
+        <v>123174258</v>
       </c>
       <c r="B27" t="n">
         <v>56722</v>
@@ -3704,24 +3699,27 @@
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>stationär</t>
-        </is>
-      </c>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513440</v>
+        <v>513428</v>
       </c>
       <c r="R27" t="n">
-        <v>6732637</v>
+        <v>6732689</v>
       </c>
       <c r="S27" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3745,22 +3743,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3775,22 +3773,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123951412</v>
+        <v>123174131</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3799,41 +3797,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513434</v>
+        <v>513575</v>
       </c>
       <c r="R28" t="n">
-        <v>6732611</v>
+        <v>6732778</v>
       </c>
       <c r="S28" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3857,22 +3863,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>På mossig stubbe, troligen blåbärsspillning</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3899,7 +3910,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123174141</v>
+        <v>123174259</v>
       </c>
       <c r="B29" t="n">
         <v>56722</v>
@@ -3947,10 +3958,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513432</v>
+        <v>513476</v>
       </c>
       <c r="R29" t="n">
-        <v>6732690</v>
+        <v>6732720</v>
       </c>
       <c r="S29" t="n">
         <v>25</v>
@@ -3977,27 +3988,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Sovträd med spillning under.</t>
+          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4024,10 +4035,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123950580</v>
+        <v>123954904</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4036,41 +4047,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513442</v>
+        <v>513440</v>
       </c>
       <c r="R30" t="n">
-        <v>6732640</v>
+        <v>6732637</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4099,7 +4110,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4109,7 +4120,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4124,22 +4135,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123956767</v>
+        <v>123951312</v>
       </c>
       <c r="B31" t="n">
-        <v>96979</v>
+        <v>96985</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4152,16 +4163,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -4172,14 +4183,14 @@
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513447</v>
+        <v>513430</v>
       </c>
       <c r="R31" t="n">
-        <v>6732560</v>
+        <v>6732614</v>
       </c>
       <c r="S31" t="n">
         <v>1</v>
@@ -4211,7 +4222,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4221,7 +4232,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Några plantor</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4248,10 +4264,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123174258</v>
+        <v>123950905</v>
       </c>
       <c r="B32" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4260,49 +4276,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513428</v>
+        <v>513442</v>
       </c>
       <c r="R32" t="n">
-        <v>6732689</v>
+        <v>6732642</v>
       </c>
       <c r="S32" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4326,22 +4334,27 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4368,7 +4381,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123949969</v>
+        <v>123951412</v>
       </c>
       <c r="B33" t="n">
         <v>98101</v>
@@ -4402,20 +4415,16 @@
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513443</v>
+        <v>513434</v>
       </c>
       <c r="R33" t="n">
-        <v>6732646</v>
+        <v>6732611</v>
       </c>
       <c r="S33" t="n">
         <v>1</v>
@@ -4447,7 +4456,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4457,12 +4466,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Mellanskog avverkar</t>
+          <t>14:44</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4471,7 +4475,6 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4490,10 +4493,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123950844</v>
+        <v>123956767</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4502,41 +4505,41 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513461</v>
+        <v>513447</v>
       </c>
       <c r="R34" t="n">
-        <v>6732632</v>
+        <v>6732560</v>
       </c>
       <c r="S34" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4565,7 +4568,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4575,7 +4578,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4602,10 +4605,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123951771</v>
+        <v>122789602</v>
       </c>
       <c r="B35" t="n">
-        <v>96985</v>
+        <v>56722</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4618,34 +4621,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513461</v>
+        <v>513429</v>
       </c>
       <c r="R35" t="n">
-        <v>6732598</v>
+        <v>6732681</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4672,22 +4683,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Några hundratal spillning under s.k. sovtall</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4714,7 +4730,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123174130</v>
+        <v>123953880</v>
       </c>
       <c r="B36" t="n">
         <v>56722</v>
@@ -4748,27 +4764,24 @@
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513586</v>
+        <v>513440</v>
       </c>
       <c r="R36" t="n">
-        <v>6732786</v>
+        <v>6732637</v>
       </c>
       <c r="S36" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4792,27 +4805,22 @@
       </c>
       <c r="Y36" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4827,22 +4835,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123951429</v>
+        <v>123174256</v>
       </c>
       <c r="B37" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4851,41 +4859,49 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513440</v>
+        <v>513476</v>
       </c>
       <c r="R37" t="n">
-        <v>6732637</v>
+        <v>6732711</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4909,22 +4925,22 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4939,22 +4955,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123954554</v>
+        <v>123174129</v>
       </c>
       <c r="B38" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4967,37 +4983,49 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513484</v>
+        <v>513357</v>
       </c>
       <c r="R38" t="n">
-        <v>6732609</v>
+        <v>6732614</v>
       </c>
       <c r="S38" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5021,22 +5049,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Fjäder från en äldre tjäderhanne</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5063,10 +5096,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123951665</v>
+        <v>123174186</v>
       </c>
       <c r="B39" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5079,37 +5112,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513434</v>
+        <v>513473</v>
       </c>
       <c r="R39" t="n">
-        <v>6732611</v>
+        <v>6732751</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5133,22 +5174,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Trol. sovträd med färsk och äldre spillning under</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5175,10 +5221,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123174259</v>
+        <v>123950117</v>
       </c>
       <c r="B40" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5187,49 +5233,50 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513476</v>
+        <v>513452</v>
       </c>
       <c r="R40" t="n">
-        <v>6732720</v>
+        <v>6732659</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5253,27 +5300,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>07:31</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5288,22 +5330,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123951744</v>
+        <v>123950580</v>
       </c>
       <c r="B41" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5312,25 +5354,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -5340,13 +5382,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513434</v>
+        <v>513442</v>
       </c>
       <c r="R41" t="n">
-        <v>6732611</v>
+        <v>6732640</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5375,7 +5417,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5385,12 +5427,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Dålig uppkoppling, bilder går inte atr få med</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5417,10 +5454,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123174131</v>
+        <v>123952048</v>
       </c>
       <c r="B42" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5429,49 +5466,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513575</v>
+        <v>513425</v>
       </c>
       <c r="R42" t="n">
-        <v>6732778</v>
+        <v>6732651</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5495,27 +5524,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>På mossig stubbe, troligen blåbärsspillning</t>
+          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5542,7 +5571,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123954347</v>
+        <v>123954554</v>
       </c>
       <c r="B43" t="n">
         <v>96979</v>
@@ -5578,17 +5607,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513440</v>
+        <v>513484</v>
       </c>
       <c r="R43" t="n">
-        <v>6732637</v>
+        <v>6732609</v>
       </c>
       <c r="S43" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5617,7 +5646,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5627,7 +5656,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5642,22 +5671,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123950247</v>
+        <v>123174257</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5666,45 +5695,49 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513435</v>
+        <v>513437</v>
       </c>
       <c r="R44" t="n">
-        <v>6732618</v>
+        <v>6732675</v>
       </c>
       <c r="S44" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5728,27 +5761,22 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5775,10 +5803,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123950905</v>
+        <v>123951744</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5787,25 +5815,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5815,10 +5843,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513442</v>
+        <v>513434</v>
       </c>
       <c r="R45" t="n">
-        <v>6732642</v>
+        <v>6732611</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5850,7 +5878,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5860,12 +5888,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
+          <t>Dålig uppkoppling, bilder går inte atr få med</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5892,10 +5920,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123174129</v>
+        <v>123950844</v>
       </c>
       <c r="B46" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5904,50 +5932,38 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513357</v>
+        <v>513461</v>
       </c>
       <c r="R46" t="n">
-        <v>6732614</v>
+        <v>6732632</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5974,27 +5990,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Fjäder från en äldre tjäderhanne</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6021,10 +6032,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123174257</v>
+        <v>123951665</v>
       </c>
       <c r="B47" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6037,45 +6048,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513437</v>
+        <v>513434</v>
       </c>
       <c r="R47" t="n">
-        <v>6732675</v>
+        <v>6732611</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6099,22 +6102,22 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6141,10 +6144,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123953103</v>
+        <v>123951367</v>
       </c>
       <c r="B48" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6153,38 +6156,38 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513440</v>
+        <v>513441</v>
       </c>
       <c r="R48" t="n">
-        <v>6732637</v>
+        <v>6732633</v>
       </c>
       <c r="S48" t="n">
         <v>1</v>
@@ -6216,7 +6219,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6226,7 +6229,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6253,10 +6256,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123174162</v>
+        <v>123953103</v>
       </c>
       <c r="B49" t="n">
-        <v>56722</v>
+        <v>5176</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6269,45 +6272,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513433</v>
+        <v>513440</v>
       </c>
       <c r="R49" t="n">
-        <v>6732675</v>
+        <v>6732637</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6331,27 +6326,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>06:45</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Under tall, troligt sovträd</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6366,22 +6356,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123174186</v>
+        <v>123950247</v>
       </c>
       <c r="B50" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6390,49 +6380,45 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513473</v>
+        <v>513435</v>
       </c>
       <c r="R50" t="n">
-        <v>6732751</v>
+        <v>6732618</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6456,27 +6442,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Trol. sovträd med färsk och äldre spillning under</t>
+          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6503,7 +6489,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122789602</v>
+        <v>122791693</v>
       </c>
       <c r="B51" t="n">
         <v>56722</v>
@@ -6541,7 +6527,7 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
@@ -6551,13 +6537,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513429</v>
+        <v>513491</v>
       </c>
       <c r="R51" t="n">
-        <v>6732681</v>
+        <v>6732749</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6586,7 +6572,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6596,12 +6582,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Några hundratal spillning under s.k. sovtall</t>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6628,10 +6614,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123174256</v>
+        <v>123953543</v>
       </c>
       <c r="B52" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6640,46 +6626,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513476</v>
+        <v>513415</v>
       </c>
       <c r="R52" t="n">
-        <v>6732711</v>
+        <v>6732596</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6706,22 +6684,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6748,10 +6726,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123950117</v>
+        <v>123174141</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6760,50 +6738,49 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513452</v>
+        <v>513432</v>
       </c>
       <c r="R53" t="n">
-        <v>6732659</v>
+        <v>6732690</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6827,22 +6804,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Sovträd med spillning under.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6857,22 +6839,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123953543</v>
+        <v>123951771</v>
       </c>
       <c r="B54" t="n">
-        <v>78810</v>
+        <v>96985</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6881,41 +6863,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>221941</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513415</v>
+        <v>513461</v>
       </c>
       <c r="R54" t="n">
-        <v>6732596</v>
+        <v>6732598</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6944,7 +6926,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6954,7 +6936,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6981,10 +6963,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123951312</v>
+        <v>123174130</v>
       </c>
       <c r="B55" t="n">
-        <v>96985</v>
+        <v>56722</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6997,37 +6979,45 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513430</v>
+        <v>513586</v>
       </c>
       <c r="R55" t="n">
-        <v>6732614</v>
+        <v>6732786</v>
       </c>
       <c r="S55" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7051,27 +7041,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Några plantor</t>
+          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7098,10 +7088,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122791693</v>
+        <v>123949803</v>
       </c>
       <c r="B56" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7110,49 +7100,41 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513491</v>
+        <v>513439</v>
       </c>
       <c r="R56" t="n">
-        <v>6732749</v>
+        <v>6732649</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7176,27 +7158,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7223,10 +7200,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122789501</v>
+        <v>123956562</v>
       </c>
       <c r="B57" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7239,49 +7216,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513426</v>
+        <v>513514</v>
       </c>
       <c r="R57" t="n">
-        <v>6732668</v>
+        <v>6732646</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7305,27 +7270,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7352,10 +7312,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123956562</v>
+        <v>123174162</v>
       </c>
       <c r="B58" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7368,34 +7328,42 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513514</v>
+        <v>513433</v>
       </c>
       <c r="R58" t="n">
-        <v>6732646</v>
+        <v>6732675</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7422,22 +7390,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Under tall, troligt sovträd</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7464,10 +7437,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123951367</v>
+        <v>122789501</v>
       </c>
       <c r="B59" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7476,41 +7449,53 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513441</v>
+        <v>513426</v>
       </c>
       <c r="R59" t="n">
-        <v>6732633</v>
+        <v>6732668</v>
       </c>
       <c r="S59" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7534,22 +7519,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7564,19 +7554,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123949914</v>
+        <v>123949969</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7610,19 +7600,23 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513440</v>
+        <v>513443</v>
       </c>
       <c r="R60" t="n">
-        <v>6732648</v>
+        <v>6732646</v>
       </c>
       <c r="S60" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7651,7 +7645,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7661,12 +7655,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
+          <t>Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7675,6 +7669,7 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
+      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7693,7 +7688,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123949803</v>
+        <v>123949914</v>
       </c>
       <c r="B61" t="n">
         <v>98101</v>
@@ -7733,10 +7728,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513439</v>
+        <v>513440</v>
       </c>
       <c r="R61" t="n">
-        <v>6732649</v>
+        <v>6732648</v>
       </c>
       <c r="S61" t="n">
         <v>5</v>
@@ -7768,7 +7763,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7778,7 +7773,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY62"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3553,7 +3553,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123955316</v>
+        <v>123951367</v>
       </c>
       <c r="B26" t="n">
         <v>98101</v>
@@ -3589,14 +3589,14 @@
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513440</v>
+        <v>513441</v>
       </c>
       <c r="R26" t="n">
-        <v>6732637</v>
+        <v>6732633</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3638,7 +3638,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3665,7 +3665,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123174258</v>
+        <v>123174162</v>
       </c>
       <c r="B27" t="n">
         <v>56722</v>
@@ -3713,10 +3713,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513428</v>
+        <v>513433</v>
       </c>
       <c r="R27" t="n">
-        <v>6732689</v>
+        <v>6732675</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3748,7 +3748,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3758,7 +3758,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Under tall, troligt sovträd</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3785,10 +3790,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123174131</v>
+        <v>123953543</v>
       </c>
       <c r="B28" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3797,46 +3802,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513575</v>
+        <v>513415</v>
       </c>
       <c r="R28" t="n">
-        <v>6732778</v>
+        <v>6732596</v>
       </c>
       <c r="S28" t="n">
         <v>25</v>
@@ -3863,27 +3860,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>På mossig stubbe, troligen blåbärsspillning</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3910,10 +3902,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123174259</v>
+        <v>123955316</v>
       </c>
       <c r="B29" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3922,49 +3914,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513476</v>
+        <v>513440</v>
       </c>
       <c r="R29" t="n">
-        <v>6732720</v>
+        <v>6732637</v>
       </c>
       <c r="S29" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3988,27 +3972,22 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>07:31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4023,22 +4002,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123954904</v>
+        <v>123949914</v>
       </c>
       <c r="B30" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4047,41 +4026,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
         <v>513440</v>
       </c>
       <c r="R30" t="n">
-        <v>6732637</v>
+        <v>6732648</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4110,7 +4089,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4120,7 +4099,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4135,22 +4119,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123951312</v>
+        <v>123174258</v>
       </c>
       <c r="B31" t="n">
-        <v>96985</v>
+        <v>56722</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4163,37 +4147,45 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513430</v>
+        <v>513428</v>
       </c>
       <c r="R31" t="n">
-        <v>6732614</v>
+        <v>6732689</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4217,27 +4209,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Några plantor</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4264,10 +4251,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123950905</v>
+        <v>123954221</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4276,38 +4263,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513442</v>
+        <v>513440</v>
       </c>
       <c r="R32" t="n">
-        <v>6732642</v>
+        <v>6732637</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4339,7 +4326,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4349,12 +4336,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4369,22 +4351,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123951412</v>
+        <v>122789602</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4393,41 +4375,49 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513434</v>
+        <v>513429</v>
       </c>
       <c r="R33" t="n">
-        <v>6732611</v>
+        <v>6732681</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4451,22 +4441,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:44</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Några hundratal spillning under s.k. sovtall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4493,10 +4488,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123956767</v>
+        <v>123949969</v>
       </c>
       <c r="B34" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4505,38 +4500,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513447</v>
+        <v>513443</v>
       </c>
       <c r="R34" t="n">
-        <v>6732560</v>
+        <v>6732646</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4568,7 +4567,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4578,7 +4577,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4587,6 +4591,7 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
+      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4605,7 +4610,7 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>122789602</v>
+        <v>123174257</v>
       </c>
       <c r="B35" t="n">
         <v>56722</v>
@@ -4649,17 +4654,17 @@
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513429</v>
+        <v>513437</v>
       </c>
       <c r="R35" t="n">
-        <v>6732681</v>
+        <v>6732675</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4683,27 +4688,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Några hundratal spillning under s.k. sovtall</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4730,10 +4730,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123953880</v>
+        <v>123951771</v>
       </c>
       <c r="B36" t="n">
-        <v>56722</v>
+        <v>96985</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4746,42 +4746,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513440</v>
+        <v>513461</v>
       </c>
       <c r="R36" t="n">
-        <v>6732637</v>
+        <v>6732598</v>
       </c>
       <c r="S36" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4810,7 +4805,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4820,7 +4815,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4835,22 +4830,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123174256</v>
+        <v>123951286</v>
       </c>
       <c r="B37" t="n">
-        <v>56722</v>
+        <v>96985</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4863,45 +4858,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513476</v>
+        <v>513430</v>
       </c>
       <c r="R37" t="n">
-        <v>6732711</v>
+        <v>6732614</v>
       </c>
       <c r="S37" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4925,22 +4912,27 @@
       </c>
       <c r="Y37" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:34</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Kammossa linnea, olika vitmossor, björnmossaetc</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4967,7 +4959,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123174129</v>
+        <v>123174141</v>
       </c>
       <c r="B38" t="n">
         <v>56722</v>
@@ -5000,16 +4992,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
       <c r="M38" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N38" t="inlineStr"/>
@@ -5019,10 +5007,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513357</v>
+        <v>513432</v>
       </c>
       <c r="R38" t="n">
-        <v>6732614</v>
+        <v>6732690</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5054,7 +5042,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5064,12 +5052,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Fjäder från en äldre tjäderhanne</t>
+          <t>Sovträd med spillning under.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5096,10 +5084,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123174186</v>
+        <v>123951599</v>
       </c>
       <c r="B39" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5108,49 +5096,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513473</v>
+        <v>513434</v>
       </c>
       <c r="R39" t="n">
-        <v>6732751</v>
+        <v>6732611</v>
       </c>
       <c r="S39" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5174,27 +5154,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Trol. sovträd med färsk och äldre spillning under</t>
+          <t>Snön har legat länge i de skuggiga svackorna</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5221,10 +5201,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123950117</v>
+        <v>123953720</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5233,50 +5213,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513452</v>
+        <v>513440</v>
       </c>
       <c r="R40" t="n">
-        <v>6732659</v>
+        <v>6732637</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5305,7 +5276,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5315,7 +5286,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5342,10 +5318,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123950580</v>
+        <v>123953103</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>5176</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5354,41 +5330,41 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513442</v>
+        <v>513440</v>
       </c>
       <c r="R41" t="n">
-        <v>6732640</v>
+        <v>6732637</v>
       </c>
       <c r="S41" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5417,7 +5393,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5427,7 +5403,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5442,22 +5418,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123952048</v>
+        <v>123174131</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5466,41 +5442,49 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513425</v>
+        <v>513575</v>
       </c>
       <c r="R42" t="n">
-        <v>6732651</v>
+        <v>6732778</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5524,27 +5508,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
+          <t>På mossig stubbe, troligen blåbärsspillning</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5571,7 +5555,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123954554</v>
+        <v>123956562</v>
       </c>
       <c r="B43" t="n">
         <v>96979</v>
@@ -5607,17 +5591,17 @@
       <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513484</v>
+        <v>513514</v>
       </c>
       <c r="R43" t="n">
-        <v>6732609</v>
+        <v>6732646</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5646,7 +5630,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5656,7 +5640,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5683,10 +5667,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123174257</v>
+        <v>123951744</v>
       </c>
       <c r="B44" t="n">
-        <v>56722</v>
+        <v>96985</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5699,45 +5683,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513437</v>
+        <v>513434</v>
       </c>
       <c r="R44" t="n">
-        <v>6732675</v>
+        <v>6732611</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5761,22 +5737,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Dålig uppkoppling, bilder går inte atr få med</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5803,10 +5784,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123951744</v>
+        <v>123954554</v>
       </c>
       <c r="B45" t="n">
-        <v>96985</v>
+        <v>96979</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5819,16 +5800,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5839,17 +5820,17 @@
       <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513434</v>
+        <v>513484</v>
       </c>
       <c r="R45" t="n">
-        <v>6732611</v>
+        <v>6732609</v>
       </c>
       <c r="S45" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5878,7 +5859,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5888,12 +5869,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Dålig uppkoppling, bilder går inte atr få med</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5920,10 +5896,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123950844</v>
+        <v>123174259</v>
       </c>
       <c r="B46" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5932,38 +5908,46 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513461</v>
+        <v>513476</v>
       </c>
       <c r="R46" t="n">
-        <v>6732632</v>
+        <v>6732720</v>
       </c>
       <c r="S46" t="n">
         <v>25</v>
@@ -5990,22 +5974,27 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6032,10 +6021,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123951665</v>
+        <v>123950905</v>
       </c>
       <c r="B47" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6044,25 +6033,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6072,10 +6061,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513434</v>
+        <v>513442</v>
       </c>
       <c r="R47" t="n">
-        <v>6732611</v>
+        <v>6732642</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6107,7 +6096,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6117,7 +6106,12 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6144,7 +6138,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123951367</v>
+        <v>123950247</v>
       </c>
       <c r="B48" t="n">
         <v>98101</v>
@@ -6177,20 +6171,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513441</v>
+        <v>513435</v>
       </c>
       <c r="R48" t="n">
-        <v>6732633</v>
+        <v>6732618</v>
       </c>
       <c r="S48" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6219,7 +6217,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6229,7 +6227,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6244,22 +6247,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123953103</v>
+        <v>123956767</v>
       </c>
       <c r="B49" t="n">
-        <v>5176</v>
+        <v>96979</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6272,34 +6275,34 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100526</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513440</v>
+        <v>513447</v>
       </c>
       <c r="R49" t="n">
-        <v>6732637</v>
+        <v>6732560</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6331,7 +6334,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6341,7 +6344,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6356,19 +6359,19 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123950247</v>
+        <v>123950117</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -6403,7 +6406,12 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6412,13 +6420,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513435</v>
+        <v>513452</v>
       </c>
       <c r="R50" t="n">
-        <v>6732618</v>
+        <v>6732659</v>
       </c>
       <c r="S50" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6447,7 +6455,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6457,12 +6465,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6477,22 +6480,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122791693</v>
+        <v>123949803</v>
       </c>
       <c r="B51" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6501,49 +6504,41 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513491</v>
+        <v>513439</v>
       </c>
       <c r="R51" t="n">
-        <v>6732749</v>
+        <v>6732649</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6567,27 +6562,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6614,10 +6604,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123953543</v>
+        <v>123950844</v>
       </c>
       <c r="B52" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6626,38 +6616,38 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513415</v>
+        <v>513461</v>
       </c>
       <c r="R52" t="n">
-        <v>6732596</v>
+        <v>6732632</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6689,7 +6679,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6699,7 +6689,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6726,10 +6716,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123174141</v>
+        <v>123951665</v>
       </c>
       <c r="B53" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6742,45 +6732,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513432</v>
+        <v>513434</v>
       </c>
       <c r="R53" t="n">
-        <v>6732690</v>
+        <v>6732611</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6804,27 +6786,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Sovträd med spillning under.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6851,10 +6828,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123951771</v>
+        <v>123950580</v>
       </c>
       <c r="B54" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6863,41 +6840,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513461</v>
+        <v>513442</v>
       </c>
       <c r="R54" t="n">
-        <v>6732598</v>
+        <v>6732640</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6926,7 +6903,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6936,7 +6913,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6963,7 +6940,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123174130</v>
+        <v>122789501</v>
       </c>
       <c r="B55" t="n">
         <v>56722</v>
@@ -6996,28 +6973,32 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513586</v>
+        <v>513426</v>
       </c>
       <c r="R55" t="n">
-        <v>6732786</v>
+        <v>6732668</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7041,27 +7022,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
+          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7088,10 +7069,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123949803</v>
+        <v>123174130</v>
       </c>
       <c r="B56" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7100,41 +7081,49 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513439</v>
+        <v>513586</v>
       </c>
       <c r="R56" t="n">
-        <v>6732649</v>
+        <v>6732786</v>
       </c>
       <c r="S56" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7158,22 +7147,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7200,10 +7194,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123956562</v>
+        <v>122791693</v>
       </c>
       <c r="B57" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7216,34 +7210,42 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513514</v>
+        <v>513491</v>
       </c>
       <c r="R57" t="n">
-        <v>6732646</v>
+        <v>6732749</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7270,22 +7272,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>17:01</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7312,7 +7319,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123174162</v>
+        <v>123174129</v>
       </c>
       <c r="B58" t="n">
         <v>56722</v>
@@ -7345,12 +7352,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7360,10 +7371,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513433</v>
+        <v>513357</v>
       </c>
       <c r="R58" t="n">
-        <v>6732675</v>
+        <v>6732614</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7390,27 +7401,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Under tall, troligt sovträd</t>
+          <t>Fjäder från en äldre tjäderhanne</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7437,7 +7448,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>122789501</v>
+        <v>123174186</v>
       </c>
       <c r="B59" t="n">
         <v>56722</v>
@@ -7470,11 +7481,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
@@ -7485,17 +7492,17 @@
       <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513426</v>
+        <v>513473</v>
       </c>
       <c r="R59" t="n">
-        <v>6732668</v>
+        <v>6732751</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7519,27 +7526,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
+          <t>Trol. sovträd med färsk och äldre spillning under</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7566,7 +7573,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123949969</v>
+        <v>123952048</v>
       </c>
       <c r="B60" t="n">
         <v>98101</v>
@@ -7600,23 +7607,19 @@
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513443</v>
+        <v>513425</v>
       </c>
       <c r="R60" t="n">
-        <v>6732646</v>
+        <v>6732651</v>
       </c>
       <c r="S60" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7645,7 +7648,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7655,12 +7658,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Mellanskog avverkar</t>
+          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7669,7 +7672,6 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
@@ -7688,10 +7690,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123949914</v>
+        <v>123174256</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7700,41 +7702,49 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513440</v>
+        <v>513476</v>
       </c>
       <c r="R61" t="n">
-        <v>6732648</v>
+        <v>6732711</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7758,27 +7768,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7929,6 +7934,127 @@
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>123949134</v>
+      </c>
+      <c r="B63" t="n">
+        <v>98101</v>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>513481</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6732705</v>
+      </c>
+      <c r="S63" t="n">
+        <v>5</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-04-10</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Evalena Sköld</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -3553,10 +3553,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123951367</v>
+        <v>123174162</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3565,41 +3565,49 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513441</v>
+        <v>513433</v>
       </c>
       <c r="R26" t="n">
-        <v>6732633</v>
+        <v>6732675</v>
       </c>
       <c r="S26" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3623,22 +3631,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Under tall, troligt sovträd</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3653,19 +3666,19 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123174162</v>
+        <v>123174130</v>
       </c>
       <c r="B27" t="n">
         <v>56722</v>
@@ -3703,20 +3716,20 @@
       <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513433</v>
+        <v>513586</v>
       </c>
       <c r="R27" t="n">
-        <v>6732675</v>
+        <v>6732786</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3743,27 +3756,27 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Under tall, troligt sovträd</t>
+          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3790,10 +3803,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123953543</v>
+        <v>123950247</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3802,41 +3815,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513415</v>
+        <v>513435</v>
       </c>
       <c r="R28" t="n">
-        <v>6732596</v>
+        <v>6732618</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3865,7 +3882,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3875,7 +3892,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3902,7 +3924,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123955316</v>
+        <v>123952048</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3942,13 +3964,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513440</v>
+        <v>513425</v>
       </c>
       <c r="R29" t="n">
-        <v>6732637</v>
+        <v>6732651</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3977,7 +3999,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3987,7 +4009,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>15:18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4002,22 +4029,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123949914</v>
+        <v>123954347</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4026,41 +4053,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
         <v>513440</v>
       </c>
       <c r="R30" t="n">
-        <v>6732648</v>
+        <v>6732637</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4089,7 +4116,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4099,12 +4126,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:36</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4119,22 +4141,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123174258</v>
+        <v>123951744</v>
       </c>
       <c r="B31" t="n">
-        <v>56722</v>
+        <v>96985</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4147,45 +4169,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513428</v>
+        <v>513434</v>
       </c>
       <c r="R31" t="n">
-        <v>6732689</v>
+        <v>6732611</v>
       </c>
       <c r="S31" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4209,22 +4223,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Dålig uppkoppling, bilder går inte atr få med</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4251,10 +4270,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123954221</v>
+        <v>123950580</v>
       </c>
       <c r="B32" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4263,41 +4282,41 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513440</v>
+        <v>513442</v>
       </c>
       <c r="R32" t="n">
-        <v>6732637</v>
+        <v>6732640</v>
       </c>
       <c r="S32" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4326,7 +4345,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4336,7 +4355,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:50</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4351,22 +4370,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>122789602</v>
+        <v>123951599</v>
       </c>
       <c r="B33" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4375,49 +4394,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513429</v>
+        <v>513434</v>
       </c>
       <c r="R33" t="n">
-        <v>6732681</v>
+        <v>6732611</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4441,27 +4452,27 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>Några hundratal spillning under s.k. sovtall</t>
+          <t>Snön har legat länge i de skuggiga svackorna</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4488,10 +4499,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123949969</v>
+        <v>123953720</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4500,42 +4511,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr"/>
-      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513443</v>
+        <v>513440</v>
       </c>
       <c r="R34" t="n">
-        <v>6732646</v>
+        <v>6732637</v>
       </c>
       <c r="S34" t="n">
         <v>1</v>
@@ -4567,7 +4574,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4577,12 +4584,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>Mellanskog avverkar</t>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4591,29 +4598,28 @@
       <c r="AE34" t="b">
         <v>0</v>
       </c>
-      <c r="AF34" t="inlineStr"/>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123174257</v>
+        <v>123951771</v>
       </c>
       <c r="B35" t="n">
-        <v>56722</v>
+        <v>96985</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4626,45 +4632,37 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513437</v>
+        <v>513461</v>
       </c>
       <c r="R35" t="n">
-        <v>6732675</v>
+        <v>6732598</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4688,22 +4686,22 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4730,10 +4728,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123951771</v>
+        <v>123955846</v>
       </c>
       <c r="B36" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4742,25 +4740,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4770,13 +4768,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513461</v>
+        <v>513440</v>
       </c>
       <c r="R36" t="n">
-        <v>6732598</v>
+        <v>6732637</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4805,7 +4803,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4815,7 +4813,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4830,19 +4828,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123951286</v>
+        <v>123951312</v>
       </c>
       <c r="B37" t="n">
         <v>96985</v>
@@ -4917,7 +4915,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4927,12 +4925,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Kammossa linnea, olika vitmossor, björnmossaetc</t>
+          <t>Några plantor</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4959,7 +4957,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123174141</v>
+        <v>123174256</v>
       </c>
       <c r="B38" t="n">
         <v>56722</v>
@@ -5007,10 +5005,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513432</v>
+        <v>513476</v>
       </c>
       <c r="R38" t="n">
-        <v>6732690</v>
+        <v>6732711</v>
       </c>
       <c r="S38" t="n">
         <v>25</v>
@@ -5042,7 +5040,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5052,12 +5050,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Sovträd med spillning under.</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5084,10 +5077,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123951599</v>
+        <v>123954554</v>
       </c>
       <c r="B39" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5096,41 +5089,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513434</v>
+        <v>513484</v>
       </c>
       <c r="R39" t="n">
-        <v>6732611</v>
+        <v>6732609</v>
       </c>
       <c r="S39" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5159,7 +5152,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5169,12 +5162,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Snön har legat länge i de skuggiga svackorna</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5201,7 +5189,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123953720</v>
+        <v>123174131</v>
       </c>
       <c r="B40" t="n">
         <v>56722</v>
@@ -5235,19 +5223,27 @@
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513440</v>
+        <v>513575</v>
       </c>
       <c r="R40" t="n">
-        <v>6732637</v>
+        <v>6732778</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5271,27 +5267,27 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Spillning</t>
+          <t>På mossig stubbe, troligen blåbärsspillning</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5306,22 +5302,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123953103</v>
+        <v>123950117</v>
       </c>
       <c r="B41" t="n">
-        <v>5176</v>
+        <v>98101</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5330,41 +5326,50 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100526</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513440</v>
+        <v>513452</v>
       </c>
       <c r="R41" t="n">
-        <v>6732637</v>
+        <v>6732659</v>
       </c>
       <c r="S41" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5393,7 +5398,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5403,7 +5408,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5430,10 +5435,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123174131</v>
+        <v>123953543</v>
       </c>
       <c r="B42" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5442,46 +5447,38 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513575</v>
+        <v>513415</v>
       </c>
       <c r="R42" t="n">
-        <v>6732778</v>
+        <v>6732596</v>
       </c>
       <c r="S42" t="n">
         <v>25</v>
@@ -5508,27 +5505,22 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>På mossig stubbe, troligen blåbärsspillning</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5555,10 +5547,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123956562</v>
+        <v>122789501</v>
       </c>
       <c r="B43" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5571,37 +5563,49 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513514</v>
+        <v>513426</v>
       </c>
       <c r="R43" t="n">
-        <v>6732646</v>
+        <v>6732668</v>
       </c>
       <c r="S43" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5625,22 +5629,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5667,10 +5676,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123951744</v>
+        <v>123953103</v>
       </c>
       <c r="B44" t="n">
-        <v>96985</v>
+        <v>5176</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5683,34 +5692,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221941</v>
+        <v>100526</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513434</v>
+        <v>513440</v>
       </c>
       <c r="R44" t="n">
-        <v>6732611</v>
+        <v>6732637</v>
       </c>
       <c r="S44" t="n">
         <v>1</v>
@@ -5742,7 +5751,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5752,12 +5761,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Dålig uppkoppling, bilder går inte atr få med</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5772,22 +5776,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123954554</v>
+        <v>123949969</v>
       </c>
       <c r="B45" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5796,41 +5800,45 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513484</v>
+        <v>513443</v>
       </c>
       <c r="R45" t="n">
-        <v>6732609</v>
+        <v>6732646</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5859,7 +5867,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5869,7 +5877,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5878,6 +5891,7 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
+      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5896,10 +5910,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123174259</v>
+        <v>123949803</v>
       </c>
       <c r="B46" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5908,49 +5922,41 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513476</v>
+        <v>513439</v>
       </c>
       <c r="R46" t="n">
-        <v>6732720</v>
+        <v>6732649</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5974,27 +5980,22 @@
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>07:31</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6021,10 +6022,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123950905</v>
+        <v>123951665</v>
       </c>
       <c r="B47" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6033,25 +6034,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -6061,10 +6062,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513442</v>
+        <v>513434</v>
       </c>
       <c r="R47" t="n">
-        <v>6732642</v>
+        <v>6732611</v>
       </c>
       <c r="S47" t="n">
         <v>1</v>
@@ -6096,7 +6097,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -6106,12 +6107,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6138,10 +6134,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123950247</v>
+        <v>122789602</v>
       </c>
       <c r="B48" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6150,45 +6146,49 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513435</v>
+        <v>513429</v>
       </c>
       <c r="R48" t="n">
-        <v>6732618</v>
+        <v>6732681</v>
       </c>
       <c r="S48" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6212,27 +6212,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
+          <t>Några hundratal spillning under s.k. sovtall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6259,10 +6259,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123956767</v>
+        <v>123950905</v>
       </c>
       <c r="B49" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6271,38 +6271,38 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513447</v>
+        <v>513442</v>
       </c>
       <c r="R49" t="n">
-        <v>6732560</v>
+        <v>6732642</v>
       </c>
       <c r="S49" t="n">
         <v>1</v>
@@ -6334,7 +6334,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6344,7 +6344,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6371,7 +6376,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123950117</v>
+        <v>123950844</v>
       </c>
       <c r="B50" t="n">
         <v>98101</v>
@@ -6404,29 +6409,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513452</v>
+        <v>513461</v>
       </c>
       <c r="R50" t="n">
-        <v>6732659</v>
+        <v>6732632</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6455,7 +6451,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6465,7 +6461,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6480,22 +6476,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123949803</v>
+        <v>123174259</v>
       </c>
       <c r="B51" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6504,41 +6500,49 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513439</v>
+        <v>513476</v>
       </c>
       <c r="R51" t="n">
-        <v>6732649</v>
+        <v>6732720</v>
       </c>
       <c r="S51" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6562,22 +6566,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6604,7 +6613,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123950844</v>
+        <v>123949914</v>
       </c>
       <c r="B52" t="n">
         <v>98101</v>
@@ -6640,17 +6649,17 @@
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513461</v>
+        <v>513440</v>
       </c>
       <c r="R52" t="n">
-        <v>6732632</v>
+        <v>6732648</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6679,7 +6688,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6689,7 +6698,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6716,10 +6730,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123951665</v>
+        <v>123174258</v>
       </c>
       <c r="B53" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6732,37 +6746,45 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513434</v>
+        <v>513428</v>
       </c>
       <c r="R53" t="n">
-        <v>6732611</v>
+        <v>6732689</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6786,22 +6808,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6828,10 +6850,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123950580</v>
+        <v>123174257</v>
       </c>
       <c r="B54" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6840,41 +6862,49 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513442</v>
+        <v>513437</v>
       </c>
       <c r="R54" t="n">
-        <v>6732640</v>
+        <v>6732675</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6898,22 +6928,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6940,7 +6970,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>122789501</v>
+        <v>123174186</v>
       </c>
       <c r="B55" t="n">
         <v>56722</v>
@@ -6973,11 +7003,7 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
@@ -6988,17 +7014,17 @@
       <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513426</v>
+        <v>513473</v>
       </c>
       <c r="R55" t="n">
-        <v>6732668</v>
+        <v>6732751</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7022,27 +7048,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
+          <t>Trol. sovträd med färsk och äldre spillning under</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7069,7 +7095,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123174130</v>
+        <v>122791693</v>
       </c>
       <c r="B56" t="n">
         <v>56722</v>
@@ -7113,14 +7139,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513586</v>
+        <v>513491</v>
       </c>
       <c r="R56" t="n">
-        <v>6732786</v>
+        <v>6732749</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7147,27 +7173,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7194,10 +7220,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>122791693</v>
+        <v>123951367</v>
       </c>
       <c r="B57" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7206,49 +7232,41 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513491</v>
+        <v>513441</v>
       </c>
       <c r="R57" t="n">
-        <v>6732749</v>
+        <v>6732633</v>
       </c>
       <c r="S57" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7272,27 +7290,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7307,19 +7320,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123174129</v>
+        <v>123174141</v>
       </c>
       <c r="B58" t="n">
         <v>56722</v>
@@ -7352,16 +7365,12 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N58" t="inlineStr"/>
@@ -7371,10 +7380,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513357</v>
+        <v>513432</v>
       </c>
       <c r="R58" t="n">
-        <v>6732614</v>
+        <v>6732690</v>
       </c>
       <c r="S58" t="n">
         <v>25</v>
@@ -7406,7 +7415,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7416,12 +7425,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Fjäder från en äldre tjäderhanne</t>
+          <t>Sovträd med spillning under.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7448,7 +7457,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123174186</v>
+        <v>123174129</v>
       </c>
       <c r="B59" t="n">
         <v>56722</v>
@@ -7481,12 +7490,16 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
       <c r="M59" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N59" t="inlineStr"/>
@@ -7496,10 +7509,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513473</v>
+        <v>513357</v>
       </c>
       <c r="R59" t="n">
-        <v>6732751</v>
+        <v>6732614</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7526,27 +7539,27 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Trol. sovträd med färsk och äldre spillning under</t>
+          <t>Fjäder från en äldre tjäderhanne</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7573,10 +7586,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123952048</v>
+        <v>123956562</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7585,25 +7598,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -7613,13 +7626,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513425</v>
+        <v>513514</v>
       </c>
       <c r="R60" t="n">
-        <v>6732651</v>
+        <v>6732646</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7648,7 +7661,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7658,12 +7671,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:18</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7690,10 +7698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123174256</v>
+        <v>123956767</v>
       </c>
       <c r="B61" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7706,45 +7714,37 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513476</v>
+        <v>513447</v>
       </c>
       <c r="R61" t="n">
-        <v>6732711</v>
+        <v>6732560</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7768,22 +7768,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -3553,10 +3553,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123174162</v>
+        <v>123951286</v>
       </c>
       <c r="B26" t="n">
-        <v>56722</v>
+        <v>96985</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3569,45 +3569,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513433</v>
+        <v>513430</v>
       </c>
       <c r="R26" t="n">
-        <v>6732675</v>
+        <v>6732614</v>
       </c>
       <c r="S26" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3631,27 +3623,27 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>14:34</t>
         </is>
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Under tall, troligt sovträd</t>
+          <t>Kammossa linnea, olika vitmossor, björnmossaetc</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3678,10 +3670,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123174130</v>
+        <v>123951429</v>
       </c>
       <c r="B27" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3690,49 +3682,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>513586</v>
+        <v>513440</v>
       </c>
       <c r="R27" t="n">
-        <v>6732786</v>
+        <v>6732637</v>
       </c>
       <c r="S27" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3756,27 +3740,22 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3791,22 +3770,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123950247</v>
+        <v>123174256</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3815,45 +3794,49 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513435</v>
+        <v>513476</v>
       </c>
       <c r="R28" t="n">
-        <v>6732618</v>
+        <v>6732711</v>
       </c>
       <c r="S28" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3877,27 +3860,22 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3924,7 +3902,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123952048</v>
+        <v>123949969</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3958,19 +3936,23 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513425</v>
+        <v>513443</v>
       </c>
       <c r="R29" t="n">
-        <v>6732651</v>
+        <v>6732646</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3999,7 +3981,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -4009,12 +3991,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC29" t="inlineStr">
         <is>
-          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
+          <t>Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4023,6 +4005,7 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
+      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4041,10 +4024,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123954347</v>
+        <v>122789501</v>
       </c>
       <c r="B30" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4057,37 +4040,49 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513440</v>
+        <v>513426</v>
       </c>
       <c r="R30" t="n">
-        <v>6732637</v>
+        <v>6732668</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4111,22 +4106,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4141,22 +4141,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123951744</v>
+        <v>123950580</v>
       </c>
       <c r="B31" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4165,25 +4165,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4193,13 +4193,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513434</v>
+        <v>513442</v>
       </c>
       <c r="R31" t="n">
-        <v>6732611</v>
+        <v>6732640</v>
       </c>
       <c r="S31" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4238,12 +4238,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Dålig uppkoppling, bilder går inte atr få med</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4270,10 +4265,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123950580</v>
+        <v>123951744</v>
       </c>
       <c r="B32" t="n">
-        <v>98101</v>
+        <v>96985</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4282,25 +4277,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>221941</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4310,13 +4305,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513442</v>
+        <v>513434</v>
       </c>
       <c r="R32" t="n">
-        <v>6732640</v>
+        <v>6732611</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4345,7 +4340,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4355,7 +4350,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Dålig uppkoppling, bilder går inte atr få med</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4382,10 +4382,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123951599</v>
+        <v>123174258</v>
       </c>
       <c r="B33" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4394,41 +4394,49 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513434</v>
+        <v>513428</v>
       </c>
       <c r="R33" t="n">
-        <v>6732611</v>
+        <v>6732689</v>
       </c>
       <c r="S33" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4452,27 +4460,22 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:52</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Snön har legat länge i de skuggiga svackorna</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4499,10 +4502,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123953720</v>
+        <v>123950117</v>
       </c>
       <c r="B34" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4511,41 +4514,50 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513440</v>
+        <v>513452</v>
       </c>
       <c r="R34" t="n">
-        <v>6732637</v>
+        <v>6732659</v>
       </c>
       <c r="S34" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4574,7 +4586,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4584,12 +4596,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4616,10 +4623,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123951771</v>
+        <v>123956562</v>
       </c>
       <c r="B35" t="n">
-        <v>96985</v>
+        <v>96979</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4632,16 +4639,16 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221941</v>
+        <v>221945</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -4656,13 +4663,13 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513461</v>
+        <v>513514</v>
       </c>
       <c r="R35" t="n">
-        <v>6732598</v>
+        <v>6732646</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4691,7 +4698,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4701,7 +4708,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4728,10 +4735,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123955846</v>
+        <v>123954904</v>
       </c>
       <c r="B36" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4740,25 +4747,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4803,7 +4810,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4813,7 +4820,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4840,10 +4847,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123951312</v>
+        <v>123949803</v>
       </c>
       <c r="B37" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4852,25 +4859,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4880,13 +4887,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513430</v>
+        <v>513439</v>
       </c>
       <c r="R37" t="n">
-        <v>6732614</v>
+        <v>6732649</v>
       </c>
       <c r="S37" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4915,7 +4922,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>14:36</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4925,12 +4932,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>14:36</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Några plantor</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4957,7 +4959,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123174256</v>
+        <v>123953720</v>
       </c>
       <c r="B38" t="n">
         <v>56722</v>
@@ -4991,27 +4993,19 @@
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513476</v>
+        <v>513440</v>
       </c>
       <c r="R38" t="n">
-        <v>6732711</v>
+        <v>6732637</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5035,22 +5029,27 @@
       </c>
       <c r="Y38" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:29</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5065,22 +5064,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123954554</v>
+        <v>123951771</v>
       </c>
       <c r="B39" t="n">
-        <v>96979</v>
+        <v>96985</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5093,16 +5092,16 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
@@ -5113,14 +5112,14 @@
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513484</v>
+        <v>513461</v>
       </c>
       <c r="R39" t="n">
-        <v>6732609</v>
+        <v>6732598</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5152,7 +5151,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -5162,7 +5161,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5189,10 +5188,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123174131</v>
+        <v>123951367</v>
       </c>
       <c r="B40" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5201,49 +5200,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513575</v>
+        <v>513441</v>
       </c>
       <c r="R40" t="n">
-        <v>6732778</v>
+        <v>6732633</v>
       </c>
       <c r="S40" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5267,27 +5258,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På mossig stubbe, troligen blåbärsspillning</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5302,22 +5288,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123950117</v>
+        <v>123954554</v>
       </c>
       <c r="B41" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5326,47 +5312,38 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513452</v>
+        <v>513484</v>
       </c>
       <c r="R41" t="n">
-        <v>6732659</v>
+        <v>6732609</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5398,7 +5375,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5408,7 +5385,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5423,22 +5400,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123953543</v>
+        <v>123950905</v>
       </c>
       <c r="B42" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5447,25 +5424,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5475,13 +5452,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513415</v>
+        <v>513442</v>
       </c>
       <c r="R42" t="n">
-        <v>6732596</v>
+        <v>6732642</v>
       </c>
       <c r="S42" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5510,7 +5487,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5520,7 +5497,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>14:16</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5547,10 +5529,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>122789501</v>
+        <v>123952048</v>
       </c>
       <c r="B43" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5559,50 +5541,38 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513426</v>
+        <v>513425</v>
       </c>
       <c r="R43" t="n">
-        <v>6732668</v>
+        <v>6732651</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5629,27 +5599,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
+          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5676,10 +5646,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123953103</v>
+        <v>123174259</v>
       </c>
       <c r="B44" t="n">
-        <v>5176</v>
+        <v>56722</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5692,37 +5662,45 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513440</v>
+        <v>513476</v>
       </c>
       <c r="R44" t="n">
-        <v>6732637</v>
+        <v>6732720</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5746,22 +5724,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5776,22 +5759,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123949969</v>
+        <v>123951665</v>
       </c>
       <c r="B45" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5800,42 +5783,38 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>513443</v>
+        <v>513434</v>
       </c>
       <c r="R45" t="n">
-        <v>6732646</v>
+        <v>6732611</v>
       </c>
       <c r="S45" t="n">
         <v>1</v>
@@ -5867,7 +5846,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5877,12 +5856,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Mellanskog avverkar</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5891,7 +5865,6 @@
       <c r="AE45" t="b">
         <v>0</v>
       </c>
-      <c r="AF45" t="inlineStr"/>
       <c r="AG45" t="b">
         <v>0</v>
       </c>
@@ -5910,7 +5883,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123949803</v>
+        <v>123951599</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5950,13 +5923,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>513439</v>
+        <v>513434</v>
       </c>
       <c r="R46" t="n">
-        <v>6732649</v>
+        <v>6732611</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5985,7 +5958,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5995,7 +5968,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:52</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Snön har legat länge i de skuggiga svackorna</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6022,10 +6000,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123951665</v>
+        <v>123174162</v>
       </c>
       <c r="B47" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6038,37 +6016,45 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513434</v>
+        <v>513433</v>
       </c>
       <c r="R47" t="n">
-        <v>6732611</v>
+        <v>6732675</v>
       </c>
       <c r="S47" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6092,22 +6078,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Under tall, troligt sovträd</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6134,7 +6125,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>122789602</v>
+        <v>123174141</v>
       </c>
       <c r="B48" t="n">
         <v>56722</v>
@@ -6178,17 +6169,17 @@
       <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513429</v>
+        <v>513432</v>
       </c>
       <c r="R48" t="n">
-        <v>6732681</v>
+        <v>6732690</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6212,27 +6203,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Några hundratal spillning under s.k. sovtall</t>
+          <t>Sovträd med spillning under.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6259,10 +6250,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123950905</v>
+        <v>123174257</v>
       </c>
       <c r="B49" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6271,41 +6262,49 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513442</v>
+        <v>513437</v>
       </c>
       <c r="R49" t="n">
-        <v>6732642</v>
+        <v>6732675</v>
       </c>
       <c r="S49" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6329,27 +6328,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6376,10 +6370,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123950844</v>
+        <v>123174129</v>
       </c>
       <c r="B50" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6388,38 +6382,50 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513461</v>
+        <v>513357</v>
       </c>
       <c r="R50" t="n">
-        <v>6732632</v>
+        <v>6732614</v>
       </c>
       <c r="S50" t="n">
         <v>25</v>
@@ -6446,22 +6452,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Fjäder från en äldre tjäderhanne</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6488,7 +6499,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>123174259</v>
+        <v>122791693</v>
       </c>
       <c r="B51" t="n">
         <v>56722</v>
@@ -6526,20 +6537,20 @@
       <c r="L51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513476</v>
+        <v>513491</v>
       </c>
       <c r="R51" t="n">
-        <v>6732720</v>
+        <v>6732749</v>
       </c>
       <c r="S51" t="n">
         <v>25</v>
@@ -6566,27 +6577,27 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6730,10 +6741,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123174258</v>
+        <v>123950247</v>
       </c>
       <c r="B53" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6742,49 +6753,45 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513428</v>
+        <v>513435</v>
       </c>
       <c r="R53" t="n">
-        <v>6732689</v>
+        <v>6732618</v>
       </c>
       <c r="S53" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6808,22 +6815,27 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>13:52</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6850,10 +6862,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123174257</v>
+        <v>123956767</v>
       </c>
       <c r="B54" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6866,45 +6878,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513437</v>
+        <v>513447</v>
       </c>
       <c r="R54" t="n">
-        <v>6732675</v>
+        <v>6732560</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6928,22 +6932,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6970,7 +6974,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123174186</v>
+        <v>123174131</v>
       </c>
       <c r="B55" t="n">
         <v>56722</v>
@@ -7008,7 +7012,7 @@
       <c r="L55" t="inlineStr"/>
       <c r="M55" t="inlineStr">
         <is>
-          <t>färsk spillning</t>
+          <t>äldre spillning</t>
         </is>
       </c>
       <c r="N55" t="inlineStr"/>
@@ -7018,10 +7022,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513473</v>
+        <v>513575</v>
       </c>
       <c r="R55" t="n">
-        <v>6732751</v>
+        <v>6732778</v>
       </c>
       <c r="S55" t="n">
         <v>25</v>
@@ -7048,27 +7052,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Trol. sovträd med färsk och äldre spillning under</t>
+          <t>På mossig stubbe, troligen blåbärsspillning</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7095,7 +7099,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>122791693</v>
+        <v>123174130</v>
       </c>
       <c r="B56" t="n">
         <v>56722</v>
@@ -7139,14 +7143,14 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513491</v>
+        <v>513586</v>
       </c>
       <c r="R56" t="n">
-        <v>6732749</v>
+        <v>6732786</v>
       </c>
       <c r="S56" t="n">
         <v>25</v>
@@ -7173,27 +7177,27 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Blåbärsspillning</t>
+          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7220,10 +7224,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123951367</v>
+        <v>123174186</v>
       </c>
       <c r="B57" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7232,41 +7236,49 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513441</v>
+        <v>513473</v>
       </c>
       <c r="R57" t="n">
-        <v>6732633</v>
+        <v>6732751</v>
       </c>
       <c r="S57" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -7290,22 +7302,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>07:39</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Trol. sovträd med färsk och äldre spillning under</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7320,22 +7337,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123174141</v>
+        <v>123953103</v>
       </c>
       <c r="B58" t="n">
-        <v>56722</v>
+        <v>5176</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7348,45 +7365,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="K58" t="inlineStr"/>
-      <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513432</v>
+        <v>513440</v>
       </c>
       <c r="R58" t="n">
-        <v>6732690</v>
+        <v>6732637</v>
       </c>
       <c r="S58" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7410,27 +7419,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:55</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Sovträd med spillning under.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7445,22 +7449,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123174129</v>
+        <v>123953543</v>
       </c>
       <c r="B59" t="n">
-        <v>56722</v>
+        <v>78810</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7469,50 +7473,38 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513357</v>
+        <v>513415</v>
       </c>
       <c r="R59" t="n">
-        <v>6732614</v>
+        <v>6732596</v>
       </c>
       <c r="S59" t="n">
         <v>25</v>
@@ -7539,27 +7531,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Fjäder från en äldre tjäderhanne</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7586,10 +7573,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123956562</v>
+        <v>122789602</v>
       </c>
       <c r="B60" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7602,37 +7589,45 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513514</v>
+        <v>513429</v>
       </c>
       <c r="R60" t="n">
-        <v>6732646</v>
+        <v>6732681</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7656,22 +7651,27 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Några hundratal spillning under s.k. sovtall</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7698,10 +7698,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123956767</v>
+        <v>123950844</v>
       </c>
       <c r="B61" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7710,41 +7710,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513447</v>
+        <v>513461</v>
       </c>
       <c r="R61" t="n">
-        <v>6732560</v>
+        <v>6732632</v>
       </c>
       <c r="S61" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7773,7 +7773,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7783,7 +7783,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -3902,7 +3902,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123949969</v>
+        <v>123950580</v>
       </c>
       <c r="B29" t="n">
         <v>98101</v>
@@ -3936,23 +3936,19 @@
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513443</v>
+        <v>513442</v>
       </c>
       <c r="R29" t="n">
-        <v>6732646</v>
+        <v>6732640</v>
       </c>
       <c r="S29" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3981,7 +3977,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3991,12 +3987,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Mellanskog avverkar</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4005,7 +3996,6 @@
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -4024,10 +4014,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>122789501</v>
+        <v>123949969</v>
       </c>
       <c r="B30" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4036,53 +4026,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513426</v>
+        <v>513443</v>
       </c>
       <c r="R30" t="n">
-        <v>6732668</v>
+        <v>6732646</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4106,27 +4088,27 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC30" t="inlineStr">
         <is>
-          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
+          <t>Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4135,6 +4117,7 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4153,10 +4136,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>123950580</v>
+        <v>122789501</v>
       </c>
       <c r="B31" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4165,41 +4148,53 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513442</v>
+        <v>513426</v>
       </c>
       <c r="R31" t="n">
-        <v>6732640</v>
+        <v>6732668</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4223,22 +4218,27 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -5300,10 +5300,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123954554</v>
+        <v>123174259</v>
       </c>
       <c r="B41" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -5316,37 +5316,45 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513484</v>
+        <v>513476</v>
       </c>
       <c r="R41" t="n">
-        <v>6732609</v>
+        <v>6732720</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5370,22 +5378,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5412,10 +5425,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123950905</v>
+        <v>123954554</v>
       </c>
       <c r="B42" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5424,41 +5437,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513442</v>
+        <v>513484</v>
       </c>
       <c r="R42" t="n">
-        <v>6732642</v>
+        <v>6732609</v>
       </c>
       <c r="S42" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5487,7 +5500,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5497,12 +5510,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>14:16</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5646,10 +5654,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123174259</v>
+        <v>123950905</v>
       </c>
       <c r="B44" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5658,49 +5666,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513476</v>
+        <v>513442</v>
       </c>
       <c r="R44" t="n">
-        <v>6732720</v>
+        <v>6732642</v>
       </c>
       <c r="S44" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5724,27 +5724,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
+          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -6624,10 +6624,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123949914</v>
+        <v>123174131</v>
       </c>
       <c r="B52" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6636,41 +6636,49 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513440</v>
+        <v>513575</v>
       </c>
       <c r="R52" t="n">
-        <v>6732648</v>
+        <v>6732778</v>
       </c>
       <c r="S52" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6694,27 +6702,27 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
+          <t>På mossig stubbe, troligen blåbärsspillning</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6741,10 +6749,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123950247</v>
+        <v>123956767</v>
       </c>
       <c r="B53" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6753,45 +6761,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513435</v>
+        <v>513447</v>
       </c>
       <c r="R53" t="n">
-        <v>6732618</v>
+        <v>6732560</v>
       </c>
       <c r="S53" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6820,7 +6824,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6830,12 +6834,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:52</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6862,10 +6861,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123956767</v>
+        <v>123949914</v>
       </c>
       <c r="B54" t="n">
-        <v>96979</v>
+        <v>98101</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6874,41 +6873,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513447</v>
+        <v>513440</v>
       </c>
       <c r="R54" t="n">
-        <v>6732560</v>
+        <v>6732648</v>
       </c>
       <c r="S54" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6937,7 +6936,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6947,7 +6946,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6974,10 +6978,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123174131</v>
+        <v>123950247</v>
       </c>
       <c r="B55" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6986,49 +6990,45 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513575</v>
+        <v>513435</v>
       </c>
       <c r="R55" t="n">
-        <v>6732778</v>
+        <v>6732618</v>
       </c>
       <c r="S55" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7052,27 +7052,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>På mossig stubbe, troligen blåbärsspillning</t>
+          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7573,10 +7573,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>122789602</v>
+        <v>123950844</v>
       </c>
       <c r="B60" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7585,49 +7585,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513429</v>
+        <v>513461</v>
       </c>
       <c r="R60" t="n">
-        <v>6732681</v>
+        <v>6732632</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7651,27 +7643,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Några hundratal spillning under s.k. sovtall</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7698,10 +7685,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>123950844</v>
+        <v>122789602</v>
       </c>
       <c r="B61" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7710,41 +7697,49 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513461</v>
+        <v>513429</v>
       </c>
       <c r="R61" t="n">
-        <v>6732632</v>
+        <v>6732681</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7768,22 +7763,27 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Några hundratal spillning under s.k. sovtall</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -3553,10 +3553,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>123951286</v>
+        <v>123951367</v>
       </c>
       <c r="B26" t="n">
-        <v>96985</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3565,25 +3565,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3593,10 +3593,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>513430</v>
+        <v>513441</v>
       </c>
       <c r="R26" t="n">
-        <v>6732614</v>
+        <v>6732633</v>
       </c>
       <c r="S26" t="n">
         <v>1</v>
@@ -3628,7 +3628,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>14:34</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3638,12 +3638,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>14:34</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Kammossa linnea, olika vitmossor, björnmossaetc</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3658,22 +3653,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>123951429</v>
+        <v>123954904</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3682,31 +3677,31 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q27" t="n">
@@ -3745,7 +3740,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3755,7 +3750,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>14:45</t>
+          <t>17:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3782,10 +3777,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>123174256</v>
+        <v>123951312</v>
       </c>
       <c r="B28" t="n">
-        <v>56722</v>
+        <v>96985</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3798,45 +3793,37 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>513476</v>
+        <v>513430</v>
       </c>
       <c r="R28" t="n">
-        <v>6732711</v>
+        <v>6732614</v>
       </c>
       <c r="S28" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3860,22 +3847,27 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:36</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:36</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Några plantor</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3902,10 +3894,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>123950580</v>
+        <v>123174130</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3914,41 +3906,49 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>513442</v>
+        <v>513586</v>
       </c>
       <c r="R29" t="n">
-        <v>6732640</v>
+        <v>6732786</v>
       </c>
       <c r="S29" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3972,22 +3972,27 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:08</t>
+          <t>14:41</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4014,10 +4019,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>123949969</v>
+        <v>123956562</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -4026,45 +4031,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>513443</v>
+        <v>513514</v>
       </c>
       <c r="R30" t="n">
         <v>6732646</v>
       </c>
       <c r="S30" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -4093,7 +4094,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -4103,12 +4104,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Mellanskog avverkar</t>
+          <t>18:54</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4117,7 +4113,6 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
@@ -4136,10 +4131,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>122789501</v>
+        <v>123951771</v>
       </c>
       <c r="B31" t="n">
-        <v>56722</v>
+        <v>96985</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -4152,46 +4147,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100138</v>
+        <v>221941</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>513426</v>
+        <v>513461</v>
       </c>
       <c r="R31" t="n">
-        <v>6732668</v>
+        <v>6732598</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4218,27 +4201,22 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4265,10 +4243,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>123951744</v>
+        <v>123953880</v>
       </c>
       <c r="B32" t="n">
-        <v>96985</v>
+        <v>56722</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -4281,34 +4259,39 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>513434</v>
+        <v>513440</v>
       </c>
       <c r="R32" t="n">
-        <v>6732611</v>
+        <v>6732637</v>
       </c>
       <c r="S32" t="n">
         <v>1</v>
@@ -4340,7 +4323,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>15:01</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4350,12 +4333,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>15:01</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Dålig uppkoppling, bilder går inte atr få med</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4370,19 +4348,19 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>123174258</v>
+        <v>123174162</v>
       </c>
       <c r="B33" t="n">
         <v>56722</v>
@@ -4430,10 +4408,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>513428</v>
+        <v>513433</v>
       </c>
       <c r="R33" t="n">
-        <v>6732689</v>
+        <v>6732675</v>
       </c>
       <c r="S33" t="n">
         <v>25</v>
@@ -4465,7 +4443,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:45</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4475,7 +4453,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>06:51</t>
+          <t>06:45</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Under tall, troligt sovträd</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4502,10 +4485,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>123950117</v>
+        <v>123174258</v>
       </c>
       <c r="B34" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4514,50 +4497,49 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>513452</v>
+        <v>513428</v>
       </c>
       <c r="R34" t="n">
-        <v>6732659</v>
+        <v>6732689</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4581,22 +4563,22 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>13:44</t>
+          <t>06:51</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4611,22 +4593,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>123956562</v>
+        <v>123174131</v>
       </c>
       <c r="B35" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4639,34 +4621,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>513514</v>
+        <v>513575</v>
       </c>
       <c r="R35" t="n">
-        <v>6732646</v>
+        <v>6732778</v>
       </c>
       <c r="S35" t="n">
         <v>25</v>
@@ -4693,22 +4683,27 @@
       </c>
       <c r="Y35" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>14:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-28</t>
         </is>
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>18:54</t>
+          <t>14:38</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>På mossig stubbe, troligen blåbärsspillning</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4735,7 +4730,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>123954904</v>
+        <v>123951665</v>
       </c>
       <c r="B36" t="n">
         <v>96979</v>
@@ -4771,14 +4766,14 @@
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>513440</v>
+        <v>513434</v>
       </c>
       <c r="R36" t="n">
-        <v>6732637</v>
+        <v>6732611</v>
       </c>
       <c r="S36" t="n">
         <v>1</v>
@@ -4810,7 +4805,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4820,7 +4815,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>17:14</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4835,19 +4830,19 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>123949803</v>
+        <v>123951429</v>
       </c>
       <c r="B37" t="n">
         <v>98101</v>
@@ -4887,13 +4882,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>513439</v>
+        <v>513440</v>
       </c>
       <c r="R37" t="n">
-        <v>6732649</v>
+        <v>6732637</v>
       </c>
       <c r="S37" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4922,7 +4917,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4932,7 +4927,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>13:32</t>
+          <t>14:45</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4947,22 +4942,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>123953720</v>
+        <v>123950580</v>
       </c>
       <c r="B38" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4971,41 +4966,41 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>513440</v>
+        <v>513442</v>
       </c>
       <c r="R38" t="n">
-        <v>6732637</v>
+        <v>6732640</v>
       </c>
       <c r="S38" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -5034,7 +5029,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -5044,12 +5039,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>16:29</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>14:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5064,22 +5054,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>123951771</v>
+        <v>123174259</v>
       </c>
       <c r="B39" t="n">
-        <v>96985</v>
+        <v>56722</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -5092,37 +5082,45 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>221941</v>
+        <v>100138</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>513461</v>
+        <v>513476</v>
       </c>
       <c r="R39" t="n">
-        <v>6732598</v>
+        <v>6732720</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -5146,22 +5144,27 @@
       </c>
       <c r="Y39" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>07:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>15:04</t>
+          <t>07:31</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5188,10 +5191,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>123951367</v>
+        <v>123174256</v>
       </c>
       <c r="B40" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -5200,41 +5203,49 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>513441</v>
+        <v>513476</v>
       </c>
       <c r="R40" t="n">
-        <v>6732633</v>
+        <v>6732711</v>
       </c>
       <c r="S40" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5258,22 +5269,22 @@
       </c>
       <c r="Y40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5288,19 +5299,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>123174259</v>
+        <v>122789501</v>
       </c>
       <c r="B41" t="n">
         <v>56722</v>
@@ -5333,7 +5344,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr">
@@ -5344,17 +5359,17 @@
       <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>513476</v>
+        <v>513426</v>
       </c>
       <c r="R41" t="n">
-        <v>6732720</v>
+        <v>6732668</v>
       </c>
       <c r="S41" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5378,27 +5393,27 @@
       </c>
       <c r="Y41" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>07:31</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Väldigt utspridda runt hela trädet. gick inte att få något rättvis foto.</t>
+          <t>Ett 40-tal spillning under äldre/gammal tall, s.k. sovtall</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5425,10 +5440,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>123954554</v>
+        <v>123174129</v>
       </c>
       <c r="B42" t="n">
-        <v>96979</v>
+        <v>56722</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -5441,37 +5456,49 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>221945</v>
+        <v>100138</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Lögkarsmyren, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>513484</v>
+        <v>513357</v>
       </c>
       <c r="R42" t="n">
-        <v>6732609</v>
+        <v>6732614</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5495,22 +5522,27 @@
       </c>
       <c r="Y42" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>16:59</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Fjäder från en äldre tjäderhanne</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5537,10 +5569,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>123952048</v>
+        <v>123174186</v>
       </c>
       <c r="B43" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5549,41 +5581,49 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr"/>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr"/>
       <c r="P43" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>513425</v>
+        <v>513473</v>
       </c>
       <c r="R43" t="n">
-        <v>6732651</v>
+        <v>6732751</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5607,27 +5647,27 @@
       </c>
       <c r="Y43" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-05</t>
         </is>
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>15:18</t>
+          <t>07:39</t>
         </is>
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
+          <t>Trol. sovträd med färsk och äldre spillning under</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5654,10 +5694,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>123950905</v>
+        <v>122789602</v>
       </c>
       <c r="B44" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5666,41 +5706,49 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>513442</v>
+        <v>513429</v>
       </c>
       <c r="R44" t="n">
-        <v>6732642</v>
+        <v>6732681</v>
       </c>
       <c r="S44" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5724,27 +5772,27 @@
       </c>
       <c r="Y44" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
+          <t>Några hundratal spillning under s.k. sovtall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5771,10 +5819,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>123951665</v>
+        <v>123951744</v>
       </c>
       <c r="B45" t="n">
-        <v>96979</v>
+        <v>96985</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5787,16 +5835,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5846,7 +5894,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:01</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5856,7 +5904,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>15:01</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Dålig uppkoppling, bilder går inte atr få med</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5883,7 +5936,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>123951599</v>
+        <v>123951374</v>
       </c>
       <c r="B46" t="n">
         <v>98101</v>
@@ -5916,7 +5969,19 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
@@ -5958,7 +6023,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5968,12 +6033,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Snön har legat länge i de skuggiga svackorna</t>
+          <t>Avverkning pågår</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5982,6 +6047,7 @@
       <c r="AE46" t="b">
         <v>0</v>
       </c>
+      <c r="AF46" t="inlineStr"/>
       <c r="AG46" t="b">
         <v>0</v>
       </c>
@@ -6000,10 +6066,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>123174162</v>
+        <v>123950247</v>
       </c>
       <c r="B47" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -6012,49 +6078,45 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr"/>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>513433</v>
+        <v>513435</v>
       </c>
       <c r="R47" t="n">
-        <v>6732675</v>
+        <v>6732618</v>
       </c>
       <c r="S47" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -6078,27 +6140,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>06:45</t>
+          <t>13:52</t>
         </is>
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Under tall, troligt sovträd</t>
+          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6125,10 +6187,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>123174141</v>
+        <v>123950905</v>
       </c>
       <c r="B48" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -6137,49 +6199,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="K48" t="inlineStr"/>
-      <c r="L48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>513432</v>
+        <v>513442</v>
       </c>
       <c r="R48" t="n">
-        <v>6732690</v>
+        <v>6732642</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -6203,27 +6257,27 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>16:55</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Sovträd med spillning under.</t>
+          <t>Kammossa överalkt och snön har legat kvar här länge.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6250,10 +6304,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>123174257</v>
+        <v>123954554</v>
       </c>
       <c r="B49" t="n">
-        <v>56722</v>
+        <v>96979</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -6266,45 +6320,37 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100138</v>
+        <v>221945</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
-      <c r="L49" t="inlineStr"/>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyren, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>513437</v>
+        <v>513484</v>
       </c>
       <c r="R49" t="n">
-        <v>6732675</v>
+        <v>6732609</v>
       </c>
       <c r="S49" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -6328,22 +6374,22 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>16:47</t>
+          <t>16:59</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6370,10 +6416,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>123174129</v>
+        <v>123949914</v>
       </c>
       <c r="B50" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -6382,53 +6428,41 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>513357</v>
+        <v>513440</v>
       </c>
       <c r="R50" t="n">
-        <v>6732614</v>
+        <v>6732648</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6452,27 +6486,27 @@
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2025-03-02</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>13:36</t>
         </is>
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Fjäder från en äldre tjäderhanne</t>
+          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6499,10 +6533,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>122791693</v>
+        <v>123950117</v>
       </c>
       <c r="B51" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -6511,49 +6545,50 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>513491</v>
+        <v>513452</v>
       </c>
       <c r="R51" t="n">
-        <v>6732749</v>
+        <v>6732659</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6577,27 +6612,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:01</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:01</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Blåbärsspillning</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6612,19 +6642,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>123174131</v>
+        <v>123174257</v>
       </c>
       <c r="B52" t="n">
         <v>56722</v>
@@ -6662,7 +6692,7 @@
       <c r="L52" t="inlineStr"/>
       <c r="M52" t="inlineStr">
         <is>
-          <t>äldre spillning</t>
+          <t>färsk spillning</t>
         </is>
       </c>
       <c r="N52" t="inlineStr"/>
@@ -6672,10 +6702,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>513575</v>
+        <v>513437</v>
       </c>
       <c r="R52" t="n">
-        <v>6732778</v>
+        <v>6732675</v>
       </c>
       <c r="S52" t="n">
         <v>25</v>
@@ -6702,27 +6732,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>14:38</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>14:38</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>På mossig stubbe, troligen blåbärsspillning</t>
+          <t>16:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6749,10 +6774,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>123956767</v>
+        <v>123953543</v>
       </c>
       <c r="B53" t="n">
-        <v>96979</v>
+        <v>78810</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6761,41 +6786,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>513447</v>
+        <v>513415</v>
       </c>
       <c r="R53" t="n">
-        <v>6732560</v>
+        <v>6732596</v>
       </c>
       <c r="S53" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6824,7 +6849,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6834,7 +6859,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>19:02</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6861,7 +6886,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>123949914</v>
+        <v>123952048</v>
       </c>
       <c r="B54" t="n">
         <v>98101</v>
@@ -6897,17 +6922,17 @@
       <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>513440</v>
+        <v>513425</v>
       </c>
       <c r="R54" t="n">
-        <v>6732648</v>
+        <v>6732651</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6936,7 +6961,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6946,12 +6971,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>15:18</t>
         </is>
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ett hundratal utspridda inom fem meter. Mellanskog avverkar</t>
+          <t>Mycket, mycket kammossa, linnea, vitmossor, blåbärsris,</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6978,10 +7003,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>123950247</v>
+        <v>122791693</v>
       </c>
       <c r="B55" t="n">
-        <v>98101</v>
+        <v>56722</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6990,45 +7015,49 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
+          <t>Falun, Falun, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>513435</v>
+        <v>513491</v>
       </c>
       <c r="R55" t="n">
-        <v>6732618</v>
+        <v>6732749</v>
       </c>
       <c r="S55" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -7052,27 +7081,27 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-02-27</t>
         </is>
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:52</t>
+          <t>17:01</t>
         </is>
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Avverkningsmaskinen kör en liten bit härifrån.</t>
+          <t>Blåbärsspillning</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7099,10 +7128,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>123174130</v>
+        <v>123953103</v>
       </c>
       <c r="B56" t="n">
-        <v>56722</v>
+        <v>5176</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -7115,45 +7144,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100138</v>
+        <v>100526</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Lögkarsmyran , Dlr</t>
+          <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>513586</v>
+        <v>513440</v>
       </c>
       <c r="R56" t="n">
-        <v>6732786</v>
+        <v>6732637</v>
       </c>
       <c r="S56" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -7177,27 +7198,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>14:41</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-02-28</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>14:41</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Luckigt, barrblandskog med mycket blåbärsris. Men tyvärr färre gömställen för fåglar och mindre djur efter röjningen som gjordes för några dagar sedan.</t>
+          <t>16:10</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7212,22 +7228,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Evalena Sköld</t>
+          <t>Åke Sköld</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>123174186</v>
+        <v>123950844</v>
       </c>
       <c r="B57" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -7236,46 +7252,38 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="L57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>513473</v>
+        <v>513461</v>
       </c>
       <c r="R57" t="n">
-        <v>6732751</v>
+        <v>6732632</v>
       </c>
       <c r="S57" t="n">
         <v>25</v>
@@ -7302,27 +7310,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>07:39</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-03-05</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>07:39</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Trol. sovträd med färsk och äldre spillning under</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7349,10 +7352,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>123953103</v>
+        <v>123174141</v>
       </c>
       <c r="B58" t="n">
-        <v>5176</v>
+        <v>56722</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -7365,37 +7368,45 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100526</v>
+        <v>100138</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>513440</v>
+        <v>513432</v>
       </c>
       <c r="R58" t="n">
-        <v>6732637</v>
+        <v>6732690</v>
       </c>
       <c r="S58" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7419,22 +7430,27 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:55</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-04-10</t>
+          <t>2025-03-02</t>
         </is>
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>16:10</t>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Sovträd med spillning under.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7449,22 +7465,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Åke Sköld</t>
+          <t>Evalena Sköld</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>123953543</v>
+        <v>123949969</v>
       </c>
       <c r="B59" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -7473,41 +7489,45 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>513415</v>
+        <v>513443</v>
       </c>
       <c r="R59" t="n">
-        <v>6732596</v>
+        <v>6732646</v>
       </c>
       <c r="S59" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7536,7 +7556,7 @@
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
@@ -7546,7 +7566,12 @@
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>16:21</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Mellanskog avverkar</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7555,6 +7580,7 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
@@ -7573,10 +7599,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>123950844</v>
+        <v>123956767</v>
       </c>
       <c r="B60" t="n">
-        <v>98101</v>
+        <v>96979</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -7585,41 +7611,41 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>221945</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Lögkarsmyran, Dlr</t>
+          <t>Lögkarsmyran , Lögkarsmyran , Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>513461</v>
+        <v>513447</v>
       </c>
       <c r="R60" t="n">
-        <v>6732632</v>
+        <v>6732560</v>
       </c>
       <c r="S60" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7648,7 +7674,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -7658,7 +7684,7 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>19:02</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7685,10 +7711,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>122789602</v>
+        <v>123949803</v>
       </c>
       <c r="B61" t="n">
-        <v>56722</v>
+        <v>98101</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7697,49 +7723,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Falun, Falun, Dlr</t>
+          <t>Lögkarsmyran, Lögkarsmyran, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>513429</v>
+        <v>513439</v>
       </c>
       <c r="R61" t="n">
-        <v>6732681</v>
+        <v>6732649</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7763,27 +7781,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-02-27</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Några hundratal spillning under s.k. sovtall</t>
+          <t>13:32</t>
         </is>
       </c>
       <c r="AD61" t="b">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -7952,7 +7952,7 @@
         <v>123949134</v>
       </c>
       <c r="B63" t="n">
-        <v>98101</v>
+        <v>98269</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -5697,12 +5697,7 @@
         <v>122789602</v>
       </c>
       <c r="B44" t="n">
-        <v>56722</v>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56844</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5727,7 +5722,11 @@
           <t>Linnaeus, 1758</t>
         </is>
       </c>
-      <c r="I44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -5697,7 +5697,7 @@
         <v>122789602</v>
       </c>
       <c r="B44" t="n">
-        <v>56844</v>
+        <v>56848</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>

--- a/artfynd/A 7236-2025 artfynd.xlsx
+++ b/artfynd/A 7236-2025 artfynd.xlsx
@@ -5697,7 +5697,7 @@
         <v>122789602</v>
       </c>
       <c r="B44" t="n">
-        <v>56848</v>
+        <v>56849</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
